--- a/reports/2026-09-20.xlsx
+++ b/reports/2026-09-20.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64275E98-17BD-ED45-A36D-4E9CFDD3E893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D015837D-1BD9-AC46-AF59-ECE15DCF91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2632,7 +2632,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="586">
+  <cellXfs count="587">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3539,6 +3539,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="21" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4741,16 +4744,16 @@
     <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="417" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="417"/>
-      <c r="E1" s="417"/>
-      <c r="F1" s="417"/>
-      <c r="G1" s="417"/>
-      <c r="H1" s="417"/>
-      <c r="I1" s="417"/>
-      <c r="J1" s="417"/>
+      <c r="C1" s="418" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="418"/>
+      <c r="E1" s="418"/>
+      <c r="F1" s="418"/>
+      <c r="G1" s="418"/>
+      <c r="H1" s="418"/>
+      <c r="I1" s="418"/>
+      <c r="J1" s="418"/>
       <c r="K1" s="67" t="s">
         <v>247</v>
       </c>
@@ -4781,11 +4784,11 @@
     <row r="3" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="419" t="s">
+      <c r="C3" s="420" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="420"/>
-      <c r="E3" s="420"/>
+      <c r="D3" s="421"/>
+      <c r="E3" s="421"/>
       <c r="F3" s="89" t="s">
         <v>1</v>
       </c>
@@ -4798,24 +4801,24 @@
       <c r="I3" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="418" t="s">
+      <c r="J3" s="419" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="418"/>
-      <c r="L3" s="418"/>
-      <c r="M3" s="418"/>
-      <c r="N3" s="418"/>
-      <c r="O3" s="418"/>
-      <c r="P3" s="418"/>
+      <c r="K3" s="419"/>
+      <c r="L3" s="419"/>
+      <c r="M3" s="419"/>
+      <c r="N3" s="419"/>
+      <c r="O3" s="419"/>
+      <c r="P3" s="419"/>
     </row>
     <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="333"/>
-      <c r="C4" s="421" t="s">
+      <c r="B4" s="334"/>
+      <c r="C4" s="422" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="422"/>
-      <c r="E4" s="422"/>
+      <c r="D4" s="423"/>
+      <c r="E4" s="423"/>
       <c r="F4" s="91">
         <v>93</v>
       </c>
@@ -4824,10 +4827,10 @@
       </c>
       <c r="H4" s="92"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="426" t="s">
+      <c r="J4" s="427" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="426"/>
+      <c r="K4" s="427"/>
       <c r="L4" s="283" t="s">
         <v>168</v>
       </c>
@@ -4849,12 +4852,12 @@
     </row>
     <row r="5" spans="1:23" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="333"/>
-      <c r="C5" s="357" t="s">
+      <c r="B5" s="334"/>
+      <c r="C5" s="358" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="358"/>
-      <c r="E5" s="358"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="359"/>
       <c r="F5" s="91">
         <v>284</v>
       </c>
@@ -4865,10 +4868,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="431" t="s">
+      <c r="J5" s="432" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="431"/>
+      <c r="K5" s="432"/>
       <c r="L5" s="292" t="s">
         <v>176</v>
       </c>
@@ -4890,12 +4893,12 @@
     </row>
     <row r="6" spans="1:23" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="333"/>
-      <c r="C6" s="421" t="s">
+      <c r="B6" s="334"/>
+      <c r="C6" s="422" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="422"/>
-      <c r="E6" s="422"/>
+      <c r="D6" s="423"/>
+      <c r="E6" s="423"/>
       <c r="F6" s="91">
         <v>347</v>
       </c>
@@ -4906,10 +4909,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="334" t="s">
+      <c r="J6" s="335" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="334"/>
+      <c r="K6" s="335"/>
       <c r="L6" s="293" t="s">
         <v>177</v>
       </c>
@@ -4931,12 +4934,12 @@
     </row>
     <row r="7" spans="1:23" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="333"/>
-      <c r="C7" s="421" t="s">
+      <c r="B7" s="334"/>
+      <c r="C7" s="422" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="422"/>
-      <c r="E7" s="422"/>
+      <c r="D7" s="423"/>
+      <c r="E7" s="423"/>
       <c r="F7" s="164">
         <f>F4+F5-F6</f>
         <v>30</v>
@@ -4949,10 +4952,10 @@
         <v>7</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="402" t="s">
+      <c r="J7" s="403" t="s">
         <v>57</v>
       </c>
-      <c r="K7" s="402"/>
+      <c r="K7" s="403"/>
       <c r="L7" s="294">
         <v>999.91</v>
       </c>
@@ -4975,11 +4978,11 @@
     <row r="8" spans="1:23" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="429" t="s">
+      <c r="C8" s="430" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="430"/>
-      <c r="E8" s="430"/>
+      <c r="D8" s="431"/>
+      <c r="E8" s="431"/>
       <c r="F8" s="103">
         <v>0</v>
       </c>
@@ -4988,10 +4991,10 @@
       </c>
       <c r="H8" s="95"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="334" t="s">
+      <c r="J8" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="334"/>
+      <c r="K8" s="335"/>
       <c r="L8" s="294">
         <v>50000</v>
       </c>
@@ -5018,10 +5021,10 @@
       <c r="D9" s="10"/>
       <c r="E9" s="4"/>
       <c r="I9" s="11"/>
-      <c r="J9" s="334" t="s">
+      <c r="J9" s="335" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="334"/>
+      <c r="K9" s="335"/>
       <c r="L9" s="295">
         <f>50000-L8</f>
         <v>0</v>
@@ -5048,12 +5051,12 @@
     </row>
     <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="333"/>
-      <c r="C10" s="423" t="s">
+      <c r="B10" s="334"/>
+      <c r="C10" s="424" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="424"/>
-      <c r="E10" s="425"/>
+      <c r="D10" s="425"/>
+      <c r="E10" s="426"/>
       <c r="F10" s="89" t="s">
         <v>1</v>
       </c>
@@ -5064,14 +5067,14 @@
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="433" t="s">
+      <c r="J10" s="434" t="s">
         <v>144</v>
       </c>
-      <c r="K10" s="434"/>
-      <c r="L10" s="427">
+      <c r="K10" s="435"/>
+      <c r="L10" s="428">
         <v>15700</v>
       </c>
-      <c r="M10" s="428"/>
+      <c r="M10" s="429"/>
       <c r="N10" s="104"/>
       <c r="O10" s="104"/>
       <c r="P10" s="104"/>
@@ -5081,12 +5084,12 @@
     </row>
     <row r="11" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="333"/>
-      <c r="C11" s="359" t="s">
+      <c r="B11" s="334"/>
+      <c r="C11" s="360" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="360"/>
-      <c r="E11" s="361"/>
+      <c r="D11" s="361"/>
+      <c r="E11" s="362"/>
       <c r="F11" s="69">
         <v>105384</v>
       </c>
@@ -5097,29 +5100,29 @@
         <v>170224.48</v>
       </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="435" t="s">
+      <c r="J11" s="436" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="436"/>
-      <c r="L11" s="406">
+      <c r="K11" s="437"/>
+      <c r="L11" s="407">
         <v>13600</v>
       </c>
-      <c r="M11" s="407"/>
+      <c r="M11" s="408"/>
       <c r="N11" s="104"/>
       <c r="O11" s="86"/>
-      <c r="P11" s="432"/>
-      <c r="Q11" s="432"/>
-      <c r="R11" s="432"/>
+      <c r="P11" s="433"/>
+      <c r="Q11" s="433"/>
+      <c r="R11" s="433"/>
       <c r="S11" s="107"/>
     </row>
     <row r="12" spans="1:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="333"/>
-      <c r="C12" s="357" t="s">
+      <c r="B12" s="334"/>
+      <c r="C12" s="358" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="358"/>
-      <c r="E12" s="358"/>
+      <c r="D12" s="359"/>
+      <c r="E12" s="359"/>
       <c r="F12" s="69">
         <f>11169+10878+5590-3759</f>
         <v>23878</v>
@@ -5133,10 +5136,10 @@
       <c r="I12" s="12"/>
       <c r="N12" s="105"/>
       <c r="O12" s="86"/>
-      <c r="T12" s="437" t="s">
+      <c r="T12" s="438" t="s">
         <v>196</v>
       </c>
-      <c r="U12" s="438"/>
+      <c r="U12" s="439"/>
       <c r="V12" s="304" t="s">
         <v>49</v>
       </c>
@@ -5146,12 +5149,12 @@
     </row>
     <row r="13" spans="1:23" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="333"/>
-      <c r="C13" s="359" t="s">
+      <c r="B13" s="334"/>
+      <c r="C13" s="360" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="360"/>
-      <c r="E13" s="361"/>
+      <c r="D13" s="361"/>
+      <c r="E13" s="362"/>
       <c r="F13" s="69">
         <f>21446+11230+4475</f>
         <v>37151</v>
@@ -5163,20 +5166,20 @@
         <v>25355</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="423" t="s">
+      <c r="J13" s="424" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="424"/>
-      <c r="L13" s="424"/>
-      <c r="M13" s="425"/>
+      <c r="K13" s="425"/>
+      <c r="L13" s="425"/>
+      <c r="M13" s="426"/>
       <c r="N13" s="143" t="s">
         <v>95</v>
       </c>
       <c r="O13" s="106"/>
-      <c r="T13" s="437" t="s">
+      <c r="T13" s="438" t="s">
         <v>197</v>
       </c>
-      <c r="U13" s="437"/>
+      <c r="U13" s="438"/>
       <c r="V13" s="299">
         <f>N19+N20</f>
         <v>96700</v>
@@ -5188,12 +5191,12 @@
     </row>
     <row r="14" spans="1:23" s="13" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
-      <c r="B14" s="335"/>
-      <c r="C14" s="362" t="s">
+      <c r="B14" s="336"/>
+      <c r="C14" s="363" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="363"/>
-      <c r="E14" s="364"/>
+      <c r="D14" s="364"/>
+      <c r="E14" s="365"/>
       <c r="F14" s="73">
         <f>F11+F12-F13</f>
         <v>92111</v>
@@ -5207,44 +5210,44 @@
         <v>167849.88</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="379" t="s">
+      <c r="J14" s="380" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="380"/>
-      <c r="L14" s="380"/>
-      <c r="M14" s="327"/>
+      <c r="K14" s="381"/>
+      <c r="L14" s="381"/>
+      <c r="M14" s="328"/>
       <c r="N14" s="144"/>
       <c r="O14" s="16"/>
       <c r="P14" s="291"/>
-      <c r="T14" s="415"/>
-      <c r="U14" s="416"/>
+      <c r="T14" s="416"/>
+      <c r="U14" s="417"/>
       <c r="V14" s="302"/>
       <c r="W14" s="302"/>
     </row>
     <row r="15" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="333"/>
-      <c r="C15" s="403"/>
-      <c r="D15" s="404"/>
-      <c r="E15" s="405"/>
+      <c r="B15" s="334"/>
+      <c r="C15" s="404"/>
+      <c r="D15" s="405"/>
+      <c r="E15" s="406"/>
       <c r="F15" s="75"/>
       <c r="G15" s="76"/>
       <c r="H15" s="76"/>
       <c r="I15" s="17"/>
-      <c r="J15" s="408" t="s">
+      <c r="J15" s="409" t="s">
         <v>137</v>
       </c>
-      <c r="K15" s="409"/>
-      <c r="L15" s="409"/>
-      <c r="M15" s="410"/>
+      <c r="K15" s="410"/>
+      <c r="L15" s="410"/>
+      <c r="M15" s="411"/>
       <c r="N15" s="153">
         <v>102779</v>
       </c>
       <c r="O15" s="18"/>
-      <c r="T15" s="437" t="s">
+      <c r="T15" s="438" t="s">
         <v>198</v>
       </c>
-      <c r="U15" s="437"/>
+      <c r="U15" s="438"/>
       <c r="V15" s="298">
         <f>N31+N32</f>
         <v>48447</v>
@@ -5256,12 +5259,12 @@
     </row>
     <row r="16" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="333"/>
-      <c r="C16" s="393" t="s">
+      <c r="B16" s="334"/>
+      <c r="C16" s="394" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="394"/>
-      <c r="E16" s="395"/>
+      <c r="D16" s="395"/>
+      <c r="E16" s="396"/>
       <c r="F16" s="89" t="s">
         <v>49</v>
       </c>
@@ -5272,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="I16" s="17"/>
-      <c r="J16" s="411" t="s">
+      <c r="J16" s="412" t="s">
         <v>146</v>
       </c>
-      <c r="K16" s="412"/>
-      <c r="L16" s="412"/>
-      <c r="M16" s="413"/>
+      <c r="K16" s="413"/>
+      <c r="L16" s="413"/>
+      <c r="M16" s="414"/>
       <c r="N16" s="154">
         <v>60361</v>
       </c>
@@ -5285,19 +5288,19 @@
       <c r="Q16" s="65"/>
       <c r="R16" s="65"/>
       <c r="S16" s="65"/>
-      <c r="T16" s="444"/>
-      <c r="U16" s="445"/>
+      <c r="T16" s="445"/>
+      <c r="U16" s="446"/>
       <c r="V16" s="303"/>
       <c r="W16" s="303"/>
     </row>
     <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="333"/>
-      <c r="C17" s="359" t="s">
+      <c r="B17" s="334"/>
+      <c r="C17" s="360" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="360"/>
-      <c r="E17" s="361"/>
+      <c r="D17" s="361"/>
+      <c r="E17" s="362"/>
       <c r="F17" s="71">
         <f>51481+21994</f>
         <v>73475</v>
@@ -5310,12 +5313,12 @@
         <v>60139.519999999997</v>
       </c>
       <c r="I17" s="17"/>
-      <c r="J17" s="365" t="s">
+      <c r="J17" s="366" t="s">
         <v>147</v>
       </c>
-      <c r="K17" s="366"/>
-      <c r="L17" s="366"/>
-      <c r="M17" s="367"/>
+      <c r="K17" s="367"/>
+      <c r="L17" s="367"/>
+      <c r="M17" s="368"/>
       <c r="N17" s="154">
         <v>4272</v>
       </c>
@@ -5323,10 +5326,10 @@
       <c r="Q17" s="65"/>
       <c r="R17" s="65"/>
       <c r="S17" s="65"/>
-      <c r="T17" s="440" t="s">
+      <c r="T17" s="441" t="s">
         <v>222</v>
       </c>
-      <c r="U17" s="441"/>
+      <c r="U17" s="442"/>
       <c r="V17" s="297">
         <f>N41</f>
         <v>0</v>
@@ -5338,12 +5341,12 @@
     </row>
     <row r="18" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="333"/>
-      <c r="C18" s="359" t="s">
+      <c r="B18" s="334"/>
+      <c r="C18" s="360" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="360"/>
-      <c r="E18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="362"/>
       <c r="F18" s="71">
         <v>12576</v>
       </c>
@@ -5354,17 +5357,17 @@
         <v>53600.78</v>
       </c>
       <c r="I18" s="17"/>
-      <c r="J18" s="390" t="s">
+      <c r="J18" s="391" t="s">
         <v>94</v>
       </c>
-      <c r="K18" s="391"/>
-      <c r="L18" s="391"/>
-      <c r="M18" s="392"/>
+      <c r="K18" s="392"/>
+      <c r="L18" s="392"/>
+      <c r="M18" s="393"/>
       <c r="N18" s="150"/>
-      <c r="T18" s="442" t="s">
+      <c r="T18" s="443" t="s">
         <v>5</v>
       </c>
-      <c r="U18" s="443"/>
+      <c r="U18" s="444"/>
       <c r="V18" s="309">
         <f>SUM(V13:V17)</f>
         <v>145147</v>
@@ -5376,12 +5379,12 @@
     </row>
     <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="333"/>
-      <c r="C19" s="359" t="s">
+      <c r="B19" s="334"/>
+      <c r="C19" s="360" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="360"/>
-      <c r="E19" s="361"/>
+      <c r="D19" s="361"/>
+      <c r="E19" s="362"/>
       <c r="F19" s="71">
         <v>6060</v>
       </c>
@@ -5392,24 +5395,24 @@
         <v>54109.58</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="365" t="s">
+      <c r="J19" s="366" t="s">
         <v>148</v>
       </c>
-      <c r="K19" s="366"/>
-      <c r="L19" s="366"/>
-      <c r="M19" s="367"/>
+      <c r="K19" s="367"/>
+      <c r="L19" s="367"/>
+      <c r="M19" s="368"/>
       <c r="N19" s="150">
         <v>35740</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="333"/>
-      <c r="C20" s="359" t="s">
+      <c r="B20" s="334"/>
+      <c r="C20" s="360" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="360"/>
-      <c r="E20" s="361"/>
+      <c r="D20" s="361"/>
+      <c r="E20" s="362"/>
       <c r="F20" s="71">
         <v>0</v>
       </c>
@@ -5418,20 +5421,20 @@
       </c>
       <c r="H20" s="69"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="365" t="s">
+      <c r="J20" s="366" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="366"/>
-      <c r="L20" s="366"/>
-      <c r="M20" s="367"/>
+      <c r="K20" s="367"/>
+      <c r="L20" s="367"/>
+      <c r="M20" s="368"/>
       <c r="N20" s="150">
         <v>60960</v>
       </c>
-      <c r="S20" s="439" t="s">
+      <c r="S20" s="440" t="s">
         <v>228</v>
       </c>
-      <c r="T20" s="439"/>
-      <c r="U20" s="439"/>
+      <c r="T20" s="440"/>
+      <c r="U20" s="440"/>
       <c r="V20" s="312">
         <f>V18+W18</f>
         <v>428749</v>
@@ -5439,12 +5442,12 @@
     </row>
     <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="333"/>
-      <c r="C21" s="359" t="s">
+      <c r="B21" s="334"/>
+      <c r="C21" s="360" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="360"/>
-      <c r="E21" s="361"/>
+      <c r="D21" s="361"/>
+      <c r="E21" s="362"/>
       <c r="F21" s="71" t="s">
         <v>117</v>
       </c>
@@ -5453,21 +5456,21 @@
         <v>0</v>
       </c>
       <c r="I21" s="19"/>
-      <c r="J21" s="365"/>
-      <c r="K21" s="366"/>
-      <c r="L21" s="366"/>
-      <c r="M21" s="367"/>
+      <c r="J21" s="366"/>
+      <c r="K21" s="367"/>
+      <c r="L21" s="367"/>
+      <c r="M21" s="368"/>
       <c r="N21" s="150"/>
       <c r="P21" s="288"/>
     </row>
     <row r="22" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="333"/>
-      <c r="C22" s="371" t="s">
+      <c r="B22" s="334"/>
+      <c r="C22" s="372" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="372"/>
-      <c r="E22" s="373"/>
+      <c r="D22" s="373"/>
+      <c r="E22" s="374"/>
       <c r="F22" s="73">
         <f>SUM(F17:F21)</f>
         <v>92111</v>
@@ -5481,12 +5484,12 @@
         <v>167849.88</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="374" t="s">
+      <c r="J22" s="375" t="s">
         <v>141</v>
       </c>
-      <c r="K22" s="375"/>
-      <c r="L22" s="375"/>
-      <c r="M22" s="376"/>
+      <c r="K22" s="376"/>
+      <c r="L22" s="376"/>
+      <c r="M22" s="377"/>
       <c r="N22" s="155">
         <f>SUM(N15:N21)</f>
         <v>264112</v>
@@ -5495,7 +5498,7 @@
     </row>
     <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="333"/>
+      <c r="B23" s="334"/>
       <c r="C23" s="52"/>
       <c r="D23" s="53"/>
       <c r="E23" s="54"/>
@@ -5507,12 +5510,12 @@
     </row>
     <row r="24" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="333"/>
-      <c r="C24" s="393" t="s">
+      <c r="B24" s="334"/>
+      <c r="C24" s="394" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="394"/>
-      <c r="E24" s="395"/>
+      <c r="D24" s="395"/>
+      <c r="E24" s="396"/>
       <c r="F24" s="89" t="s">
         <v>1</v>
       </c>
@@ -5523,17 +5526,17 @@
         <v>3</v>
       </c>
       <c r="I24" s="7"/>
-      <c r="J24" s="384" t="s">
+      <c r="J24" s="385" t="s">
         <v>143</v>
       </c>
-      <c r="K24" s="385"/>
-      <c r="L24" s="385"/>
-      <c r="M24" s="386"/>
+      <c r="K24" s="386"/>
+      <c r="L24" s="386"/>
+      <c r="M24" s="387"/>
       <c r="N24" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="O24" s="377"/>
-      <c r="P24" s="378"/>
+      <c r="O24" s="378"/>
+      <c r="P24" s="379"/>
       <c r="Q24" s="58"/>
       <c r="R24" s="66"/>
       <c r="S24" s="66"/>
@@ -5541,11 +5544,11 @@
     <row r="25" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="359" t="s">
+      <c r="C25" s="360" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="360"/>
-      <c r="E25" s="361"/>
+      <c r="D25" s="361"/>
+      <c r="E25" s="362"/>
       <c r="F25" s="71">
         <f>F13-F26-F28-F29</f>
         <v>21446</v>
@@ -5555,12 +5558,12 @@
         <v>6006</v>
       </c>
       <c r="I25" s="7"/>
-      <c r="J25" s="379" t="s">
+      <c r="J25" s="380" t="s">
         <v>2</v>
       </c>
-      <c r="K25" s="380"/>
-      <c r="L25" s="380"/>
-      <c r="M25" s="327"/>
+      <c r="K25" s="381"/>
+      <c r="L25" s="381"/>
+      <c r="M25" s="328"/>
       <c r="N25" s="145"/>
       <c r="O25" s="58"/>
       <c r="P25" s="58"/>
@@ -5571,11 +5574,11 @@
     <row r="26" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="20"/>
-      <c r="C26" s="359" t="s">
+      <c r="C26" s="360" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="360"/>
-      <c r="E26" s="361"/>
+      <c r="D26" s="361"/>
+      <c r="E26" s="362"/>
       <c r="F26" s="71">
         <v>11230</v>
       </c>
@@ -5585,12 +5588,12 @@
         <v>8722</v>
       </c>
       <c r="I26" s="7"/>
-      <c r="J26" s="344" t="s">
+      <c r="J26" s="345" t="s">
         <v>223</v>
       </c>
-      <c r="K26" s="345"/>
-      <c r="L26" s="345"/>
-      <c r="M26" s="346"/>
+      <c r="K26" s="346"/>
+      <c r="L26" s="346"/>
+      <c r="M26" s="347"/>
       <c r="N26" s="150">
         <v>2546</v>
       </c>
@@ -5609,12 +5612,12 @@
       <c r="G27" s="181"/>
       <c r="H27" s="121"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="344" t="s">
+      <c r="J27" s="345" t="s">
         <v>224</v>
       </c>
-      <c r="K27" s="345"/>
-      <c r="L27" s="345"/>
-      <c r="M27" s="346"/>
+      <c r="K27" s="346"/>
+      <c r="L27" s="346"/>
+      <c r="M27" s="347"/>
       <c r="N27" s="150">
         <v>29272</v>
       </c>
@@ -5626,11 +5629,11 @@
     <row r="28" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="20"/>
-      <c r="C28" s="359" t="s">
+      <c r="C28" s="360" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="360"/>
-      <c r="E28" s="361"/>
+      <c r="D28" s="361"/>
+      <c r="E28" s="362"/>
       <c r="F28" s="71">
         <v>4475</v>
       </c>
@@ -5640,12 +5643,12 @@
         <v>10627</v>
       </c>
       <c r="I28" s="7"/>
-      <c r="J28" s="344" t="s">
+      <c r="J28" s="345" t="s">
         <v>225</v>
       </c>
-      <c r="K28" s="345"/>
-      <c r="L28" s="345"/>
-      <c r="M28" s="346"/>
+      <c r="K28" s="346"/>
+      <c r="L28" s="346"/>
+      <c r="M28" s="347"/>
       <c r="N28" s="150">
         <v>46324</v>
       </c>
@@ -5657,11 +5660,11 @@
     <row r="29" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="359" t="s">
+      <c r="C29" s="360" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="360"/>
-      <c r="E29" s="361"/>
+      <c r="D29" s="361"/>
+      <c r="E29" s="362"/>
       <c r="F29" s="71">
         <v>0</v>
       </c>
@@ -5670,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="7"/>
-      <c r="J29" s="344"/>
-      <c r="K29" s="345"/>
-      <c r="L29" s="345"/>
-      <c r="M29" s="346"/>
+      <c r="J29" s="345"/>
+      <c r="K29" s="346"/>
+      <c r="L29" s="346"/>
+      <c r="M29" s="347"/>
       <c r="N29" s="150"/>
       <c r="P29" s="58"/>
       <c r="Q29" s="58"/>
@@ -5683,23 +5686,23 @@
     <row r="30" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="20"/>
-      <c r="C30" s="359" t="s">
+      <c r="C30" s="360" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="360"/>
-      <c r="E30" s="361"/>
+      <c r="D30" s="361"/>
+      <c r="E30" s="362"/>
       <c r="F30" s="71"/>
       <c r="G30" s="102"/>
       <c r="H30" s="123">
         <v>0</v>
       </c>
       <c r="I30" s="7"/>
-      <c r="J30" s="390" t="s">
+      <c r="J30" s="391" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="391"/>
-      <c r="L30" s="391"/>
-      <c r="M30" s="392"/>
+      <c r="K30" s="392"/>
+      <c r="L30" s="392"/>
+      <c r="M30" s="393"/>
       <c r="N30" s="151"/>
       <c r="P30" s="58"/>
       <c r="Q30" s="58"/>
@@ -5709,23 +5712,23 @@
     <row r="31" spans="1:23" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="359" t="s">
+      <c r="C31" s="360" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="360"/>
-      <c r="E31" s="361"/>
+      <c r="D31" s="361"/>
+      <c r="E31" s="362"/>
       <c r="F31" s="71"/>
       <c r="G31" s="99"/>
       <c r="H31" s="121">
         <v>0</v>
       </c>
       <c r="I31" s="7"/>
-      <c r="J31" s="381" t="s">
+      <c r="J31" s="382" t="s">
         <v>226</v>
       </c>
-      <c r="K31" s="382"/>
-      <c r="L31" s="382"/>
-      <c r="M31" s="383"/>
+      <c r="K31" s="383"/>
+      <c r="L31" s="383"/>
+      <c r="M31" s="384"/>
       <c r="N31" s="150">
         <f>46433+500</f>
         <v>46933</v>
@@ -5738,11 +5741,11 @@
     <row r="32" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="20"/>
-      <c r="C32" s="371" t="s">
+      <c r="C32" s="372" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="372"/>
-      <c r="E32" s="373"/>
+      <c r="D32" s="373"/>
+      <c r="E32" s="374"/>
       <c r="F32" s="71">
         <f>SUM(F25:F31)</f>
         <v>37151</v>
@@ -5756,12 +5759,12 @@
         <v>25355</v>
       </c>
       <c r="I32" s="7"/>
-      <c r="J32" s="381" t="s">
+      <c r="J32" s="382" t="s">
         <v>227</v>
       </c>
-      <c r="K32" s="382"/>
-      <c r="L32" s="382"/>
-      <c r="M32" s="383"/>
+      <c r="K32" s="383"/>
+      <c r="L32" s="383"/>
+      <c r="M32" s="384"/>
       <c r="N32" s="150">
         <v>1514</v>
       </c>
@@ -5774,10 +5777,10 @@
       <c r="A33" s="3"/>
       <c r="B33" s="20"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="381"/>
-      <c r="K33" s="382"/>
-      <c r="L33" s="382"/>
-      <c r="M33" s="383"/>
+      <c r="J33" s="382"/>
+      <c r="K33" s="383"/>
+      <c r="L33" s="383"/>
+      <c r="M33" s="384"/>
       <c r="N33" s="152"/>
       <c r="O33" s="61"/>
       <c r="P33" s="61"/>
@@ -5788,11 +5791,11 @@
     <row r="34" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="20"/>
-      <c r="C34" s="396" t="s">
+      <c r="C34" s="397" t="s">
         <v>103</v>
       </c>
-      <c r="D34" s="397"/>
-      <c r="E34" s="398"/>
+      <c r="D34" s="398"/>
+      <c r="E34" s="399"/>
       <c r="F34" s="77" t="str">
         <f>K1</f>
         <v>20.09.2026</v>
@@ -5804,12 +5807,12 @@
         <v>250</v>
       </c>
       <c r="I34" s="7"/>
-      <c r="J34" s="399" t="s">
+      <c r="J34" s="400" t="s">
         <v>140</v>
       </c>
-      <c r="K34" s="400"/>
-      <c r="L34" s="400"/>
-      <c r="M34" s="401"/>
+      <c r="K34" s="401"/>
+      <c r="L34" s="401"/>
+      <c r="M34" s="402"/>
       <c r="N34" s="163">
         <f>SUM(N26:N33)</f>
         <v>126589</v>
@@ -5868,11 +5871,11 @@
         <v>0</v>
       </c>
       <c r="I36" s="7"/>
-      <c r="J36" s="337" t="s">
+      <c r="J36" s="338" t="s">
         <v>156</v>
       </c>
-      <c r="K36" s="338"/>
-      <c r="L36" s="339"/>
+      <c r="K36" s="339"/>
+      <c r="L36" s="340"/>
       <c r="M36" s="112" t="s">
         <v>115</v>
       </c>
@@ -5885,10 +5888,10 @@
       <c r="P36" s="165" t="s">
         <v>138</v>
       </c>
-      <c r="Q36" s="446" t="s">
+      <c r="Q36" s="447" t="s">
         <v>149</v>
       </c>
-      <c r="R36" s="447"/>
+      <c r="R36" s="448"/>
       <c r="S36" s="61"/>
     </row>
     <row r="37" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5907,11 +5910,11 @@
       <c r="G37" s="134"/>
       <c r="H37" s="134"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="340" t="s">
+      <c r="J37" s="341" t="s">
         <v>229</v>
       </c>
-      <c r="K37" s="341"/>
-      <c r="L37" s="342"/>
+      <c r="K37" s="342"/>
+      <c r="L37" s="343"/>
       <c r="M37" s="149">
         <v>75204</v>
       </c>
@@ -5924,10 +5927,10 @@
       <c r="P37" s="256" t="s">
         <v>240</v>
       </c>
-      <c r="Q37" s="455" t="s">
+      <c r="Q37" s="456" t="s">
         <v>241</v>
       </c>
-      <c r="R37" s="455"/>
+      <c r="R37" s="456"/>
       <c r="S37" s="61"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5949,11 +5952,11 @@
       </c>
       <c r="H38" s="134"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="340" t="s">
+      <c r="J38" s="341" t="s">
         <v>213</v>
       </c>
-      <c r="K38" s="341"/>
-      <c r="L38" s="342"/>
+      <c r="K38" s="342"/>
+      <c r="L38" s="343"/>
       <c r="M38" s="149">
         <v>79700</v>
       </c>
@@ -5966,10 +5969,10 @@
       <c r="P38" s="256" t="s">
         <v>263</v>
       </c>
-      <c r="Q38" s="455" t="s">
+      <c r="Q38" s="456" t="s">
         <v>247</v>
       </c>
-      <c r="R38" s="455"/>
+      <c r="R38" s="456"/>
       <c r="S38" s="61"/>
     </row>
     <row r="39" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5991,11 +5994,11 @@
       </c>
       <c r="H39" s="134"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="340" t="s">
+      <c r="J39" s="341" t="s">
         <v>245</v>
       </c>
-      <c r="K39" s="341"/>
-      <c r="L39" s="342"/>
+      <c r="K39" s="342"/>
+      <c r="L39" s="343"/>
       <c r="M39" s="149">
         <v>75203</v>
       </c>
@@ -6006,10 +6009,10 @@
       <c r="P39" s="256" t="s">
         <v>216</v>
       </c>
-      <c r="Q39" s="455" t="s">
+      <c r="Q39" s="456" t="s">
         <v>246</v>
       </c>
-      <c r="R39" s="455"/>
+      <c r="R39" s="456"/>
       <c r="S39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6022,15 +6025,15 @@
       <c r="G40" s="134"/>
       <c r="H40" s="134"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="340"/>
-      <c r="K40" s="341"/>
-      <c r="L40" s="342"/>
+      <c r="J40" s="341"/>
+      <c r="K40" s="342"/>
+      <c r="L40" s="343"/>
       <c r="M40" s="149"/>
       <c r="N40" s="149"/>
       <c r="O40" s="265"/>
       <c r="P40" s="256"/>
-      <c r="Q40" s="450"/>
-      <c r="R40" s="451"/>
+      <c r="Q40" s="451"/>
+      <c r="R40" s="452"/>
       <c r="S40" s="61"/>
     </row>
     <row r="41" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6043,11 +6046,11 @@
       <c r="G41" s="134"/>
       <c r="H41" s="134"/>
       <c r="I41" s="7"/>
-      <c r="J41" s="454" t="s">
+      <c r="J41" s="455" t="s">
         <v>208</v>
       </c>
-      <c r="K41" s="454"/>
-      <c r="L41" s="454"/>
+      <c r="K41" s="455"/>
+      <c r="L41" s="455"/>
       <c r="M41" s="149">
         <v>59695</v>
       </c>
@@ -6060,10 +6063,10 @@
       <c r="P41" s="256" t="s">
         <v>306</v>
       </c>
-      <c r="Q41" s="455" t="s">
+      <c r="Q41" s="456" t="s">
         <v>215</v>
       </c>
-      <c r="R41" s="455"/>
+      <c r="R41" s="456"/>
       <c r="S41" s="61"/>
     </row>
     <row r="42" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6076,11 +6079,11 @@
       <c r="G42" s="134"/>
       <c r="H42" s="134"/>
       <c r="I42" s="7"/>
-      <c r="J42" s="454" t="s">
+      <c r="J42" s="455" t="s">
         <v>237</v>
       </c>
-      <c r="K42" s="454"/>
-      <c r="L42" s="454"/>
+      <c r="K42" s="455"/>
+      <c r="L42" s="455"/>
       <c r="M42" s="149">
         <v>53000</v>
       </c>
@@ -6091,10 +6094,10 @@
       <c r="P42" s="256" t="s">
         <v>216</v>
       </c>
-      <c r="Q42" s="455" t="s">
+      <c r="Q42" s="456" t="s">
         <v>239</v>
       </c>
-      <c r="R42" s="455"/>
+      <c r="R42" s="456"/>
       <c r="S42" s="61"/>
     </row>
     <row r="43" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6107,31 +6110,31 @@
         <v>0</v>
       </c>
       <c r="E43" s="129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" s="129">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="134"/>
       <c r="H43" s="134">
         <v>0</v>
       </c>
       <c r="I43" s="7"/>
-      <c r="J43" s="456" t="s">
+      <c r="J43" s="457" t="s">
         <v>98</v>
       </c>
-      <c r="K43" s="457"/>
-      <c r="L43" s="457"/>
-      <c r="M43" s="457"/>
+      <c r="K43" s="458"/>
+      <c r="L43" s="458"/>
+      <c r="M43" s="458"/>
       <c r="N43" s="166"/>
       <c r="O43" s="167">
         <f>SUM(N37:N42)</f>
         <v>38048</v>
       </c>
       <c r="P43" s="254"/>
-      <c r="Q43" s="448"/>
-      <c r="R43" s="448"/>
+      <c r="Q43" s="449"/>
+      <c r="R43" s="449"/>
       <c r="S43" s="61"/>
     </row>
     <row r="44" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6145,25 +6148,25 @@
       </c>
       <c r="E44" s="129"/>
       <c r="F44" s="129"/>
-      <c r="G44" s="135">
+      <c r="G44" s="325">
         <v>1</v>
       </c>
       <c r="H44" s="136"/>
       <c r="I44" s="7"/>
-      <c r="J44" s="387" t="s">
+      <c r="J44" s="388" t="s">
         <v>99</v>
       </c>
-      <c r="K44" s="388"/>
-      <c r="L44" s="388"/>
-      <c r="M44" s="388"/>
-      <c r="N44" s="389"/>
+      <c r="K44" s="389"/>
+      <c r="L44" s="389"/>
+      <c r="M44" s="389"/>
+      <c r="N44" s="390"/>
       <c r="O44" s="148">
         <f>N22+N34+O43</f>
         <v>428749</v>
       </c>
       <c r="P44" s="255"/>
-      <c r="Q44" s="449"/>
-      <c r="R44" s="449"/>
+      <c r="Q44" s="450"/>
+      <c r="R44" s="450"/>
       <c r="S44" s="61"/>
     </row>
     <row r="45" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6208,15 +6211,15 @@
       </c>
       <c r="F46" s="129"/>
       <c r="G46" s="135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="134">
         <v>5</v>
       </c>
-      <c r="J46" s="458" t="s">
+      <c r="J46" s="459" t="s">
         <v>102</v>
       </c>
-      <c r="K46" s="459"/>
+      <c r="K46" s="460"/>
       <c r="L46" s="116" t="s">
         <v>1</v>
       </c>
@@ -6245,21 +6248,19 @@
       <c r="C47" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="130">
+      <c r="D47" s="130"/>
+      <c r="E47" s="130">
         <v>2</v>
-      </c>
-      <c r="E47" s="130">
-        <v>0</v>
       </c>
       <c r="F47" s="130"/>
       <c r="G47" s="137"/>
       <c r="H47" s="134">
         <v>2</v>
       </c>
-      <c r="J47" s="354" t="s">
+      <c r="J47" s="355" t="s">
         <v>15</v>
       </c>
-      <c r="K47" s="355"/>
+      <c r="K47" s="356"/>
       <c r="L47" s="156">
         <v>48.71</v>
       </c>
@@ -6293,28 +6294,28 @@
       </c>
       <c r="D48" s="131">
         <f>SUM(D36:D47)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" s="131">
         <f>SUM(E36:E47)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F48" s="131">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G48" s="138">
         <f>SUM(G36:G47)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H48" s="139">
         <f>SUM(H36:H47)</f>
         <v>7</v>
       </c>
-      <c r="J48" s="354" t="s">
+      <c r="J48" s="355" t="s">
         <v>16</v>
       </c>
-      <c r="K48" s="355"/>
+      <c r="K48" s="356"/>
       <c r="L48" s="156">
         <v>45.113999999999997</v>
       </c>
@@ -6350,10 +6351,10 @@
       <c r="F49" s="80"/>
       <c r="G49" s="84"/>
       <c r="H49" s="85"/>
-      <c r="J49" s="354" t="s">
+      <c r="J49" s="355" t="s">
         <v>17</v>
       </c>
-      <c r="K49" s="355"/>
+      <c r="K49" s="356"/>
       <c r="L49" s="156">
         <f>(L47-L48)/L47*100</f>
         <v>7.3824676657770549</v>
@@ -6400,10 +6401,10 @@
         <v>3</v>
       </c>
       <c r="I50" s="64"/>
-      <c r="J50" s="368" t="s">
+      <c r="J50" s="369" t="s">
         <v>18</v>
       </c>
-      <c r="K50" s="369"/>
+      <c r="K50" s="370"/>
       <c r="L50" s="156">
         <f>F13/L47/1000</f>
         <v>0.76269759802915216</v>
@@ -6451,17 +6452,17 @@
       </c>
       <c r="J51" s="140"/>
       <c r="K51" s="141"/>
-      <c r="L51" s="354" t="s">
+      <c r="L51" s="355" t="s">
         <v>145</v>
       </c>
-      <c r="M51" s="355"/>
-      <c r="N51" s="356"/>
+      <c r="M51" s="356"/>
+      <c r="N51" s="357"/>
       <c r="O51" s="158">
         <v>240.27</v>
       </c>
       <c r="P51" s="142"/>
-      <c r="Q51" s="452"/>
-      <c r="R51" s="453"/>
+      <c r="Q51" s="453"/>
+      <c r="R51" s="454"/>
       <c r="S51" s="109"/>
     </row>
     <row r="52" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6481,24 +6482,24 @@
     </row>
     <row r="53" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="B53" s="351" t="s">
+      <c r="B53" s="352" t="s">
         <v>134</v>
       </c>
-      <c r="C53" s="352"/>
-      <c r="D53" s="352"/>
-      <c r="E53" s="352"/>
-      <c r="F53" s="352"/>
-      <c r="G53" s="353"/>
+      <c r="C53" s="353"/>
+      <c r="D53" s="353"/>
+      <c r="E53" s="353"/>
+      <c r="F53" s="353"/>
+      <c r="G53" s="354"/>
       <c r="H53" s="68"/>
-      <c r="J53" s="351" t="s">
+      <c r="J53" s="352" t="s">
         <v>135</v>
       </c>
-      <c r="K53" s="352"/>
-      <c r="L53" s="352"/>
-      <c r="M53" s="352"/>
-      <c r="N53" s="352"/>
-      <c r="O53" s="352"/>
-      <c r="P53" s="353"/>
+      <c r="K53" s="353"/>
+      <c r="L53" s="353"/>
+      <c r="M53" s="353"/>
+      <c r="N53" s="353"/>
+      <c r="O53" s="353"/>
+      <c r="P53" s="354"/>
       <c r="Q53" s="60"/>
       <c r="R53" s="60"/>
       <c r="S53" s="60"/>
@@ -6508,33 +6509,33 @@
       <c r="B54" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="347" t="s">
+      <c r="C54" s="348" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="348"/>
+      <c r="D54" s="349"/>
       <c r="E54" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F54" s="326" t="s">
+      <c r="F54" s="327" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="328"/>
+      <c r="G54" s="329"/>
       <c r="H54" s="60"/>
       <c r="J54" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="K54" s="370" t="s">
+      <c r="K54" s="371" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="370"/>
-      <c r="M54" s="370"/>
+      <c r="L54" s="371"/>
+      <c r="M54" s="371"/>
       <c r="N54" s="159" t="s">
         <v>142</v>
       </c>
-      <c r="O54" s="349" t="s">
+      <c r="O54" s="350" t="s">
         <v>22</v>
       </c>
-      <c r="P54" s="350"/>
+      <c r="P54" s="351"/>
       <c r="Q54" s="60"/>
       <c r="R54" s="60"/>
       <c r="S54" s="60"/>
@@ -6544,33 +6545,33 @@
       <c r="B55" s="182">
         <v>1</v>
       </c>
-      <c r="C55" s="326" t="s">
+      <c r="C55" s="327" t="s">
         <v>255</v>
       </c>
-      <c r="D55" s="327"/>
+      <c r="D55" s="328"/>
       <c r="E55" s="258" t="s">
         <v>254</v>
       </c>
-      <c r="F55" s="326" t="s">
+      <c r="F55" s="327" t="s">
         <v>248</v>
       </c>
-      <c r="G55" s="328"/>
+      <c r="G55" s="329"/>
       <c r="H55" s="44"/>
       <c r="J55" s="257">
         <v>1</v>
       </c>
-      <c r="K55" s="329" t="s">
+      <c r="K55" s="330" t="s">
         <v>194</v>
       </c>
-      <c r="L55" s="329"/>
-      <c r="M55" s="329"/>
+      <c r="L55" s="330"/>
+      <c r="M55" s="330"/>
       <c r="N55" s="258" t="s">
         <v>256</v>
       </c>
-      <c r="O55" s="329" t="s">
+      <c r="O55" s="330" t="s">
         <v>304</v>
       </c>
-      <c r="P55" s="329"/>
+      <c r="P55" s="330"/>
       <c r="Q55" s="60"/>
       <c r="R55" s="60"/>
       <c r="S55" s="60"/>
@@ -6580,33 +6581,33 @@
       <c r="B56" s="305">
         <v>2</v>
       </c>
-      <c r="C56" s="326" t="s">
+      <c r="C56" s="327" t="s">
         <v>252</v>
       </c>
-      <c r="D56" s="327"/>
+      <c r="D56" s="328"/>
       <c r="E56" s="169" t="s">
         <v>253</v>
       </c>
-      <c r="F56" s="326" t="s">
+      <c r="F56" s="327" t="s">
         <v>248</v>
       </c>
-      <c r="G56" s="328"/>
+      <c r="G56" s="329"/>
       <c r="H56" s="44"/>
       <c r="J56" s="306">
         <v>2</v>
       </c>
-      <c r="K56" s="329" t="s">
+      <c r="K56" s="330" t="s">
         <v>194</v>
       </c>
-      <c r="L56" s="329"/>
-      <c r="M56" s="329"/>
+      <c r="L56" s="330"/>
+      <c r="M56" s="330"/>
       <c r="N56" s="258" t="s">
         <v>257</v>
       </c>
-      <c r="O56" s="329" t="s">
+      <c r="O56" s="330" t="s">
         <v>305</v>
       </c>
-      <c r="P56" s="329"/>
+      <c r="P56" s="330"/>
       <c r="Q56" s="60"/>
       <c r="R56" s="60"/>
       <c r="S56" s="60"/>
@@ -6616,33 +6617,33 @@
       <c r="B57" s="316">
         <v>3</v>
       </c>
-      <c r="C57" s="326" t="s">
+      <c r="C57" s="327" t="s">
         <v>259</v>
       </c>
-      <c r="D57" s="327"/>
+      <c r="D57" s="328"/>
       <c r="E57" s="169" t="s">
         <v>260</v>
       </c>
-      <c r="F57" s="326" t="s">
+      <c r="F57" s="327" t="s">
         <v>307</v>
       </c>
-      <c r="G57" s="328"/>
+      <c r="G57" s="329"/>
       <c r="H57" s="44"/>
       <c r="J57" s="315">
         <v>3</v>
       </c>
-      <c r="K57" s="329" t="s">
+      <c r="K57" s="330" t="s">
         <v>261</v>
       </c>
-      <c r="L57" s="329"/>
-      <c r="M57" s="329"/>
+      <c r="L57" s="330"/>
+      <c r="M57" s="330"/>
       <c r="N57" s="258" t="s">
         <v>262</v>
       </c>
-      <c r="O57" s="329" t="s">
+      <c r="O57" s="330" t="s">
         <v>233</v>
       </c>
-      <c r="P57" s="329"/>
+      <c r="P57" s="330"/>
       <c r="Q57" s="60"/>
       <c r="R57" s="60"/>
       <c r="S57" s="60"/>
@@ -6652,17 +6653,17 @@
       <c r="B58" s="324">
         <v>4</v>
       </c>
-      <c r="C58" s="326" t="s">
+      <c r="C58" s="327" t="s">
         <v>302</v>
       </c>
-      <c r="D58" s="327"/>
+      <c r="D58" s="328"/>
       <c r="E58" s="169" t="s">
         <v>303</v>
       </c>
-      <c r="F58" s="326" t="s">
+      <c r="F58" s="327" t="s">
         <v>233</v>
       </c>
-      <c r="G58" s="328"/>
+      <c r="G58" s="329"/>
       <c r="H58" s="44"/>
       <c r="J58" s="275"/>
       <c r="K58" s="275"/>
@@ -6697,23 +6698,23 @@
     </row>
     <row r="60" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
-      <c r="B60" s="343" t="s">
+      <c r="B60" s="344" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="343"/>
-      <c r="D60" s="343"/>
-      <c r="E60" s="343"/>
-      <c r="F60" s="343"/>
-      <c r="G60" s="343"/>
-      <c r="H60" s="343"/>
-      <c r="I60" s="343"/>
-      <c r="J60" s="343"/>
-      <c r="K60" s="343"/>
-      <c r="L60" s="343"/>
-      <c r="M60" s="343"/>
-      <c r="N60" s="343"/>
-      <c r="O60" s="343"/>
-      <c r="P60" s="343"/>
+      <c r="C60" s="344"/>
+      <c r="D60" s="344"/>
+      <c r="E60" s="344"/>
+      <c r="F60" s="344"/>
+      <c r="G60" s="344"/>
+      <c r="H60" s="344"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
     </row>
     <row r="61" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
@@ -6735,46 +6736,46 @@
     </row>
     <row r="62" spans="1:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="3"/>
-      <c r="C62" s="325" t="s">
+      <c r="C62" s="326" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="325"/>
-      <c r="E62" s="325"/>
-      <c r="F62" s="325"/>
+      <c r="D62" s="326"/>
+      <c r="E62" s="326"/>
+      <c r="F62" s="326"/>
       <c r="G62" s="40"/>
       <c r="H62" s="40"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="325" t="s">
+      <c r="J62" s="326" t="s">
         <v>89</v>
       </c>
-      <c r="K62" s="325"/>
-      <c r="L62" s="325"/>
-      <c r="M62" s="325"/>
-      <c r="N62" s="325"/>
+      <c r="K62" s="326"/>
+      <c r="L62" s="326"/>
+      <c r="M62" s="326"/>
+      <c r="N62" s="326"/>
       <c r="O62" s="42"/>
     </row>
     <row r="63" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B63" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="336" t="s">
+      <c r="C63" s="337" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="D63" s="337"/>
+      <c r="E63" s="337"/>
+      <c r="F63" s="337"/>
       <c r="G63" s="40"/>
       <c r="H63" s="40"/>
       <c r="I63" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="J63" s="336" t="s">
+      <c r="J63" s="337" t="s">
         <v>78</v>
       </c>
-      <c r="K63" s="336"/>
-      <c r="L63" s="336"/>
-      <c r="M63" s="336"/>
-      <c r="N63" s="336"/>
+      <c r="K63" s="337"/>
+      <c r="L63" s="337"/>
+      <c r="M63" s="337"/>
+      <c r="N63" s="337"/>
       <c r="O63" s="42"/>
     </row>
     <row r="64" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
@@ -7234,11 +7235,11 @@
       <c r="G83" s="290"/>
       <c r="H83" s="279"/>
       <c r="I83" s="271"/>
-      <c r="J83" s="414"/>
-      <c r="K83" s="414"/>
-      <c r="L83" s="414"/>
-      <c r="M83" s="414"/>
-      <c r="N83" s="414"/>
+      <c r="J83" s="415"/>
+      <c r="K83" s="415"/>
+      <c r="L83" s="415"/>
+      <c r="M83" s="415"/>
+      <c r="N83" s="415"/>
       <c r="O83" s="281"/>
     </row>
     <row r="84" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7254,11 +7255,11 @@
       <c r="G84" s="290"/>
       <c r="H84" s="279"/>
       <c r="I84" s="271"/>
-      <c r="J84" s="414"/>
-      <c r="K84" s="414"/>
-      <c r="L84" s="414"/>
-      <c r="M84" s="414"/>
-      <c r="N84" s="414"/>
+      <c r="J84" s="415"/>
+      <c r="K84" s="415"/>
+      <c r="L84" s="415"/>
+      <c r="M84" s="415"/>
+      <c r="N84" s="415"/>
       <c r="O84" s="287"/>
     </row>
     <row r="85" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7318,14 +7319,14 @@
       <c r="I87" s="271">
         <v>1</v>
       </c>
-      <c r="J87" s="331" t="s">
+      <c r="J87" s="332" t="s">
         <v>264</v>
       </c>
-      <c r="K87" s="331"/>
-      <c r="L87" s="331"/>
-      <c r="M87" s="331"/>
-      <c r="N87" s="331"/>
-      <c r="O87" s="331"/>
+      <c r="K87" s="332"/>
+      <c r="L87" s="332"/>
+      <c r="M87" s="332"/>
+      <c r="N87" s="332"/>
+      <c r="O87" s="332"/>
     </row>
     <row r="88" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="111">
@@ -7342,14 +7343,14 @@
       <c r="I88" s="271">
         <v>2</v>
       </c>
-      <c r="J88" s="331" t="s">
+      <c r="J88" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="K88" s="331"/>
-      <c r="L88" s="331"/>
-      <c r="M88" s="331"/>
-      <c r="N88" s="331"/>
-      <c r="O88" s="331"/>
+      <c r="K88" s="332"/>
+      <c r="L88" s="332"/>
+      <c r="M88" s="332"/>
+      <c r="N88" s="332"/>
+      <c r="O88" s="332"/>
     </row>
     <row r="89" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="111">
@@ -7366,14 +7367,14 @@
       <c r="I89" s="271">
         <v>3</v>
       </c>
-      <c r="J89" s="331" t="s">
+      <c r="J89" s="332" t="s">
         <v>268</v>
       </c>
-      <c r="K89" s="331"/>
-      <c r="L89" s="331"/>
-      <c r="M89" s="331"/>
-      <c r="N89" s="331"/>
-      <c r="O89" s="331"/>
+      <c r="K89" s="332"/>
+      <c r="L89" s="332"/>
+      <c r="M89" s="332"/>
+      <c r="N89" s="332"/>
+      <c r="O89" s="332"/>
     </row>
     <row r="90" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="111"/>
@@ -7385,14 +7386,14 @@
       <c r="I90" s="271">
         <v>4</v>
       </c>
-      <c r="J90" s="331" t="s">
+      <c r="J90" s="332" t="s">
         <v>268</v>
       </c>
-      <c r="K90" s="331"/>
-      <c r="L90" s="331"/>
-      <c r="M90" s="331"/>
-      <c r="N90" s="331"/>
-      <c r="O90" s="331"/>
+      <c r="K90" s="332"/>
+      <c r="L90" s="332"/>
+      <c r="M90" s="332"/>
+      <c r="N90" s="332"/>
+      <c r="O90" s="332"/>
     </row>
     <row r="91" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="111"/>
@@ -7401,14 +7402,14 @@
       <c r="I91" s="271">
         <v>5</v>
       </c>
-      <c r="J91" s="331" t="s">
+      <c r="J91" s="332" t="s">
         <v>266</v>
       </c>
-      <c r="K91" s="331"/>
-      <c r="L91" s="331"/>
-      <c r="M91" s="331"/>
-      <c r="N91" s="331"/>
-      <c r="O91" s="331"/>
+      <c r="K91" s="332"/>
+      <c r="L91" s="332"/>
+      <c r="M91" s="332"/>
+      <c r="N91" s="332"/>
+      <c r="O91" s="332"/>
     </row>
     <row r="92" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="111"/>
@@ -7420,14 +7421,14 @@
       <c r="I92" s="271">
         <v>6</v>
       </c>
-      <c r="J92" s="331" t="s">
+      <c r="J92" s="332" t="s">
         <v>267</v>
       </c>
-      <c r="K92" s="331"/>
-      <c r="L92" s="331"/>
-      <c r="M92" s="331"/>
-      <c r="N92" s="331"/>
-      <c r="O92" s="331"/>
+      <c r="K92" s="332"/>
+      <c r="L92" s="332"/>
+      <c r="M92" s="332"/>
+      <c r="N92" s="332"/>
+      <c r="O92" s="332"/>
       <c r="P92" s="266"/>
     </row>
     <row r="93" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7439,12 +7440,12 @@
       <c r="G93" s="289"/>
       <c r="H93" s="279"/>
       <c r="I93" s="271"/>
-      <c r="J93" s="331"/>
-      <c r="K93" s="331"/>
-      <c r="L93" s="331"/>
-      <c r="M93" s="331"/>
-      <c r="N93" s="331"/>
-      <c r="O93" s="331"/>
+      <c r="J93" s="332"/>
+      <c r="K93" s="332"/>
+      <c r="L93" s="332"/>
+      <c r="M93" s="332"/>
+      <c r="N93" s="332"/>
+      <c r="O93" s="332"/>
     </row>
     <row r="94" spans="2:16" ht="24" x14ac:dyDescent="0.15">
       <c r="B94" s="111"/>
@@ -7455,12 +7456,12 @@
       <c r="G94" s="289"/>
       <c r="H94" s="279"/>
       <c r="I94" s="271"/>
-      <c r="J94" s="331"/>
-      <c r="K94" s="331"/>
-      <c r="L94" s="331"/>
-      <c r="M94" s="331"/>
-      <c r="N94" s="331"/>
-      <c r="O94" s="331"/>
+      <c r="J94" s="332"/>
+      <c r="K94" s="332"/>
+      <c r="L94" s="332"/>
+      <c r="M94" s="332"/>
+      <c r="N94" s="332"/>
+      <c r="O94" s="332"/>
     </row>
     <row r="95" spans="2:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B95" s="111"/>
@@ -7471,12 +7472,12 @@
       <c r="G95" s="290"/>
       <c r="H95" s="279"/>
       <c r="I95" s="271"/>
-      <c r="J95" s="331"/>
-      <c r="K95" s="331"/>
-      <c r="L95" s="331"/>
-      <c r="M95" s="331"/>
-      <c r="N95" s="331"/>
-      <c r="O95" s="331"/>
+      <c r="J95" s="332"/>
+      <c r="K95" s="332"/>
+      <c r="L95" s="332"/>
+      <c r="M95" s="332"/>
+      <c r="N95" s="332"/>
+      <c r="O95" s="332"/>
     </row>
     <row r="96" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="111"/>
@@ -7486,11 +7487,11 @@
       <c r="G96" s="290"/>
       <c r="H96" s="279"/>
       <c r="I96" s="266"/>
-      <c r="J96" s="330"/>
-      <c r="K96" s="330"/>
-      <c r="L96" s="330"/>
-      <c r="M96" s="330"/>
-      <c r="N96" s="330"/>
+      <c r="J96" s="331"/>
+      <c r="K96" s="331"/>
+      <c r="L96" s="331"/>
+      <c r="M96" s="331"/>
+      <c r="N96" s="331"/>
       <c r="O96" s="39"/>
     </row>
     <row r="97" spans="2:15" ht="24" x14ac:dyDescent="0.2">
@@ -7500,11 +7501,11 @@
       <c r="F97" s="290"/>
       <c r="G97" s="290"/>
       <c r="H97" s="279"/>
-      <c r="J97" s="330"/>
-      <c r="K97" s="330"/>
-      <c r="L97" s="330"/>
-      <c r="M97" s="330"/>
-      <c r="N97" s="330"/>
+      <c r="J97" s="331"/>
+      <c r="K97" s="331"/>
+      <c r="L97" s="331"/>
+      <c r="M97" s="331"/>
+      <c r="N97" s="331"/>
       <c r="O97" s="39"/>
     </row>
     <row r="98" spans="2:15" ht="24" x14ac:dyDescent="0.2">
@@ -7514,11 +7515,11 @@
       <c r="F98" s="279"/>
       <c r="G98" s="279"/>
       <c r="H98" s="279"/>
-      <c r="J98" s="330"/>
-      <c r="K98" s="330"/>
-      <c r="L98" s="330"/>
-      <c r="M98" s="330"/>
-      <c r="N98" s="330"/>
+      <c r="J98" s="331"/>
+      <c r="K98" s="331"/>
+      <c r="L98" s="331"/>
+      <c r="M98" s="331"/>
+      <c r="N98" s="331"/>
       <c r="O98" s="39"/>
     </row>
     <row r="99" spans="2:15" ht="24" x14ac:dyDescent="0.15">
@@ -7529,11 +7530,11 @@
       <c r="F99" s="267"/>
       <c r="G99" s="267"/>
       <c r="H99" s="267"/>
-      <c r="J99" s="330"/>
-      <c r="K99" s="330"/>
-      <c r="L99" s="330"/>
-      <c r="M99" s="330"/>
-      <c r="N99" s="330"/>
+      <c r="J99" s="331"/>
+      <c r="K99" s="331"/>
+      <c r="L99" s="331"/>
+      <c r="M99" s="331"/>
+      <c r="N99" s="331"/>
       <c r="O99" s="39"/>
     </row>
     <row r="100" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7560,11 +7561,11 @@
       <c r="F101" s="251"/>
       <c r="G101" s="251"/>
       <c r="H101" s="251"/>
-      <c r="J101" s="330"/>
-      <c r="K101" s="330"/>
-      <c r="L101" s="330"/>
-      <c r="M101" s="330"/>
-      <c r="N101" s="330"/>
+      <c r="J101" s="331"/>
+      <c r="K101" s="331"/>
+      <c r="L101" s="331"/>
+      <c r="M101" s="331"/>
+      <c r="N101" s="331"/>
       <c r="O101" s="39"/>
     </row>
     <row r="102" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7575,11 +7576,11 @@
       <c r="F102" s="251"/>
       <c r="G102" s="251"/>
       <c r="H102" s="251"/>
-      <c r="J102" s="330"/>
-      <c r="K102" s="330"/>
-      <c r="L102" s="330"/>
-      <c r="M102" s="330"/>
-      <c r="N102" s="330"/>
+      <c r="J102" s="331"/>
+      <c r="K102" s="331"/>
+      <c r="L102" s="331"/>
+      <c r="M102" s="331"/>
+      <c r="N102" s="331"/>
       <c r="O102" s="39"/>
     </row>
     <row r="103" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7590,1251 +7591,1251 @@
       <c r="F103" s="251"/>
       <c r="G103" s="251"/>
       <c r="H103" s="251"/>
-      <c r="J103" s="330"/>
-      <c r="K103" s="330"/>
-      <c r="L103" s="330"/>
-      <c r="M103" s="330"/>
-      <c r="N103" s="330"/>
+      <c r="J103" s="331"/>
+      <c r="K103" s="331"/>
+      <c r="L103" s="331"/>
+      <c r="M103" s="331"/>
+      <c r="N103" s="331"/>
       <c r="O103" s="39"/>
     </row>
     <row r="104" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C104" s="332"/>
-      <c r="D104" s="332"/>
-      <c r="E104" s="332"/>
-      <c r="F104" s="332"/>
-      <c r="G104" s="332"/>
-      <c r="H104" s="332"/>
-      <c r="J104" s="330"/>
-      <c r="K104" s="330"/>
-      <c r="L104" s="330"/>
-      <c r="M104" s="330"/>
-      <c r="N104" s="330"/>
+      <c r="C104" s="333"/>
+      <c r="D104" s="333"/>
+      <c r="E104" s="333"/>
+      <c r="F104" s="333"/>
+      <c r="G104" s="333"/>
+      <c r="H104" s="333"/>
+      <c r="J104" s="331"/>
+      <c r="K104" s="331"/>
+      <c r="L104" s="331"/>
+      <c r="M104" s="331"/>
+      <c r="N104" s="331"/>
       <c r="O104" s="39"/>
     </row>
     <row r="105" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C105" s="332"/>
-      <c r="D105" s="332"/>
-      <c r="E105" s="332"/>
-      <c r="F105" s="332"/>
-      <c r="G105" s="332"/>
-      <c r="H105" s="332"/>
-      <c r="J105" s="330"/>
-      <c r="K105" s="330"/>
-      <c r="L105" s="330"/>
-      <c r="M105" s="330"/>
-      <c r="N105" s="330"/>
+      <c r="C105" s="333"/>
+      <c r="D105" s="333"/>
+      <c r="E105" s="333"/>
+      <c r="F105" s="333"/>
+      <c r="G105" s="333"/>
+      <c r="H105" s="333"/>
+      <c r="J105" s="331"/>
+      <c r="K105" s="331"/>
+      <c r="L105" s="331"/>
+      <c r="M105" s="331"/>
+      <c r="N105" s="331"/>
       <c r="O105" s="39"/>
     </row>
     <row r="106" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C106" s="332"/>
-      <c r="D106" s="332"/>
-      <c r="E106" s="332"/>
-      <c r="F106" s="332"/>
-      <c r="G106" s="332"/>
-      <c r="H106" s="332"/>
-      <c r="J106" s="330"/>
-      <c r="K106" s="330"/>
-      <c r="L106" s="330"/>
-      <c r="M106" s="330"/>
-      <c r="N106" s="330"/>
+      <c r="C106" s="333"/>
+      <c r="D106" s="333"/>
+      <c r="E106" s="333"/>
+      <c r="F106" s="333"/>
+      <c r="G106" s="333"/>
+      <c r="H106" s="333"/>
+      <c r="J106" s="331"/>
+      <c r="K106" s="331"/>
+      <c r="L106" s="331"/>
+      <c r="M106" s="331"/>
+      <c r="N106" s="331"/>
       <c r="O106" s="39"/>
     </row>
     <row r="107" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C107" s="332"/>
-      <c r="D107" s="332"/>
-      <c r="E107" s="332"/>
-      <c r="F107" s="332"/>
-      <c r="G107" s="332"/>
-      <c r="H107" s="332"/>
-      <c r="J107" s="330"/>
-      <c r="K107" s="330"/>
-      <c r="L107" s="330"/>
-      <c r="M107" s="330"/>
-      <c r="N107" s="330"/>
+      <c r="C107" s="333"/>
+      <c r="D107" s="333"/>
+      <c r="E107" s="333"/>
+      <c r="F107" s="333"/>
+      <c r="G107" s="333"/>
+      <c r="H107" s="333"/>
+      <c r="J107" s="331"/>
+      <c r="K107" s="331"/>
+      <c r="L107" s="331"/>
+      <c r="M107" s="331"/>
+      <c r="N107" s="331"/>
       <c r="O107" s="39"/>
     </row>
     <row r="108" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C108" s="332"/>
-      <c r="D108" s="332"/>
-      <c r="E108" s="332"/>
-      <c r="F108" s="332"/>
-      <c r="G108" s="332"/>
-      <c r="H108" s="332"/>
-      <c r="J108" s="330"/>
-      <c r="K108" s="330"/>
-      <c r="L108" s="330"/>
-      <c r="M108" s="330"/>
-      <c r="N108" s="330"/>
+      <c r="C108" s="333"/>
+      <c r="D108" s="333"/>
+      <c r="E108" s="333"/>
+      <c r="F108" s="333"/>
+      <c r="G108" s="333"/>
+      <c r="H108" s="333"/>
+      <c r="J108" s="331"/>
+      <c r="K108" s="331"/>
+      <c r="L108" s="331"/>
+      <c r="M108" s="331"/>
+      <c r="N108" s="331"/>
       <c r="O108" s="39"/>
     </row>
     <row r="109" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C109" s="332"/>
-      <c r="D109" s="332"/>
-      <c r="E109" s="332"/>
-      <c r="F109" s="332"/>
-      <c r="G109" s="332"/>
-      <c r="H109" s="332"/>
-      <c r="J109" s="330"/>
-      <c r="K109" s="330"/>
-      <c r="L109" s="330"/>
-      <c r="M109" s="330"/>
-      <c r="N109" s="330"/>
+      <c r="C109" s="333"/>
+      <c r="D109" s="333"/>
+      <c r="E109" s="333"/>
+      <c r="F109" s="333"/>
+      <c r="G109" s="333"/>
+      <c r="H109" s="333"/>
+      <c r="J109" s="331"/>
+      <c r="K109" s="331"/>
+      <c r="L109" s="331"/>
+      <c r="M109" s="331"/>
+      <c r="N109" s="331"/>
       <c r="O109" s="39"/>
     </row>
     <row r="110" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C110" s="332"/>
-      <c r="D110" s="332"/>
-      <c r="E110" s="332"/>
-      <c r="F110" s="332"/>
-      <c r="G110" s="332"/>
-      <c r="H110" s="332"/>
-      <c r="J110" s="330"/>
-      <c r="K110" s="330"/>
-      <c r="L110" s="330"/>
-      <c r="M110" s="330"/>
-      <c r="N110" s="330"/>
+      <c r="C110" s="333"/>
+      <c r="D110" s="333"/>
+      <c r="E110" s="333"/>
+      <c r="F110" s="333"/>
+      <c r="G110" s="333"/>
+      <c r="H110" s="333"/>
+      <c r="J110" s="331"/>
+      <c r="K110" s="331"/>
+      <c r="L110" s="331"/>
+      <c r="M110" s="331"/>
+      <c r="N110" s="331"/>
       <c r="O110" s="39"/>
     </row>
     <row r="111" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C111" s="332"/>
-      <c r="D111" s="332"/>
-      <c r="E111" s="332"/>
-      <c r="F111" s="332"/>
-      <c r="G111" s="332"/>
-      <c r="H111" s="332"/>
-      <c r="J111" s="330"/>
-      <c r="K111" s="330"/>
-      <c r="L111" s="330"/>
-      <c r="M111" s="330"/>
-      <c r="N111" s="330"/>
+      <c r="C111" s="333"/>
+      <c r="D111" s="333"/>
+      <c r="E111" s="333"/>
+      <c r="F111" s="333"/>
+      <c r="G111" s="333"/>
+      <c r="H111" s="333"/>
+      <c r="J111" s="331"/>
+      <c r="K111" s="331"/>
+      <c r="L111" s="331"/>
+      <c r="M111" s="331"/>
+      <c r="N111" s="331"/>
       <c r="O111" s="39"/>
     </row>
     <row r="112" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C112" s="332"/>
-      <c r="D112" s="332"/>
-      <c r="E112" s="332"/>
-      <c r="F112" s="332"/>
-      <c r="G112" s="332"/>
-      <c r="H112" s="332"/>
-      <c r="J112" s="330"/>
-      <c r="K112" s="330"/>
-      <c r="L112" s="330"/>
-      <c r="M112" s="330"/>
-      <c r="N112" s="330"/>
+      <c r="C112" s="333"/>
+      <c r="D112" s="333"/>
+      <c r="E112" s="333"/>
+      <c r="F112" s="333"/>
+      <c r="G112" s="333"/>
+      <c r="H112" s="333"/>
+      <c r="J112" s="331"/>
+      <c r="K112" s="331"/>
+      <c r="L112" s="331"/>
+      <c r="M112" s="331"/>
+      <c r="N112" s="331"/>
       <c r="O112" s="39"/>
     </row>
     <row r="113" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C113" s="332"/>
-      <c r="D113" s="332"/>
-      <c r="E113" s="332"/>
-      <c r="F113" s="332"/>
-      <c r="G113" s="332"/>
-      <c r="H113" s="332"/>
-      <c r="J113" s="330"/>
-      <c r="K113" s="330"/>
-      <c r="L113" s="330"/>
-      <c r="M113" s="330"/>
-      <c r="N113" s="330"/>
+      <c r="C113" s="333"/>
+      <c r="D113" s="333"/>
+      <c r="E113" s="333"/>
+      <c r="F113" s="333"/>
+      <c r="G113" s="333"/>
+      <c r="H113" s="333"/>
+      <c r="J113" s="331"/>
+      <c r="K113" s="331"/>
+      <c r="L113" s="331"/>
+      <c r="M113" s="331"/>
+      <c r="N113" s="331"/>
       <c r="O113" s="39"/>
     </row>
     <row r="114" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C114" s="332"/>
-      <c r="D114" s="332"/>
-      <c r="E114" s="332"/>
-      <c r="F114" s="332"/>
-      <c r="G114" s="332"/>
-      <c r="H114" s="332"/>
-      <c r="J114" s="330"/>
-      <c r="K114" s="330"/>
-      <c r="L114" s="330"/>
-      <c r="M114" s="330"/>
-      <c r="N114" s="330"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
+      <c r="G114" s="333"/>
+      <c r="H114" s="333"/>
+      <c r="J114" s="331"/>
+      <c r="K114" s="331"/>
+      <c r="L114" s="331"/>
+      <c r="M114" s="331"/>
+      <c r="N114" s="331"/>
       <c r="O114" s="39"/>
     </row>
     <row r="115" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C115" s="332"/>
-      <c r="D115" s="332"/>
-      <c r="E115" s="332"/>
-      <c r="F115" s="332"/>
-      <c r="G115" s="332"/>
-      <c r="H115" s="332"/>
-      <c r="J115" s="330"/>
-      <c r="K115" s="330"/>
-      <c r="L115" s="330"/>
-      <c r="M115" s="330"/>
-      <c r="N115" s="330"/>
+      <c r="C115" s="333"/>
+      <c r="D115" s="333"/>
+      <c r="E115" s="333"/>
+      <c r="F115" s="333"/>
+      <c r="G115" s="333"/>
+      <c r="H115" s="333"/>
+      <c r="J115" s="331"/>
+      <c r="K115" s="331"/>
+      <c r="L115" s="331"/>
+      <c r="M115" s="331"/>
+      <c r="N115" s="331"/>
       <c r="O115" s="39"/>
     </row>
     <row r="116" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C116" s="332"/>
-      <c r="D116" s="332"/>
-      <c r="E116" s="332"/>
-      <c r="F116" s="332"/>
-      <c r="G116" s="332"/>
-      <c r="H116" s="332"/>
-      <c r="J116" s="330"/>
-      <c r="K116" s="330"/>
-      <c r="L116" s="330"/>
-      <c r="M116" s="330"/>
-      <c r="N116" s="330"/>
+      <c r="C116" s="333"/>
+      <c r="D116" s="333"/>
+      <c r="E116" s="333"/>
+      <c r="F116" s="333"/>
+      <c r="G116" s="333"/>
+      <c r="H116" s="333"/>
+      <c r="J116" s="331"/>
+      <c r="K116" s="331"/>
+      <c r="L116" s="331"/>
+      <c r="M116" s="331"/>
+      <c r="N116" s="331"/>
       <c r="O116" s="39"/>
     </row>
     <row r="117" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C117" s="332"/>
-      <c r="D117" s="332"/>
-      <c r="E117" s="332"/>
-      <c r="F117" s="332"/>
-      <c r="G117" s="332"/>
-      <c r="H117" s="332"/>
-      <c r="J117" s="330"/>
-      <c r="K117" s="330"/>
-      <c r="L117" s="330"/>
-      <c r="M117" s="330"/>
-      <c r="N117" s="330"/>
+      <c r="C117" s="333"/>
+      <c r="D117" s="333"/>
+      <c r="E117" s="333"/>
+      <c r="F117" s="333"/>
+      <c r="G117" s="333"/>
+      <c r="H117" s="333"/>
+      <c r="J117" s="331"/>
+      <c r="K117" s="331"/>
+      <c r="L117" s="331"/>
+      <c r="M117" s="331"/>
+      <c r="N117" s="331"/>
       <c r="O117" s="39"/>
     </row>
     <row r="118" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C118" s="332"/>
-      <c r="D118" s="332"/>
-      <c r="E118" s="332"/>
-      <c r="F118" s="332"/>
-      <c r="G118" s="332"/>
-      <c r="H118" s="332"/>
-      <c r="J118" s="330"/>
-      <c r="K118" s="330"/>
-      <c r="L118" s="330"/>
-      <c r="M118" s="330"/>
-      <c r="N118" s="330"/>
+      <c r="C118" s="333"/>
+      <c r="D118" s="333"/>
+      <c r="E118" s="333"/>
+      <c r="F118" s="333"/>
+      <c r="G118" s="333"/>
+      <c r="H118" s="333"/>
+      <c r="J118" s="331"/>
+      <c r="K118" s="331"/>
+      <c r="L118" s="331"/>
+      <c r="M118" s="331"/>
+      <c r="N118" s="331"/>
       <c r="O118" s="39"/>
     </row>
     <row r="119" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C119" s="332"/>
-      <c r="D119" s="332"/>
-      <c r="E119" s="332"/>
-      <c r="F119" s="332"/>
-      <c r="G119" s="332"/>
-      <c r="H119" s="332"/>
-      <c r="J119" s="330"/>
-      <c r="K119" s="330"/>
-      <c r="L119" s="330"/>
-      <c r="M119" s="330"/>
-      <c r="N119" s="330"/>
+      <c r="C119" s="333"/>
+      <c r="D119" s="333"/>
+      <c r="E119" s="333"/>
+      <c r="F119" s="333"/>
+      <c r="G119" s="333"/>
+      <c r="H119" s="333"/>
+      <c r="J119" s="331"/>
+      <c r="K119" s="331"/>
+      <c r="L119" s="331"/>
+      <c r="M119" s="331"/>
+      <c r="N119" s="331"/>
       <c r="O119" s="39"/>
     </row>
     <row r="120" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C120" s="332"/>
-      <c r="D120" s="332"/>
-      <c r="E120" s="332"/>
-      <c r="F120" s="332"/>
-      <c r="G120" s="332"/>
-      <c r="H120" s="332"/>
-      <c r="J120" s="330"/>
-      <c r="K120" s="330"/>
-      <c r="L120" s="330"/>
-      <c r="M120" s="330"/>
-      <c r="N120" s="330"/>
+      <c r="C120" s="333"/>
+      <c r="D120" s="333"/>
+      <c r="E120" s="333"/>
+      <c r="F120" s="333"/>
+      <c r="G120" s="333"/>
+      <c r="H120" s="333"/>
+      <c r="J120" s="331"/>
+      <c r="K120" s="331"/>
+      <c r="L120" s="331"/>
+      <c r="M120" s="331"/>
+      <c r="N120" s="331"/>
       <c r="O120" s="39"/>
     </row>
     <row r="121" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C121" s="332"/>
-      <c r="D121" s="332"/>
-      <c r="E121" s="332"/>
-      <c r="F121" s="332"/>
-      <c r="G121" s="332"/>
-      <c r="H121" s="332"/>
-      <c r="J121" s="330"/>
-      <c r="K121" s="330"/>
-      <c r="L121" s="330"/>
-      <c r="M121" s="330"/>
-      <c r="N121" s="330"/>
+      <c r="C121" s="333"/>
+      <c r="D121" s="333"/>
+      <c r="E121" s="333"/>
+      <c r="F121" s="333"/>
+      <c r="G121" s="333"/>
+      <c r="H121" s="333"/>
+      <c r="J121" s="331"/>
+      <c r="K121" s="331"/>
+      <c r="L121" s="331"/>
+      <c r="M121" s="331"/>
+      <c r="N121" s="331"/>
       <c r="O121" s="39"/>
     </row>
     <row r="122" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C122" s="332"/>
-      <c r="D122" s="332"/>
-      <c r="E122" s="332"/>
-      <c r="F122" s="332"/>
-      <c r="G122" s="332"/>
-      <c r="H122" s="332"/>
-      <c r="J122" s="330"/>
-      <c r="K122" s="330"/>
-      <c r="L122" s="330"/>
-      <c r="M122" s="330"/>
-      <c r="N122" s="330"/>
+      <c r="C122" s="333"/>
+      <c r="D122" s="333"/>
+      <c r="E122" s="333"/>
+      <c r="F122" s="333"/>
+      <c r="G122" s="333"/>
+      <c r="H122" s="333"/>
+      <c r="J122" s="331"/>
+      <c r="K122" s="331"/>
+      <c r="L122" s="331"/>
+      <c r="M122" s="331"/>
+      <c r="N122" s="331"/>
       <c r="O122" s="39"/>
     </row>
     <row r="123" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C123" s="332"/>
-      <c r="D123" s="332"/>
-      <c r="E123" s="332"/>
-      <c r="F123" s="332"/>
-      <c r="G123" s="332"/>
-      <c r="H123" s="332"/>
-      <c r="J123" s="330"/>
-      <c r="K123" s="330"/>
-      <c r="L123" s="330"/>
-      <c r="M123" s="330"/>
-      <c r="N123" s="330"/>
+      <c r="C123" s="333"/>
+      <c r="D123" s="333"/>
+      <c r="E123" s="333"/>
+      <c r="F123" s="333"/>
+      <c r="G123" s="333"/>
+      <c r="H123" s="333"/>
+      <c r="J123" s="331"/>
+      <c r="K123" s="331"/>
+      <c r="L123" s="331"/>
+      <c r="M123" s="331"/>
+      <c r="N123" s="331"/>
       <c r="O123" s="39"/>
     </row>
     <row r="124" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C124" s="332"/>
-      <c r="D124" s="332"/>
-      <c r="E124" s="332"/>
-      <c r="F124" s="332"/>
-      <c r="G124" s="332"/>
-      <c r="H124" s="332"/>
-      <c r="J124" s="330"/>
-      <c r="K124" s="330"/>
-      <c r="L124" s="330"/>
-      <c r="M124" s="330"/>
-      <c r="N124" s="330"/>
+      <c r="C124" s="333"/>
+      <c r="D124" s="333"/>
+      <c r="E124" s="333"/>
+      <c r="F124" s="333"/>
+      <c r="G124" s="333"/>
+      <c r="H124" s="333"/>
+      <c r="J124" s="331"/>
+      <c r="K124" s="331"/>
+      <c r="L124" s="331"/>
+      <c r="M124" s="331"/>
+      <c r="N124" s="331"/>
       <c r="O124" s="39"/>
     </row>
     <row r="125" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C125" s="332"/>
-      <c r="D125" s="332"/>
-      <c r="E125" s="332"/>
-      <c r="F125" s="332"/>
-      <c r="G125" s="332"/>
-      <c r="H125" s="332"/>
-      <c r="J125" s="330"/>
-      <c r="K125" s="330"/>
-      <c r="L125" s="330"/>
-      <c r="M125" s="330"/>
-      <c r="N125" s="330"/>
+      <c r="C125" s="333"/>
+      <c r="D125" s="333"/>
+      <c r="E125" s="333"/>
+      <c r="F125" s="333"/>
+      <c r="G125" s="333"/>
+      <c r="H125" s="333"/>
+      <c r="J125" s="331"/>
+      <c r="K125" s="331"/>
+      <c r="L125" s="331"/>
+      <c r="M125" s="331"/>
+      <c r="N125" s="331"/>
       <c r="O125" s="39"/>
     </row>
     <row r="126" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C126" s="332"/>
-      <c r="D126" s="332"/>
-      <c r="E126" s="332"/>
-      <c r="F126" s="332"/>
-      <c r="G126" s="332"/>
-      <c r="H126" s="332"/>
-      <c r="J126" s="330"/>
-      <c r="K126" s="330"/>
-      <c r="L126" s="330"/>
-      <c r="M126" s="330"/>
-      <c r="N126" s="330"/>
+      <c r="C126" s="333"/>
+      <c r="D126" s="333"/>
+      <c r="E126" s="333"/>
+      <c r="F126" s="333"/>
+      <c r="G126" s="333"/>
+      <c r="H126" s="333"/>
+      <c r="J126" s="331"/>
+      <c r="K126" s="331"/>
+      <c r="L126" s="331"/>
+      <c r="M126" s="331"/>
+      <c r="N126" s="331"/>
       <c r="O126" s="39"/>
     </row>
     <row r="127" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C127" s="332"/>
-      <c r="D127" s="332"/>
-      <c r="E127" s="332"/>
-      <c r="F127" s="332"/>
-      <c r="G127" s="332"/>
-      <c r="H127" s="332"/>
-      <c r="J127" s="330"/>
-      <c r="K127" s="330"/>
-      <c r="L127" s="330"/>
-      <c r="M127" s="330"/>
-      <c r="N127" s="330"/>
+      <c r="C127" s="333"/>
+      <c r="D127" s="333"/>
+      <c r="E127" s="333"/>
+      <c r="F127" s="333"/>
+      <c r="G127" s="333"/>
+      <c r="H127" s="333"/>
+      <c r="J127" s="331"/>
+      <c r="K127" s="331"/>
+      <c r="L127" s="331"/>
+      <c r="M127" s="331"/>
+      <c r="N127" s="331"/>
       <c r="O127" s="39"/>
     </row>
     <row r="128" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C128" s="332"/>
-      <c r="D128" s="332"/>
-      <c r="E128" s="332"/>
-      <c r="F128" s="332"/>
-      <c r="G128" s="332"/>
-      <c r="H128" s="332"/>
-      <c r="J128" s="330"/>
-      <c r="K128" s="330"/>
-      <c r="L128" s="330"/>
-      <c r="M128" s="330"/>
-      <c r="N128" s="330"/>
+      <c r="C128" s="333"/>
+      <c r="D128" s="333"/>
+      <c r="E128" s="333"/>
+      <c r="F128" s="333"/>
+      <c r="G128" s="333"/>
+      <c r="H128" s="333"/>
+      <c r="J128" s="331"/>
+      <c r="K128" s="331"/>
+      <c r="L128" s="331"/>
+      <c r="M128" s="331"/>
+      <c r="N128" s="331"/>
       <c r="O128" s="39"/>
     </row>
     <row r="129" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C129" s="332"/>
-      <c r="D129" s="332"/>
-      <c r="E129" s="332"/>
-      <c r="F129" s="332"/>
-      <c r="G129" s="332"/>
-      <c r="H129" s="332"/>
-      <c r="J129" s="330"/>
-      <c r="K129" s="330"/>
-      <c r="L129" s="330"/>
-      <c r="M129" s="330"/>
-      <c r="N129" s="330"/>
+      <c r="C129" s="333"/>
+      <c r="D129" s="333"/>
+      <c r="E129" s="333"/>
+      <c r="F129" s="333"/>
+      <c r="G129" s="333"/>
+      <c r="H129" s="333"/>
+      <c r="J129" s="331"/>
+      <c r="K129" s="331"/>
+      <c r="L129" s="331"/>
+      <c r="M129" s="331"/>
+      <c r="N129" s="331"/>
       <c r="O129" s="39"/>
     </row>
     <row r="130" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C130" s="332"/>
-      <c r="D130" s="332"/>
-      <c r="E130" s="332"/>
-      <c r="F130" s="332"/>
-      <c r="G130" s="332"/>
-      <c r="H130" s="332"/>
-      <c r="J130" s="330"/>
-      <c r="K130" s="330"/>
-      <c r="L130" s="330"/>
-      <c r="M130" s="330"/>
-      <c r="N130" s="330"/>
+      <c r="C130" s="333"/>
+      <c r="D130" s="333"/>
+      <c r="E130" s="333"/>
+      <c r="F130" s="333"/>
+      <c r="G130" s="333"/>
+      <c r="H130" s="333"/>
+      <c r="J130" s="331"/>
+      <c r="K130" s="331"/>
+      <c r="L130" s="331"/>
+      <c r="M130" s="331"/>
+      <c r="N130" s="331"/>
       <c r="O130" s="39"/>
     </row>
     <row r="131" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C131" s="332"/>
-      <c r="D131" s="332"/>
-      <c r="E131" s="332"/>
-      <c r="F131" s="332"/>
-      <c r="G131" s="332"/>
-      <c r="H131" s="332"/>
-      <c r="J131" s="330"/>
-      <c r="K131" s="330"/>
-      <c r="L131" s="330"/>
-      <c r="M131" s="330"/>
-      <c r="N131" s="330"/>
+      <c r="C131" s="333"/>
+      <c r="D131" s="333"/>
+      <c r="E131" s="333"/>
+      <c r="F131" s="333"/>
+      <c r="G131" s="333"/>
+      <c r="H131" s="333"/>
+      <c r="J131" s="331"/>
+      <c r="K131" s="331"/>
+      <c r="L131" s="331"/>
+      <c r="M131" s="331"/>
+      <c r="N131" s="331"/>
       <c r="O131" s="39"/>
     </row>
     <row r="132" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C132" s="332"/>
-      <c r="D132" s="332"/>
-      <c r="E132" s="332"/>
-      <c r="F132" s="332"/>
-      <c r="G132" s="332"/>
-      <c r="H132" s="332"/>
-      <c r="J132" s="330"/>
-      <c r="K132" s="330"/>
-      <c r="L132" s="330"/>
-      <c r="M132" s="330"/>
-      <c r="N132" s="330"/>
+      <c r="C132" s="333"/>
+      <c r="D132" s="333"/>
+      <c r="E132" s="333"/>
+      <c r="F132" s="333"/>
+      <c r="G132" s="333"/>
+      <c r="H132" s="333"/>
+      <c r="J132" s="331"/>
+      <c r="K132" s="331"/>
+      <c r="L132" s="331"/>
+      <c r="M132" s="331"/>
+      <c r="N132" s="331"/>
       <c r="O132" s="39"/>
     </row>
     <row r="133" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C133" s="332"/>
-      <c r="D133" s="332"/>
-      <c r="E133" s="332"/>
-      <c r="F133" s="332"/>
-      <c r="G133" s="332"/>
-      <c r="H133" s="332"/>
-      <c r="J133" s="330"/>
-      <c r="K133" s="330"/>
-      <c r="L133" s="330"/>
-      <c r="M133" s="330"/>
-      <c r="N133" s="330"/>
+      <c r="C133" s="333"/>
+      <c r="D133" s="333"/>
+      <c r="E133" s="333"/>
+      <c r="F133" s="333"/>
+      <c r="G133" s="333"/>
+      <c r="H133" s="333"/>
+      <c r="J133" s="331"/>
+      <c r="K133" s="331"/>
+      <c r="L133" s="331"/>
+      <c r="M133" s="331"/>
+      <c r="N133" s="331"/>
       <c r="O133" s="39"/>
     </row>
     <row r="134" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C134" s="332"/>
-      <c r="D134" s="332"/>
-      <c r="E134" s="332"/>
-      <c r="F134" s="332"/>
-      <c r="G134" s="332"/>
-      <c r="H134" s="332"/>
-      <c r="J134" s="330"/>
-      <c r="K134" s="330"/>
-      <c r="L134" s="330"/>
-      <c r="M134" s="330"/>
-      <c r="N134" s="330"/>
+      <c r="C134" s="333"/>
+      <c r="D134" s="333"/>
+      <c r="E134" s="333"/>
+      <c r="F134" s="333"/>
+      <c r="G134" s="333"/>
+      <c r="H134" s="333"/>
+      <c r="J134" s="331"/>
+      <c r="K134" s="331"/>
+      <c r="L134" s="331"/>
+      <c r="M134" s="331"/>
+      <c r="N134" s="331"/>
       <c r="O134" s="39"/>
     </row>
     <row r="135" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C135" s="332"/>
-      <c r="D135" s="332"/>
-      <c r="E135" s="332"/>
-      <c r="F135" s="332"/>
-      <c r="G135" s="332"/>
-      <c r="H135" s="332"/>
-      <c r="J135" s="330"/>
-      <c r="K135" s="330"/>
-      <c r="L135" s="330"/>
-      <c r="M135" s="330"/>
-      <c r="N135" s="330"/>
+      <c r="C135" s="333"/>
+      <c r="D135" s="333"/>
+      <c r="E135" s="333"/>
+      <c r="F135" s="333"/>
+      <c r="G135" s="333"/>
+      <c r="H135" s="333"/>
+      <c r="J135" s="331"/>
+      <c r="K135" s="331"/>
+      <c r="L135" s="331"/>
+      <c r="M135" s="331"/>
+      <c r="N135" s="331"/>
       <c r="O135" s="39"/>
     </row>
     <row r="136" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C136" s="332"/>
-      <c r="D136" s="332"/>
-      <c r="E136" s="332"/>
-      <c r="F136" s="332"/>
-      <c r="G136" s="332"/>
-      <c r="H136" s="332"/>
-      <c r="J136" s="330"/>
-      <c r="K136" s="330"/>
-      <c r="L136" s="330"/>
-      <c r="M136" s="330"/>
-      <c r="N136" s="330"/>
+      <c r="C136" s="333"/>
+      <c r="D136" s="333"/>
+      <c r="E136" s="333"/>
+      <c r="F136" s="333"/>
+      <c r="G136" s="333"/>
+      <c r="H136" s="333"/>
+      <c r="J136" s="331"/>
+      <c r="K136" s="331"/>
+      <c r="L136" s="331"/>
+      <c r="M136" s="331"/>
+      <c r="N136" s="331"/>
       <c r="O136" s="39"/>
     </row>
     <row r="137" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C137" s="332"/>
-      <c r="D137" s="332"/>
-      <c r="E137" s="332"/>
-      <c r="F137" s="332"/>
-      <c r="G137" s="332"/>
-      <c r="H137" s="332"/>
-      <c r="J137" s="330"/>
-      <c r="K137" s="330"/>
-      <c r="L137" s="330"/>
-      <c r="M137" s="330"/>
-      <c r="N137" s="330"/>
+      <c r="C137" s="333"/>
+      <c r="D137" s="333"/>
+      <c r="E137" s="333"/>
+      <c r="F137" s="333"/>
+      <c r="G137" s="333"/>
+      <c r="H137" s="333"/>
+      <c r="J137" s="331"/>
+      <c r="K137" s="331"/>
+      <c r="L137" s="331"/>
+      <c r="M137" s="331"/>
+      <c r="N137" s="331"/>
       <c r="O137" s="39"/>
     </row>
     <row r="138" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C138" s="332"/>
-      <c r="D138" s="332"/>
-      <c r="E138" s="332"/>
-      <c r="F138" s="332"/>
-      <c r="G138" s="332"/>
-      <c r="H138" s="332"/>
-      <c r="J138" s="330"/>
-      <c r="K138" s="330"/>
-      <c r="L138" s="330"/>
-      <c r="M138" s="330"/>
-      <c r="N138" s="330"/>
+      <c r="C138" s="333"/>
+      <c r="D138" s="333"/>
+      <c r="E138" s="333"/>
+      <c r="F138" s="333"/>
+      <c r="G138" s="333"/>
+      <c r="H138" s="333"/>
+      <c r="J138" s="331"/>
+      <c r="K138" s="331"/>
+      <c r="L138" s="331"/>
+      <c r="M138" s="331"/>
+      <c r="N138" s="331"/>
       <c r="O138" s="39"/>
     </row>
     <row r="139" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C139" s="332"/>
-      <c r="D139" s="332"/>
-      <c r="E139" s="332"/>
-      <c r="F139" s="332"/>
-      <c r="G139" s="332"/>
-      <c r="H139" s="332"/>
-      <c r="J139" s="330"/>
-      <c r="K139" s="330"/>
-      <c r="L139" s="330"/>
-      <c r="M139" s="330"/>
-      <c r="N139" s="330"/>
+      <c r="C139" s="333"/>
+      <c r="D139" s="333"/>
+      <c r="E139" s="333"/>
+      <c r="F139" s="333"/>
+      <c r="G139" s="333"/>
+      <c r="H139" s="333"/>
+      <c r="J139" s="331"/>
+      <c r="K139" s="331"/>
+      <c r="L139" s="331"/>
+      <c r="M139" s="331"/>
+      <c r="N139" s="331"/>
       <c r="O139" s="39"/>
     </row>
     <row r="140" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C140" s="332"/>
-      <c r="D140" s="332"/>
-      <c r="E140" s="332"/>
-      <c r="F140" s="332"/>
-      <c r="G140" s="332"/>
-      <c r="H140" s="332"/>
-      <c r="J140" s="330"/>
-      <c r="K140" s="330"/>
-      <c r="L140" s="330"/>
-      <c r="M140" s="330"/>
-      <c r="N140" s="330"/>
+      <c r="C140" s="333"/>
+      <c r="D140" s="333"/>
+      <c r="E140" s="333"/>
+      <c r="F140" s="333"/>
+      <c r="G140" s="333"/>
+      <c r="H140" s="333"/>
+      <c r="J140" s="331"/>
+      <c r="K140" s="331"/>
+      <c r="L140" s="331"/>
+      <c r="M140" s="331"/>
+      <c r="N140" s="331"/>
       <c r="O140" s="39"/>
     </row>
     <row r="141" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C141" s="332"/>
-      <c r="D141" s="332"/>
-      <c r="E141" s="332"/>
-      <c r="F141" s="332"/>
-      <c r="G141" s="332"/>
-      <c r="H141" s="332"/>
-      <c r="J141" s="330"/>
-      <c r="K141" s="330"/>
-      <c r="L141" s="330"/>
-      <c r="M141" s="330"/>
-      <c r="N141" s="330"/>
+      <c r="C141" s="333"/>
+      <c r="D141" s="333"/>
+      <c r="E141" s="333"/>
+      <c r="F141" s="333"/>
+      <c r="G141" s="333"/>
+      <c r="H141" s="333"/>
+      <c r="J141" s="331"/>
+      <c r="K141" s="331"/>
+      <c r="L141" s="331"/>
+      <c r="M141" s="331"/>
+      <c r="N141" s="331"/>
       <c r="O141" s="39"/>
     </row>
     <row r="142" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C142" s="332"/>
-      <c r="D142" s="332"/>
-      <c r="E142" s="332"/>
-      <c r="F142" s="332"/>
-      <c r="G142" s="332"/>
-      <c r="H142" s="332"/>
-      <c r="J142" s="330"/>
-      <c r="K142" s="330"/>
-      <c r="L142" s="330"/>
-      <c r="M142" s="330"/>
-      <c r="N142" s="330"/>
+      <c r="C142" s="333"/>
+      <c r="D142" s="333"/>
+      <c r="E142" s="333"/>
+      <c r="F142" s="333"/>
+      <c r="G142" s="333"/>
+      <c r="H142" s="333"/>
+      <c r="J142" s="331"/>
+      <c r="K142" s="331"/>
+      <c r="L142" s="331"/>
+      <c r="M142" s="331"/>
+      <c r="N142" s="331"/>
       <c r="O142" s="39"/>
     </row>
     <row r="143" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C143" s="332"/>
-      <c r="D143" s="332"/>
-      <c r="E143" s="332"/>
-      <c r="F143" s="332"/>
-      <c r="G143" s="332"/>
-      <c r="H143" s="332"/>
-      <c r="J143" s="330"/>
-      <c r="K143" s="330"/>
-      <c r="L143" s="330"/>
-      <c r="M143" s="330"/>
-      <c r="N143" s="330"/>
+      <c r="C143" s="333"/>
+      <c r="D143" s="333"/>
+      <c r="E143" s="333"/>
+      <c r="F143" s="333"/>
+      <c r="G143" s="333"/>
+      <c r="H143" s="333"/>
+      <c r="J143" s="331"/>
+      <c r="K143" s="331"/>
+      <c r="L143" s="331"/>
+      <c r="M143" s="331"/>
+      <c r="N143" s="331"/>
       <c r="O143" s="39"/>
     </row>
     <row r="144" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C144" s="332"/>
-      <c r="D144" s="332"/>
-      <c r="E144" s="332"/>
-      <c r="F144" s="332"/>
-      <c r="G144" s="332"/>
-      <c r="H144" s="332"/>
-      <c r="J144" s="330"/>
-      <c r="K144" s="330"/>
-      <c r="L144" s="330"/>
-      <c r="M144" s="330"/>
-      <c r="N144" s="330"/>
+      <c r="C144" s="333"/>
+      <c r="D144" s="333"/>
+      <c r="E144" s="333"/>
+      <c r="F144" s="333"/>
+      <c r="G144" s="333"/>
+      <c r="H144" s="333"/>
+      <c r="J144" s="331"/>
+      <c r="K144" s="331"/>
+      <c r="L144" s="331"/>
+      <c r="M144" s="331"/>
+      <c r="N144" s="331"/>
       <c r="O144" s="39"/>
     </row>
     <row r="145" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C145" s="332"/>
-      <c r="D145" s="332"/>
-      <c r="E145" s="332"/>
-      <c r="F145" s="332"/>
-      <c r="G145" s="332"/>
-      <c r="H145" s="332"/>
-      <c r="J145" s="330"/>
-      <c r="K145" s="330"/>
-      <c r="L145" s="330"/>
-      <c r="M145" s="330"/>
-      <c r="N145" s="330"/>
+      <c r="C145" s="333"/>
+      <c r="D145" s="333"/>
+      <c r="E145" s="333"/>
+      <c r="F145" s="333"/>
+      <c r="G145" s="333"/>
+      <c r="H145" s="333"/>
+      <c r="J145" s="331"/>
+      <c r="K145" s="331"/>
+      <c r="L145" s="331"/>
+      <c r="M145" s="331"/>
+      <c r="N145" s="331"/>
       <c r="O145" s="39"/>
     </row>
     <row r="146" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C146" s="332"/>
-      <c r="D146" s="332"/>
-      <c r="E146" s="332"/>
-      <c r="F146" s="332"/>
-      <c r="G146" s="332"/>
-      <c r="H146" s="332"/>
-      <c r="J146" s="330"/>
-      <c r="K146" s="330"/>
-      <c r="L146" s="330"/>
-      <c r="M146" s="330"/>
-      <c r="N146" s="330"/>
+      <c r="C146" s="333"/>
+      <c r="D146" s="333"/>
+      <c r="E146" s="333"/>
+      <c r="F146" s="333"/>
+      <c r="G146" s="333"/>
+      <c r="H146" s="333"/>
+      <c r="J146" s="331"/>
+      <c r="K146" s="331"/>
+      <c r="L146" s="331"/>
+      <c r="M146" s="331"/>
+      <c r="N146" s="331"/>
       <c r="O146" s="39"/>
     </row>
     <row r="147" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C147" s="332"/>
-      <c r="D147" s="332"/>
-      <c r="E147" s="332"/>
-      <c r="F147" s="332"/>
-      <c r="G147" s="332"/>
-      <c r="H147" s="332"/>
-      <c r="J147" s="330"/>
-      <c r="K147" s="330"/>
-      <c r="L147" s="330"/>
-      <c r="M147" s="330"/>
-      <c r="N147" s="330"/>
+      <c r="C147" s="333"/>
+      <c r="D147" s="333"/>
+      <c r="E147" s="333"/>
+      <c r="F147" s="333"/>
+      <c r="G147" s="333"/>
+      <c r="H147" s="333"/>
+      <c r="J147" s="331"/>
+      <c r="K147" s="331"/>
+      <c r="L147" s="331"/>
+      <c r="M147" s="331"/>
+      <c r="N147" s="331"/>
       <c r="O147" s="39"/>
     </row>
     <row r="148" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C148" s="332"/>
-      <c r="D148" s="332"/>
-      <c r="E148" s="332"/>
-      <c r="F148" s="332"/>
-      <c r="G148" s="332"/>
-      <c r="H148" s="332"/>
-      <c r="J148" s="330"/>
-      <c r="K148" s="330"/>
-      <c r="L148" s="330"/>
-      <c r="M148" s="330"/>
-      <c r="N148" s="330"/>
+      <c r="C148" s="333"/>
+      <c r="D148" s="333"/>
+      <c r="E148" s="333"/>
+      <c r="F148" s="333"/>
+      <c r="G148" s="333"/>
+      <c r="H148" s="333"/>
+      <c r="J148" s="331"/>
+      <c r="K148" s="331"/>
+      <c r="L148" s="331"/>
+      <c r="M148" s="331"/>
+      <c r="N148" s="331"/>
       <c r="O148" s="39"/>
     </row>
     <row r="149" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C149" s="332"/>
-      <c r="D149" s="332"/>
-      <c r="E149" s="332"/>
-      <c r="F149" s="332"/>
-      <c r="G149" s="332"/>
-      <c r="H149" s="332"/>
-      <c r="J149" s="330"/>
-      <c r="K149" s="330"/>
-      <c r="L149" s="330"/>
-      <c r="M149" s="330"/>
-      <c r="N149" s="330"/>
+      <c r="C149" s="333"/>
+      <c r="D149" s="333"/>
+      <c r="E149" s="333"/>
+      <c r="F149" s="333"/>
+      <c r="G149" s="333"/>
+      <c r="H149" s="333"/>
+      <c r="J149" s="331"/>
+      <c r="K149" s="331"/>
+      <c r="L149" s="331"/>
+      <c r="M149" s="331"/>
+      <c r="N149" s="331"/>
       <c r="O149" s="39"/>
     </row>
     <row r="150" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C150" s="332"/>
-      <c r="D150" s="332"/>
-      <c r="E150" s="332"/>
-      <c r="F150" s="332"/>
-      <c r="G150" s="332"/>
-      <c r="H150" s="332"/>
-      <c r="J150" s="330"/>
-      <c r="K150" s="330"/>
-      <c r="L150" s="330"/>
-      <c r="M150" s="330"/>
-      <c r="N150" s="330"/>
+      <c r="C150" s="333"/>
+      <c r="D150" s="333"/>
+      <c r="E150" s="333"/>
+      <c r="F150" s="333"/>
+      <c r="G150" s="333"/>
+      <c r="H150" s="333"/>
+      <c r="J150" s="331"/>
+      <c r="K150" s="331"/>
+      <c r="L150" s="331"/>
+      <c r="M150" s="331"/>
+      <c r="N150" s="331"/>
       <c r="O150" s="39"/>
     </row>
     <row r="151" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C151" s="332"/>
-      <c r="D151" s="332"/>
-      <c r="E151" s="332"/>
-      <c r="F151" s="332"/>
-      <c r="G151" s="332"/>
-      <c r="H151" s="332"/>
-      <c r="J151" s="330"/>
-      <c r="K151" s="330"/>
-      <c r="L151" s="330"/>
-      <c r="M151" s="330"/>
-      <c r="N151" s="330"/>
+      <c r="C151" s="333"/>
+      <c r="D151" s="333"/>
+      <c r="E151" s="333"/>
+      <c r="F151" s="333"/>
+      <c r="G151" s="333"/>
+      <c r="H151" s="333"/>
+      <c r="J151" s="331"/>
+      <c r="K151" s="331"/>
+      <c r="L151" s="331"/>
+      <c r="M151" s="331"/>
+      <c r="N151" s="331"/>
       <c r="O151" s="39"/>
     </row>
     <row r="152" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C152" s="332"/>
-      <c r="D152" s="332"/>
-      <c r="E152" s="332"/>
-      <c r="F152" s="332"/>
-      <c r="G152" s="332"/>
-      <c r="H152" s="332"/>
-      <c r="J152" s="330"/>
-      <c r="K152" s="330"/>
-      <c r="L152" s="330"/>
-      <c r="M152" s="330"/>
-      <c r="N152" s="330"/>
+      <c r="C152" s="333"/>
+      <c r="D152" s="333"/>
+      <c r="E152" s="333"/>
+      <c r="F152" s="333"/>
+      <c r="G152" s="333"/>
+      <c r="H152" s="333"/>
+      <c r="J152" s="331"/>
+      <c r="K152" s="331"/>
+      <c r="L152" s="331"/>
+      <c r="M152" s="331"/>
+      <c r="N152" s="331"/>
       <c r="O152" s="39"/>
     </row>
     <row r="153" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C153" s="332"/>
-      <c r="D153" s="332"/>
-      <c r="E153" s="332"/>
-      <c r="F153" s="332"/>
-      <c r="G153" s="332"/>
-      <c r="H153" s="332"/>
-      <c r="J153" s="330"/>
-      <c r="K153" s="330"/>
-      <c r="L153" s="330"/>
-      <c r="M153" s="330"/>
-      <c r="N153" s="330"/>
+      <c r="C153" s="333"/>
+      <c r="D153" s="333"/>
+      <c r="E153" s="333"/>
+      <c r="F153" s="333"/>
+      <c r="G153" s="333"/>
+      <c r="H153" s="333"/>
+      <c r="J153" s="331"/>
+      <c r="K153" s="331"/>
+      <c r="L153" s="331"/>
+      <c r="M153" s="331"/>
+      <c r="N153" s="331"/>
       <c r="O153" s="39"/>
     </row>
     <row r="154" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C154" s="332"/>
-      <c r="D154" s="332"/>
-      <c r="E154" s="332"/>
-      <c r="F154" s="332"/>
-      <c r="G154" s="332"/>
-      <c r="H154" s="332"/>
-      <c r="J154" s="330"/>
-      <c r="K154" s="330"/>
-      <c r="L154" s="330"/>
-      <c r="M154" s="330"/>
-      <c r="N154" s="330"/>
+      <c r="C154" s="333"/>
+      <c r="D154" s="333"/>
+      <c r="E154" s="333"/>
+      <c r="F154" s="333"/>
+      <c r="G154" s="333"/>
+      <c r="H154" s="333"/>
+      <c r="J154" s="331"/>
+      <c r="K154" s="331"/>
+      <c r="L154" s="331"/>
+      <c r="M154" s="331"/>
+      <c r="N154" s="331"/>
       <c r="O154" s="39"/>
     </row>
     <row r="155" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C155" s="332"/>
-      <c r="D155" s="332"/>
-      <c r="E155" s="332"/>
-      <c r="F155" s="332"/>
-      <c r="G155" s="332"/>
-      <c r="H155" s="332"/>
-      <c r="J155" s="330"/>
-      <c r="K155" s="330"/>
-      <c r="L155" s="330"/>
-      <c r="M155" s="330"/>
-      <c r="N155" s="330"/>
+      <c r="C155" s="333"/>
+      <c r="D155" s="333"/>
+      <c r="E155" s="333"/>
+      <c r="F155" s="333"/>
+      <c r="G155" s="333"/>
+      <c r="H155" s="333"/>
+      <c r="J155" s="331"/>
+      <c r="K155" s="331"/>
+      <c r="L155" s="331"/>
+      <c r="M155" s="331"/>
+      <c r="N155" s="331"/>
       <c r="O155" s="39"/>
     </row>
     <row r="156" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C156" s="332"/>
-      <c r="D156" s="332"/>
-      <c r="E156" s="332"/>
-      <c r="F156" s="332"/>
-      <c r="G156" s="332"/>
-      <c r="H156" s="332"/>
-      <c r="J156" s="330"/>
-      <c r="K156" s="330"/>
-      <c r="L156" s="330"/>
-      <c r="M156" s="330"/>
-      <c r="N156" s="330"/>
+      <c r="C156" s="333"/>
+      <c r="D156" s="333"/>
+      <c r="E156" s="333"/>
+      <c r="F156" s="333"/>
+      <c r="G156" s="333"/>
+      <c r="H156" s="333"/>
+      <c r="J156" s="331"/>
+      <c r="K156" s="331"/>
+      <c r="L156" s="331"/>
+      <c r="M156" s="331"/>
+      <c r="N156" s="331"/>
       <c r="O156" s="39"/>
     </row>
     <row r="157" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C157" s="332"/>
-      <c r="D157" s="332"/>
-      <c r="E157" s="332"/>
-      <c r="F157" s="332"/>
-      <c r="G157" s="332"/>
-      <c r="H157" s="332"/>
-      <c r="J157" s="330"/>
-      <c r="K157" s="330"/>
-      <c r="L157" s="330"/>
-      <c r="M157" s="330"/>
-      <c r="N157" s="330"/>
+      <c r="C157" s="333"/>
+      <c r="D157" s="333"/>
+      <c r="E157" s="333"/>
+      <c r="F157" s="333"/>
+      <c r="G157" s="333"/>
+      <c r="H157" s="333"/>
+      <c r="J157" s="331"/>
+      <c r="K157" s="331"/>
+      <c r="L157" s="331"/>
+      <c r="M157" s="331"/>
+      <c r="N157" s="331"/>
       <c r="O157" s="39"/>
     </row>
     <row r="158" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C158" s="332"/>
-      <c r="D158" s="332"/>
-      <c r="E158" s="332"/>
-      <c r="F158" s="332"/>
-      <c r="G158" s="332"/>
-      <c r="H158" s="332"/>
-      <c r="J158" s="330"/>
-      <c r="K158" s="330"/>
-      <c r="L158" s="330"/>
-      <c r="M158" s="330"/>
-      <c r="N158" s="330"/>
+      <c r="C158" s="333"/>
+      <c r="D158" s="333"/>
+      <c r="E158" s="333"/>
+      <c r="F158" s="333"/>
+      <c r="G158" s="333"/>
+      <c r="H158" s="333"/>
+      <c r="J158" s="331"/>
+      <c r="K158" s="331"/>
+      <c r="L158" s="331"/>
+      <c r="M158" s="331"/>
+      <c r="N158" s="331"/>
       <c r="O158" s="39"/>
     </row>
     <row r="159" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C159" s="332"/>
-      <c r="D159" s="332"/>
-      <c r="E159" s="332"/>
-      <c r="F159" s="332"/>
-      <c r="G159" s="332"/>
-      <c r="H159" s="332"/>
-      <c r="J159" s="330"/>
-      <c r="K159" s="330"/>
-      <c r="L159" s="330"/>
-      <c r="M159" s="330"/>
-      <c r="N159" s="330"/>
+      <c r="C159" s="333"/>
+      <c r="D159" s="333"/>
+      <c r="E159" s="333"/>
+      <c r="F159" s="333"/>
+      <c r="G159" s="333"/>
+      <c r="H159" s="333"/>
+      <c r="J159" s="331"/>
+      <c r="K159" s="331"/>
+      <c r="L159" s="331"/>
+      <c r="M159" s="331"/>
+      <c r="N159" s="331"/>
       <c r="O159" s="39"/>
     </row>
     <row r="160" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C160" s="332"/>
-      <c r="D160" s="332"/>
-      <c r="E160" s="332"/>
-      <c r="F160" s="332"/>
-      <c r="G160" s="332"/>
-      <c r="H160" s="332"/>
-      <c r="J160" s="330"/>
-      <c r="K160" s="330"/>
-      <c r="L160" s="330"/>
-      <c r="M160" s="330"/>
-      <c r="N160" s="330"/>
+      <c r="C160" s="333"/>
+      <c r="D160" s="333"/>
+      <c r="E160" s="333"/>
+      <c r="F160" s="333"/>
+      <c r="G160" s="333"/>
+      <c r="H160" s="333"/>
+      <c r="J160" s="331"/>
+      <c r="K160" s="331"/>
+      <c r="L160" s="331"/>
+      <c r="M160" s="331"/>
+      <c r="N160" s="331"/>
       <c r="O160" s="39"/>
     </row>
     <row r="161" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C161" s="332"/>
-      <c r="D161" s="332"/>
-      <c r="E161" s="332"/>
-      <c r="F161" s="332"/>
-      <c r="G161" s="332"/>
-      <c r="H161" s="332"/>
-      <c r="J161" s="330"/>
-      <c r="K161" s="330"/>
-      <c r="L161" s="330"/>
-      <c r="M161" s="330"/>
-      <c r="N161" s="330"/>
+      <c r="C161" s="333"/>
+      <c r="D161" s="333"/>
+      <c r="E161" s="333"/>
+      <c r="F161" s="333"/>
+      <c r="G161" s="333"/>
+      <c r="H161" s="333"/>
+      <c r="J161" s="331"/>
+      <c r="K161" s="331"/>
+      <c r="L161" s="331"/>
+      <c r="M161" s="331"/>
+      <c r="N161" s="331"/>
       <c r="O161" s="39"/>
     </row>
     <row r="162" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C162" s="332"/>
-      <c r="D162" s="332"/>
-      <c r="E162" s="332"/>
-      <c r="F162" s="332"/>
-      <c r="G162" s="332"/>
-      <c r="H162" s="332"/>
-      <c r="J162" s="330"/>
-      <c r="K162" s="330"/>
-      <c r="L162" s="330"/>
-      <c r="M162" s="330"/>
-      <c r="N162" s="330"/>
+      <c r="C162" s="333"/>
+      <c r="D162" s="333"/>
+      <c r="E162" s="333"/>
+      <c r="F162" s="333"/>
+      <c r="G162" s="333"/>
+      <c r="H162" s="333"/>
+      <c r="J162" s="331"/>
+      <c r="K162" s="331"/>
+      <c r="L162" s="331"/>
+      <c r="M162" s="331"/>
+      <c r="N162" s="331"/>
       <c r="O162" s="39"/>
     </row>
     <row r="163" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C163" s="332"/>
-      <c r="D163" s="332"/>
-      <c r="E163" s="332"/>
-      <c r="F163" s="332"/>
-      <c r="G163" s="332"/>
-      <c r="H163" s="332"/>
-      <c r="J163" s="330"/>
-      <c r="K163" s="330"/>
-      <c r="L163" s="330"/>
-      <c r="M163" s="330"/>
-      <c r="N163" s="330"/>
+      <c r="C163" s="333"/>
+      <c r="D163" s="333"/>
+      <c r="E163" s="333"/>
+      <c r="F163" s="333"/>
+      <c r="G163" s="333"/>
+      <c r="H163" s="333"/>
+      <c r="J163" s="331"/>
+      <c r="K163" s="331"/>
+      <c r="L163" s="331"/>
+      <c r="M163" s="331"/>
+      <c r="N163" s="331"/>
       <c r="O163" s="39"/>
     </row>
     <row r="164" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C164" s="332"/>
-      <c r="D164" s="332"/>
-      <c r="E164" s="332"/>
-      <c r="F164" s="332"/>
-      <c r="G164" s="332"/>
-      <c r="H164" s="332"/>
-      <c r="J164" s="330"/>
-      <c r="K164" s="330"/>
-      <c r="L164" s="330"/>
-      <c r="M164" s="330"/>
-      <c r="N164" s="330"/>
+      <c r="C164" s="333"/>
+      <c r="D164" s="333"/>
+      <c r="E164" s="333"/>
+      <c r="F164" s="333"/>
+      <c r="G164" s="333"/>
+      <c r="H164" s="333"/>
+      <c r="J164" s="331"/>
+      <c r="K164" s="331"/>
+      <c r="L164" s="331"/>
+      <c r="M164" s="331"/>
+      <c r="N164" s="331"/>
       <c r="O164" s="39"/>
     </row>
     <row r="165" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C165" s="332"/>
-      <c r="D165" s="332"/>
-      <c r="E165" s="332"/>
-      <c r="F165" s="332"/>
-      <c r="G165" s="332"/>
-      <c r="H165" s="332"/>
-      <c r="J165" s="330"/>
-      <c r="K165" s="330"/>
-      <c r="L165" s="330"/>
-      <c r="M165" s="330"/>
-      <c r="N165" s="330"/>
+      <c r="C165" s="333"/>
+      <c r="D165" s="333"/>
+      <c r="E165" s="333"/>
+      <c r="F165" s="333"/>
+      <c r="G165" s="333"/>
+      <c r="H165" s="333"/>
+      <c r="J165" s="331"/>
+      <c r="K165" s="331"/>
+      <c r="L165" s="331"/>
+      <c r="M165" s="331"/>
+      <c r="N165" s="331"/>
       <c r="O165" s="39"/>
     </row>
     <row r="166" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C166" s="332"/>
-      <c r="D166" s="332"/>
-      <c r="E166" s="332"/>
-      <c r="F166" s="332"/>
-      <c r="G166" s="332"/>
-      <c r="H166" s="332"/>
-      <c r="J166" s="330"/>
-      <c r="K166" s="330"/>
-      <c r="L166" s="330"/>
-      <c r="M166" s="330"/>
-      <c r="N166" s="330"/>
+      <c r="C166" s="333"/>
+      <c r="D166" s="333"/>
+      <c r="E166" s="333"/>
+      <c r="F166" s="333"/>
+      <c r="G166" s="333"/>
+      <c r="H166" s="333"/>
+      <c r="J166" s="331"/>
+      <c r="K166" s="331"/>
+      <c r="L166" s="331"/>
+      <c r="M166" s="331"/>
+      <c r="N166" s="331"/>
       <c r="O166" s="39"/>
     </row>
     <row r="167" spans="3:15" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C167" s="332"/>
-      <c r="D167" s="332"/>
-      <c r="E167" s="332"/>
-      <c r="F167" s="332"/>
-      <c r="G167" s="332"/>
-      <c r="H167" s="332"/>
-      <c r="J167" s="330"/>
-      <c r="K167" s="330"/>
-      <c r="L167" s="330"/>
-      <c r="M167" s="330"/>
-      <c r="N167" s="330"/>
+      <c r="C167" s="333"/>
+      <c r="D167" s="333"/>
+      <c r="E167" s="333"/>
+      <c r="F167" s="333"/>
+      <c r="G167" s="333"/>
+      <c r="H167" s="333"/>
+      <c r="J167" s="331"/>
+      <c r="K167" s="331"/>
+      <c r="L167" s="331"/>
+      <c r="M167" s="331"/>
+      <c r="N167" s="331"/>
       <c r="O167" s="39"/>
     </row>
     <row r="168" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C168" s="332"/>
-      <c r="D168" s="332"/>
-      <c r="E168" s="332"/>
-      <c r="F168" s="332"/>
-      <c r="G168" s="332"/>
-      <c r="H168" s="332"/>
-      <c r="J168" s="330"/>
-      <c r="K168" s="330"/>
-      <c r="L168" s="330"/>
-      <c r="M168" s="330"/>
-      <c r="N168" s="330"/>
+      <c r="C168" s="333"/>
+      <c r="D168" s="333"/>
+      <c r="E168" s="333"/>
+      <c r="F168" s="333"/>
+      <c r="G168" s="333"/>
+      <c r="H168" s="333"/>
+      <c r="J168" s="331"/>
+      <c r="K168" s="331"/>
+      <c r="L168" s="331"/>
+      <c r="M168" s="331"/>
+      <c r="N168" s="331"/>
       <c r="O168" s="39"/>
     </row>
     <row r="169" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C169" s="332"/>
-      <c r="D169" s="332"/>
-      <c r="E169" s="332"/>
-      <c r="F169" s="332"/>
-      <c r="G169" s="332"/>
-      <c r="H169" s="332"/>
-      <c r="J169" s="330"/>
-      <c r="K169" s="330"/>
-      <c r="L169" s="330"/>
-      <c r="M169" s="330"/>
-      <c r="N169" s="330"/>
+      <c r="C169" s="333"/>
+      <c r="D169" s="333"/>
+      <c r="E169" s="333"/>
+      <c r="F169" s="333"/>
+      <c r="G169" s="333"/>
+      <c r="H169" s="333"/>
+      <c r="J169" s="331"/>
+      <c r="K169" s="331"/>
+      <c r="L169" s="331"/>
+      <c r="M169" s="331"/>
+      <c r="N169" s="331"/>
       <c r="O169" s="39"/>
     </row>
     <row r="170" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C170" s="332"/>
-      <c r="D170" s="332"/>
-      <c r="E170" s="332"/>
-      <c r="F170" s="332"/>
-      <c r="G170" s="332"/>
-      <c r="H170" s="332"/>
-      <c r="J170" s="330"/>
-      <c r="K170" s="330"/>
-      <c r="L170" s="330"/>
-      <c r="M170" s="330"/>
-      <c r="N170" s="330"/>
+      <c r="C170" s="333"/>
+      <c r="D170" s="333"/>
+      <c r="E170" s="333"/>
+      <c r="F170" s="333"/>
+      <c r="G170" s="333"/>
+      <c r="H170" s="333"/>
+      <c r="J170" s="331"/>
+      <c r="K170" s="331"/>
+      <c r="L170" s="331"/>
+      <c r="M170" s="331"/>
+      <c r="N170" s="331"/>
       <c r="O170" s="39"/>
     </row>
     <row r="171" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C171" s="332"/>
-      <c r="D171" s="332"/>
-      <c r="E171" s="332"/>
-      <c r="F171" s="332"/>
-      <c r="G171" s="332"/>
-      <c r="H171" s="332"/>
-      <c r="J171" s="330"/>
-      <c r="K171" s="330"/>
-      <c r="L171" s="330"/>
-      <c r="M171" s="330"/>
-      <c r="N171" s="330"/>
+      <c r="C171" s="333"/>
+      <c r="D171" s="333"/>
+      <c r="E171" s="333"/>
+      <c r="F171" s="333"/>
+      <c r="G171" s="333"/>
+      <c r="H171" s="333"/>
+      <c r="J171" s="331"/>
+      <c r="K171" s="331"/>
+      <c r="L171" s="331"/>
+      <c r="M171" s="331"/>
+      <c r="N171" s="331"/>
       <c r="O171" s="39"/>
     </row>
     <row r="172" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C172" s="332"/>
-      <c r="D172" s="332"/>
-      <c r="E172" s="332"/>
-      <c r="F172" s="332"/>
-      <c r="G172" s="332"/>
-      <c r="H172" s="332"/>
-      <c r="J172" s="330"/>
-      <c r="K172" s="330"/>
-      <c r="L172" s="330"/>
-      <c r="M172" s="330"/>
-      <c r="N172" s="330"/>
+      <c r="C172" s="333"/>
+      <c r="D172" s="333"/>
+      <c r="E172" s="333"/>
+      <c r="F172" s="333"/>
+      <c r="G172" s="333"/>
+      <c r="H172" s="333"/>
+      <c r="J172" s="331"/>
+      <c r="K172" s="331"/>
+      <c r="L172" s="331"/>
+      <c r="M172" s="331"/>
+      <c r="N172" s="331"/>
       <c r="O172" s="39"/>
     </row>
     <row r="173" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C173" s="332"/>
-      <c r="D173" s="332"/>
-      <c r="E173" s="332"/>
-      <c r="F173" s="332"/>
-      <c r="G173" s="332"/>
-      <c r="H173" s="332"/>
-      <c r="J173" s="330"/>
-      <c r="K173" s="330"/>
-      <c r="L173" s="330"/>
-      <c r="M173" s="330"/>
-      <c r="N173" s="330"/>
+      <c r="C173" s="333"/>
+      <c r="D173" s="333"/>
+      <c r="E173" s="333"/>
+      <c r="F173" s="333"/>
+      <c r="G173" s="333"/>
+      <c r="H173" s="333"/>
+      <c r="J173" s="331"/>
+      <c r="K173" s="331"/>
+      <c r="L173" s="331"/>
+      <c r="M173" s="331"/>
+      <c r="N173" s="331"/>
       <c r="O173" s="39"/>
     </row>
     <row r="174" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C174" s="332"/>
-      <c r="D174" s="332"/>
-      <c r="E174" s="332"/>
-      <c r="F174" s="332"/>
-      <c r="G174" s="332"/>
-      <c r="H174" s="332"/>
-      <c r="J174" s="330"/>
-      <c r="K174" s="330"/>
-      <c r="L174" s="330"/>
-      <c r="M174" s="330"/>
-      <c r="N174" s="330"/>
+      <c r="C174" s="333"/>
+      <c r="D174" s="333"/>
+      <c r="E174" s="333"/>
+      <c r="F174" s="333"/>
+      <c r="G174" s="333"/>
+      <c r="H174" s="333"/>
+      <c r="J174" s="331"/>
+      <c r="K174" s="331"/>
+      <c r="L174" s="331"/>
+      <c r="M174" s="331"/>
+      <c r="N174" s="331"/>
       <c r="O174" s="39"/>
     </row>
     <row r="175" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C175" s="332"/>
-      <c r="D175" s="332"/>
-      <c r="E175" s="332"/>
-      <c r="F175" s="332"/>
-      <c r="G175" s="332"/>
-      <c r="H175" s="332"/>
-      <c r="J175" s="330"/>
-      <c r="K175" s="330"/>
-      <c r="L175" s="330"/>
-      <c r="M175" s="330"/>
-      <c r="N175" s="330"/>
+      <c r="C175" s="333"/>
+      <c r="D175" s="333"/>
+      <c r="E175" s="333"/>
+      <c r="F175" s="333"/>
+      <c r="G175" s="333"/>
+      <c r="H175" s="333"/>
+      <c r="J175" s="331"/>
+      <c r="K175" s="331"/>
+      <c r="L175" s="331"/>
+      <c r="M175" s="331"/>
+      <c r="N175" s="331"/>
       <c r="O175" s="39"/>
     </row>
     <row r="176" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C176" s="332"/>
-      <c r="D176" s="332"/>
-      <c r="E176" s="332"/>
-      <c r="F176" s="332"/>
-      <c r="G176" s="332"/>
-      <c r="H176" s="332"/>
-      <c r="J176" s="330"/>
-      <c r="K176" s="330"/>
-      <c r="L176" s="330"/>
-      <c r="M176" s="330"/>
-      <c r="N176" s="330"/>
+      <c r="C176" s="333"/>
+      <c r="D176" s="333"/>
+      <c r="E176" s="333"/>
+      <c r="F176" s="333"/>
+      <c r="G176" s="333"/>
+      <c r="H176" s="333"/>
+      <c r="J176" s="331"/>
+      <c r="K176" s="331"/>
+      <c r="L176" s="331"/>
+      <c r="M176" s="331"/>
+      <c r="N176" s="331"/>
       <c r="O176" s="39"/>
     </row>
     <row r="177" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C177" s="332"/>
-      <c r="D177" s="332"/>
-      <c r="E177" s="332"/>
-      <c r="F177" s="332"/>
-      <c r="G177" s="332"/>
-      <c r="H177" s="332"/>
-      <c r="J177" s="330"/>
-      <c r="K177" s="330"/>
-      <c r="L177" s="330"/>
-      <c r="M177" s="330"/>
-      <c r="N177" s="330"/>
+      <c r="C177" s="333"/>
+      <c r="D177" s="333"/>
+      <c r="E177" s="333"/>
+      <c r="F177" s="333"/>
+      <c r="G177" s="333"/>
+      <c r="H177" s="333"/>
+      <c r="J177" s="331"/>
+      <c r="K177" s="331"/>
+      <c r="L177" s="331"/>
+      <c r="M177" s="331"/>
+      <c r="N177" s="331"/>
       <c r="O177" s="39"/>
     </row>
     <row r="178" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C178" s="332"/>
-      <c r="D178" s="332"/>
-      <c r="E178" s="332"/>
-      <c r="F178" s="332"/>
-      <c r="G178" s="332"/>
-      <c r="H178" s="332"/>
-      <c r="J178" s="330"/>
-      <c r="K178" s="330"/>
-      <c r="L178" s="330"/>
-      <c r="M178" s="330"/>
-      <c r="N178" s="330"/>
+      <c r="C178" s="333"/>
+      <c r="D178" s="333"/>
+      <c r="E178" s="333"/>
+      <c r="F178" s="333"/>
+      <c r="G178" s="333"/>
+      <c r="H178" s="333"/>
+      <c r="J178" s="331"/>
+      <c r="K178" s="331"/>
+      <c r="L178" s="331"/>
+      <c r="M178" s="331"/>
+      <c r="N178" s="331"/>
       <c r="O178" s="39"/>
     </row>
     <row r="179" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C179" s="332"/>
-      <c r="D179" s="332"/>
-      <c r="E179" s="332"/>
-      <c r="F179" s="332"/>
-      <c r="G179" s="332"/>
-      <c r="H179" s="332"/>
-      <c r="J179" s="330"/>
-      <c r="K179" s="330"/>
-      <c r="L179" s="330"/>
-      <c r="M179" s="330"/>
-      <c r="N179" s="330"/>
+      <c r="C179" s="333"/>
+      <c r="D179" s="333"/>
+      <c r="E179" s="333"/>
+      <c r="F179" s="333"/>
+      <c r="G179" s="333"/>
+      <c r="H179" s="333"/>
+      <c r="J179" s="331"/>
+      <c r="K179" s="331"/>
+      <c r="L179" s="331"/>
+      <c r="M179" s="331"/>
+      <c r="N179" s="331"/>
       <c r="O179" s="39"/>
     </row>
     <row r="180" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C180" s="332"/>
-      <c r="D180" s="332"/>
-      <c r="E180" s="332"/>
-      <c r="F180" s="332"/>
-      <c r="G180" s="332"/>
-      <c r="H180" s="332"/>
-      <c r="J180" s="330"/>
-      <c r="K180" s="330"/>
-      <c r="L180" s="330"/>
-      <c r="M180" s="330"/>
-      <c r="N180" s="330"/>
+      <c r="C180" s="333"/>
+      <c r="D180" s="333"/>
+      <c r="E180" s="333"/>
+      <c r="F180" s="333"/>
+      <c r="G180" s="333"/>
+      <c r="H180" s="333"/>
+      <c r="J180" s="331"/>
+      <c r="K180" s="331"/>
+      <c r="L180" s="331"/>
+      <c r="M180" s="331"/>
+      <c r="N180" s="331"/>
       <c r="O180" s="39"/>
     </row>
     <row r="181" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C181" s="332"/>
-      <c r="D181" s="332"/>
-      <c r="E181" s="332"/>
-      <c r="F181" s="332"/>
-      <c r="G181" s="332"/>
-      <c r="H181" s="332"/>
-      <c r="J181" s="330"/>
-      <c r="K181" s="330"/>
-      <c r="L181" s="330"/>
-      <c r="M181" s="330"/>
-      <c r="N181" s="330"/>
+      <c r="C181" s="333"/>
+      <c r="D181" s="333"/>
+      <c r="E181" s="333"/>
+      <c r="F181" s="333"/>
+      <c r="G181" s="333"/>
+      <c r="H181" s="333"/>
+      <c r="J181" s="331"/>
+      <c r="K181" s="331"/>
+      <c r="L181" s="331"/>
+      <c r="M181" s="331"/>
+      <c r="N181" s="331"/>
       <c r="O181" s="39"/>
     </row>
     <row r="182" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C182" s="332"/>
-      <c r="D182" s="332"/>
-      <c r="E182" s="332"/>
-      <c r="F182" s="332"/>
-      <c r="G182" s="332"/>
-      <c r="H182" s="332"/>
-      <c r="J182" s="330"/>
-      <c r="K182" s="330"/>
-      <c r="L182" s="330"/>
-      <c r="M182" s="330"/>
-      <c r="N182" s="330"/>
+      <c r="C182" s="333"/>
+      <c r="D182" s="333"/>
+      <c r="E182" s="333"/>
+      <c r="F182" s="333"/>
+      <c r="G182" s="333"/>
+      <c r="H182" s="333"/>
+      <c r="J182" s="331"/>
+      <c r="K182" s="331"/>
+      <c r="L182" s="331"/>
+      <c r="M182" s="331"/>
+      <c r="N182" s="331"/>
       <c r="O182" s="39"/>
     </row>
     <row r="183" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C183" s="332"/>
-      <c r="D183" s="332"/>
-      <c r="E183" s="332"/>
-      <c r="F183" s="332"/>
-      <c r="G183" s="332"/>
-      <c r="H183" s="332"/>
-      <c r="J183" s="330"/>
-      <c r="K183" s="330"/>
-      <c r="L183" s="330"/>
-      <c r="M183" s="330"/>
-      <c r="N183" s="330"/>
+      <c r="C183" s="333"/>
+      <c r="D183" s="333"/>
+      <c r="E183" s="333"/>
+      <c r="F183" s="333"/>
+      <c r="G183" s="333"/>
+      <c r="H183" s="333"/>
+      <c r="J183" s="331"/>
+      <c r="K183" s="331"/>
+      <c r="L183" s="331"/>
+      <c r="M183" s="331"/>
+      <c r="N183" s="331"/>
       <c r="O183" s="39"/>
     </row>
     <row r="184" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C184" s="332"/>
-      <c r="D184" s="332"/>
-      <c r="E184" s="332"/>
-      <c r="F184" s="332"/>
-      <c r="G184" s="332"/>
-      <c r="H184" s="332"/>
-      <c r="J184" s="330"/>
-      <c r="K184" s="330"/>
-      <c r="L184" s="330"/>
-      <c r="M184" s="330"/>
-      <c r="N184" s="330"/>
+      <c r="C184" s="333"/>
+      <c r="D184" s="333"/>
+      <c r="E184" s="333"/>
+      <c r="F184" s="333"/>
+      <c r="G184" s="333"/>
+      <c r="H184" s="333"/>
+      <c r="J184" s="331"/>
+      <c r="K184" s="331"/>
+      <c r="L184" s="331"/>
+      <c r="M184" s="331"/>
+      <c r="N184" s="331"/>
       <c r="O184" s="39"/>
     </row>
     <row r="185" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C185" s="332"/>
-      <c r="D185" s="332"/>
-      <c r="E185" s="332"/>
-      <c r="F185" s="332"/>
-      <c r="G185" s="332"/>
-      <c r="H185" s="332"/>
-      <c r="J185" s="330"/>
-      <c r="K185" s="330"/>
-      <c r="L185" s="330"/>
-      <c r="M185" s="330"/>
-      <c r="N185" s="330"/>
+      <c r="C185" s="333"/>
+      <c r="D185" s="333"/>
+      <c r="E185" s="333"/>
+      <c r="F185" s="333"/>
+      <c r="G185" s="333"/>
+      <c r="H185" s="333"/>
+      <c r="J185" s="331"/>
+      <c r="K185" s="331"/>
+      <c r="L185" s="331"/>
+      <c r="M185" s="331"/>
+      <c r="N185" s="331"/>
       <c r="O185" s="39"/>
     </row>
     <row r="186" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C186" s="332"/>
-      <c r="D186" s="332"/>
-      <c r="E186" s="332"/>
-      <c r="F186" s="332"/>
-      <c r="G186" s="332"/>
-      <c r="H186" s="332"/>
-      <c r="J186" s="330"/>
-      <c r="K186" s="330"/>
-      <c r="L186" s="330"/>
-      <c r="M186" s="330"/>
-      <c r="N186" s="330"/>
+      <c r="C186" s="333"/>
+      <c r="D186" s="333"/>
+      <c r="E186" s="333"/>
+      <c r="F186" s="333"/>
+      <c r="G186" s="333"/>
+      <c r="H186" s="333"/>
+      <c r="J186" s="331"/>
+      <c r="K186" s="331"/>
+      <c r="L186" s="331"/>
+      <c r="M186" s="331"/>
+      <c r="N186" s="331"/>
       <c r="O186" s="39"/>
     </row>
     <row r="187" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C187" s="332"/>
-      <c r="D187" s="332"/>
-      <c r="E187" s="332"/>
-      <c r="F187" s="332"/>
-      <c r="G187" s="332"/>
-      <c r="H187" s="332"/>
-      <c r="J187" s="330"/>
-      <c r="K187" s="330"/>
-      <c r="L187" s="330"/>
-      <c r="M187" s="330"/>
-      <c r="N187" s="330"/>
+      <c r="C187" s="333"/>
+      <c r="D187" s="333"/>
+      <c r="E187" s="333"/>
+      <c r="F187" s="333"/>
+      <c r="G187" s="333"/>
+      <c r="H187" s="333"/>
+      <c r="J187" s="331"/>
+      <c r="K187" s="331"/>
+      <c r="L187" s="331"/>
+      <c r="M187" s="331"/>
+      <c r="N187" s="331"/>
       <c r="O187" s="39"/>
     </row>
     <row r="188" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C188" s="332"/>
-      <c r="D188" s="332"/>
-      <c r="E188" s="332"/>
-      <c r="F188" s="332"/>
-      <c r="G188" s="332"/>
-      <c r="H188" s="332"/>
-      <c r="J188" s="330"/>
-      <c r="K188" s="330"/>
-      <c r="L188" s="330"/>
-      <c r="M188" s="330"/>
-      <c r="N188" s="330"/>
+      <c r="C188" s="333"/>
+      <c r="D188" s="333"/>
+      <c r="E188" s="333"/>
+      <c r="F188" s="333"/>
+      <c r="G188" s="333"/>
+      <c r="H188" s="333"/>
+      <c r="J188" s="331"/>
+      <c r="K188" s="331"/>
+      <c r="L188" s="331"/>
+      <c r="M188" s="331"/>
+      <c r="N188" s="331"/>
       <c r="O188" s="39"/>
     </row>
     <row r="189" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C189" s="332"/>
-      <c r="D189" s="332"/>
-      <c r="E189" s="332"/>
-      <c r="F189" s="332"/>
-      <c r="G189" s="332"/>
-      <c r="H189" s="332"/>
-      <c r="J189" s="330"/>
-      <c r="K189" s="330"/>
-      <c r="L189" s="330"/>
-      <c r="M189" s="330"/>
-      <c r="N189" s="330"/>
+      <c r="C189" s="333"/>
+      <c r="D189" s="333"/>
+      <c r="E189" s="333"/>
+      <c r="F189" s="333"/>
+      <c r="G189" s="333"/>
+      <c r="H189" s="333"/>
+      <c r="J189" s="331"/>
+      <c r="K189" s="331"/>
+      <c r="L189" s="331"/>
+      <c r="M189" s="331"/>
+      <c r="N189" s="331"/>
       <c r="O189" s="39"/>
     </row>
     <row r="190" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C190" s="332"/>
-      <c r="D190" s="332"/>
-      <c r="E190" s="332"/>
-      <c r="F190" s="332"/>
-      <c r="G190" s="332"/>
-      <c r="H190" s="332"/>
-      <c r="J190" s="330"/>
-      <c r="K190" s="330"/>
-      <c r="L190" s="330"/>
-      <c r="M190" s="330"/>
-      <c r="N190" s="330"/>
+      <c r="C190" s="333"/>
+      <c r="D190" s="333"/>
+      <c r="E190" s="333"/>
+      <c r="F190" s="333"/>
+      <c r="G190" s="333"/>
+      <c r="H190" s="333"/>
+      <c r="J190" s="331"/>
+      <c r="K190" s="331"/>
+      <c r="L190" s="331"/>
+      <c r="M190" s="331"/>
+      <c r="N190" s="331"/>
       <c r="O190" s="39"/>
     </row>
     <row r="191" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C191" s="332"/>
-      <c r="D191" s="332"/>
-      <c r="E191" s="332"/>
-      <c r="F191" s="332"/>
-      <c r="G191" s="332"/>
-      <c r="H191" s="332"/>
-      <c r="J191" s="330"/>
-      <c r="K191" s="330"/>
-      <c r="L191" s="330"/>
-      <c r="M191" s="330"/>
-      <c r="N191" s="330"/>
+      <c r="C191" s="333"/>
+      <c r="D191" s="333"/>
+      <c r="E191" s="333"/>
+      <c r="F191" s="333"/>
+      <c r="G191" s="333"/>
+      <c r="H191" s="333"/>
+      <c r="J191" s="331"/>
+      <c r="K191" s="331"/>
+      <c r="L191" s="331"/>
+      <c r="M191" s="331"/>
+      <c r="N191" s="331"/>
       <c r="O191" s="39"/>
     </row>
     <row r="192" spans="3:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="J192" s="330"/>
-      <c r="K192" s="330"/>
-      <c r="L192" s="330"/>
-      <c r="M192" s="330"/>
-      <c r="N192" s="330"/>
+      <c r="J192" s="331"/>
+      <c r="K192" s="331"/>
+      <c r="L192" s="331"/>
+      <c r="M192" s="331"/>
+      <c r="N192" s="331"/>
       <c r="O192" s="39"/>
     </row>
   </sheetData>
@@ -9244,204 +9245,204 @@
   <sheetData>
     <row r="1" spans="1:31" ht="21.75" x14ac:dyDescent="0.25">
       <c r="A1" s="211"/>
-      <c r="B1" s="562" t="s">
+      <c r="B1" s="563" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="562"/>
-      <c r="D1" s="562"/>
-      <c r="E1" s="562"/>
-      <c r="F1" s="562"/>
-      <c r="G1" s="562"/>
-      <c r="H1" s="562"/>
-      <c r="I1" s="562"/>
-      <c r="J1" s="562"/>
-      <c r="K1" s="562"/>
-      <c r="L1" s="562"/>
-      <c r="M1" s="562"/>
-      <c r="N1" s="562"/>
-      <c r="O1" s="562"/>
-      <c r="P1" s="562"/>
-      <c r="Q1" s="562"/>
-      <c r="R1" s="562"/>
-      <c r="S1" s="562"/>
-      <c r="T1" s="562"/>
-      <c r="U1" s="562"/>
-      <c r="V1" s="562"/>
-      <c r="W1" s="562"/>
-      <c r="X1" s="562"/>
+      <c r="C1" s="563"/>
+      <c r="D1" s="563"/>
+      <c r="E1" s="563"/>
+      <c r="F1" s="563"/>
+      <c r="G1" s="563"/>
+      <c r="H1" s="563"/>
+      <c r="I1" s="563"/>
+      <c r="J1" s="563"/>
+      <c r="K1" s="563"/>
+      <c r="L1" s="563"/>
+      <c r="M1" s="563"/>
+      <c r="N1" s="563"/>
+      <c r="O1" s="563"/>
+      <c r="P1" s="563"/>
+      <c r="Q1" s="563"/>
+      <c r="R1" s="563"/>
+      <c r="S1" s="563"/>
+      <c r="T1" s="563"/>
+      <c r="U1" s="563"/>
+      <c r="V1" s="563"/>
+      <c r="W1" s="563"/>
+      <c r="X1" s="563"/>
       <c r="Y1" s="212"/>
       <c r="Z1" s="212"/>
       <c r="AA1" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="563" t="s">
+      <c r="AB1" s="564" t="s">
         <v>247</v>
       </c>
-      <c r="AC1" s="563"/>
-      <c r="AD1" s="563"/>
-      <c r="AE1" s="563"/>
+      <c r="AC1" s="564"/>
+      <c r="AD1" s="564"/>
+      <c r="AE1" s="564"/>
     </row>
     <row r="2" spans="1:31" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="551" t="s">
+      <c r="A2" s="552" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="565" t="s">
+      <c r="B2" s="566" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="566"/>
-      <c r="D2" s="566"/>
-      <c r="E2" s="566"/>
-      <c r="F2" s="566"/>
-      <c r="G2" s="566"/>
-      <c r="H2" s="566"/>
-      <c r="I2" s="566"/>
-      <c r="J2" s="566"/>
-      <c r="K2" s="566"/>
-      <c r="L2" s="566"/>
-      <c r="M2" s="566"/>
-      <c r="N2" s="566"/>
-      <c r="O2" s="566"/>
-      <c r="P2" s="566"/>
-      <c r="Q2" s="566"/>
-      <c r="R2" s="566"/>
-      <c r="S2" s="566"/>
-      <c r="T2" s="566"/>
-      <c r="U2" s="566"/>
-      <c r="V2" s="566"/>
-      <c r="W2" s="567"/>
-      <c r="X2" s="568"/>
-      <c r="Y2" s="569"/>
-      <c r="Z2" s="569"/>
-      <c r="AA2" s="569"/>
-      <c r="AB2" s="569"/>
-      <c r="AC2" s="569"/>
-      <c r="AD2" s="570"/>
-      <c r="AE2" s="571" t="s">
+      <c r="C2" s="567"/>
+      <c r="D2" s="567"/>
+      <c r="E2" s="567"/>
+      <c r="F2" s="567"/>
+      <c r="G2" s="567"/>
+      <c r="H2" s="567"/>
+      <c r="I2" s="567"/>
+      <c r="J2" s="567"/>
+      <c r="K2" s="567"/>
+      <c r="L2" s="567"/>
+      <c r="M2" s="567"/>
+      <c r="N2" s="567"/>
+      <c r="O2" s="567"/>
+      <c r="P2" s="567"/>
+      <c r="Q2" s="567"/>
+      <c r="R2" s="567"/>
+      <c r="S2" s="567"/>
+      <c r="T2" s="567"/>
+      <c r="U2" s="567"/>
+      <c r="V2" s="567"/>
+      <c r="W2" s="568"/>
+      <c r="X2" s="569"/>
+      <c r="Y2" s="570"/>
+      <c r="Z2" s="570"/>
+      <c r="AA2" s="570"/>
+      <c r="AB2" s="570"/>
+      <c r="AC2" s="570"/>
+      <c r="AD2" s="571"/>
+      <c r="AE2" s="572" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="564"/>
-      <c r="B3" s="548" t="s">
+      <c r="A3" s="565"/>
+      <c r="B3" s="549" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="550"/>
-      <c r="D3" s="549"/>
-      <c r="E3" s="548" t="s">
+      <c r="C3" s="551"/>
+      <c r="D3" s="550"/>
+      <c r="E3" s="549" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="550"/>
-      <c r="G3" s="550"/>
-      <c r="H3" s="550"/>
-      <c r="I3" s="550"/>
-      <c r="J3" s="550"/>
-      <c r="K3" s="550"/>
-      <c r="L3" s="550"/>
-      <c r="M3" s="550"/>
-      <c r="N3" s="550"/>
-      <c r="O3" s="550"/>
-      <c r="P3" s="550"/>
-      <c r="Q3" s="550"/>
-      <c r="R3" s="549"/>
+      <c r="F3" s="551"/>
+      <c r="G3" s="551"/>
+      <c r="H3" s="551"/>
+      <c r="I3" s="551"/>
+      <c r="J3" s="551"/>
+      <c r="K3" s="551"/>
+      <c r="L3" s="551"/>
+      <c r="M3" s="551"/>
+      <c r="N3" s="551"/>
+      <c r="O3" s="551"/>
+      <c r="P3" s="551"/>
+      <c r="Q3" s="551"/>
+      <c r="R3" s="550"/>
       <c r="S3" s="225"/>
       <c r="T3" s="225"/>
-      <c r="U3" s="574" t="s">
+      <c r="U3" s="575" t="s">
         <v>62</v>
       </c>
-      <c r="V3" s="575"/>
-      <c r="W3" s="576"/>
-      <c r="X3" s="583" t="s">
+      <c r="V3" s="576"/>
+      <c r="W3" s="577"/>
+      <c r="X3" s="584" t="s">
         <v>64</v>
       </c>
-      <c r="Y3" s="584"/>
-      <c r="Z3" s="584"/>
-      <c r="AA3" s="585"/>
-      <c r="AB3" s="583" t="s">
+      <c r="Y3" s="585"/>
+      <c r="Z3" s="585"/>
+      <c r="AA3" s="586"/>
+      <c r="AB3" s="584" t="s">
         <v>65</v>
       </c>
-      <c r="AC3" s="584"/>
-      <c r="AD3" s="585"/>
-      <c r="AE3" s="572"/>
+      <c r="AC3" s="585"/>
+      <c r="AD3" s="586"/>
+      <c r="AE3" s="573"/>
     </row>
     <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="564"/>
-      <c r="B4" s="551" t="s">
+      <c r="A4" s="565"/>
+      <c r="B4" s="552" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="551" t="s">
+      <c r="C4" s="552" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="551" t="s">
+      <c r="D4" s="552" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="548" t="s">
+      <c r="E4" s="549" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="550"/>
-      <c r="G4" s="550"/>
-      <c r="H4" s="550"/>
-      <c r="I4" s="550"/>
-      <c r="J4" s="550"/>
-      <c r="K4" s="550"/>
-      <c r="L4" s="550"/>
-      <c r="M4" s="549"/>
-      <c r="N4" s="548"/>
-      <c r="O4" s="550"/>
-      <c r="P4" s="550"/>
-      <c r="Q4" s="550"/>
-      <c r="R4" s="549"/>
+      <c r="F4" s="551"/>
+      <c r="G4" s="551"/>
+      <c r="H4" s="551"/>
+      <c r="I4" s="551"/>
+      <c r="J4" s="551"/>
+      <c r="K4" s="551"/>
+      <c r="L4" s="551"/>
+      <c r="M4" s="550"/>
+      <c r="N4" s="549"/>
+      <c r="O4" s="551"/>
+      <c r="P4" s="551"/>
+      <c r="Q4" s="551"/>
+      <c r="R4" s="550"/>
       <c r="S4" s="226"/>
       <c r="T4" s="226"/>
-      <c r="U4" s="577"/>
-      <c r="V4" s="578"/>
-      <c r="W4" s="579"/>
-      <c r="X4" s="553" t="s">
+      <c r="U4" s="578"/>
+      <c r="V4" s="579"/>
+      <c r="W4" s="580"/>
+      <c r="X4" s="554" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="554"/>
-      <c r="Z4" s="555"/>
-      <c r="AA4" s="559" t="s">
+      <c r="Y4" s="555"/>
+      <c r="Z4" s="556"/>
+      <c r="AA4" s="560" t="s">
         <v>32</v>
       </c>
-      <c r="AB4" s="559" t="s">
+      <c r="AB4" s="560" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="559" t="s">
+      <c r="AC4" s="560" t="s">
         <v>84</v>
       </c>
-      <c r="AD4" s="559" t="s">
+      <c r="AD4" s="560" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="572"/>
+      <c r="AE4" s="573"/>
     </row>
     <row r="5" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="564"/>
-      <c r="B5" s="564"/>
-      <c r="C5" s="564"/>
-      <c r="D5" s="564"/>
-      <c r="E5" s="548" t="s">
+      <c r="A5" s="565"/>
+      <c r="B5" s="565"/>
+      <c r="C5" s="565"/>
+      <c r="D5" s="565"/>
+      <c r="E5" s="549" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="549"/>
-      <c r="G5" s="548" t="s">
+      <c r="F5" s="550"/>
+      <c r="G5" s="549" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="549"/>
-      <c r="I5" s="548" t="s">
+      <c r="H5" s="550"/>
+      <c r="I5" s="549" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="550"/>
-      <c r="K5" s="549"/>
+      <c r="J5" s="551"/>
+      <c r="K5" s="550"/>
       <c r="L5" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="551" t="s">
+      <c r="M5" s="552" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="548"/>
-      <c r="O5" s="550"/>
-      <c r="P5" s="550"/>
-      <c r="Q5" s="549"/>
+      <c r="N5" s="549"/>
+      <c r="O5" s="551"/>
+      <c r="P5" s="551"/>
+      <c r="Q5" s="550"/>
       <c r="R5" s="228" t="s">
         <v>47</v>
       </c>
@@ -9451,23 +9452,23 @@
       <c r="T5" s="228" t="s">
         <v>76</v>
       </c>
-      <c r="U5" s="580"/>
-      <c r="V5" s="581"/>
-      <c r="W5" s="582"/>
-      <c r="X5" s="556"/>
-      <c r="Y5" s="557"/>
-      <c r="Z5" s="558"/>
-      <c r="AA5" s="560"/>
-      <c r="AB5" s="560"/>
-      <c r="AC5" s="560"/>
-      <c r="AD5" s="560"/>
-      <c r="AE5" s="572"/>
+      <c r="U5" s="581"/>
+      <c r="V5" s="582"/>
+      <c r="W5" s="583"/>
+      <c r="X5" s="557"/>
+      <c r="Y5" s="558"/>
+      <c r="Z5" s="559"/>
+      <c r="AA5" s="561"/>
+      <c r="AB5" s="561"/>
+      <c r="AC5" s="561"/>
+      <c r="AD5" s="561"/>
+      <c r="AE5" s="573"/>
     </row>
     <row r="6" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="552"/>
-      <c r="B6" s="552"/>
-      <c r="C6" s="552"/>
-      <c r="D6" s="552"/>
+      <c r="A6" s="553"/>
+      <c r="B6" s="553"/>
+      <c r="C6" s="553"/>
+      <c r="D6" s="553"/>
       <c r="E6" s="228" t="s">
         <v>61</v>
       </c>
@@ -9492,7 +9493,7 @@
       <c r="L6" s="228" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="552"/>
+      <c r="M6" s="553"/>
       <c r="N6" s="228" t="s">
         <v>36</v>
       </c>
@@ -9532,11 +9533,11 @@
       <c r="Z6" s="230" t="s">
         <v>150</v>
       </c>
-      <c r="AA6" s="561"/>
-      <c r="AB6" s="561"/>
-      <c r="AC6" s="561"/>
-      <c r="AD6" s="561"/>
-      <c r="AE6" s="573"/>
+      <c r="AA6" s="562"/>
+      <c r="AB6" s="562"/>
+      <c r="AC6" s="562"/>
+      <c r="AD6" s="562"/>
+      <c r="AE6" s="574"/>
     </row>
     <row r="7" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="236">
@@ -10169,205 +10170,205 @@
       </c>
     </row>
     <row r="13" spans="1:31" ht="21.75" x14ac:dyDescent="0.15">
-      <c r="A13" s="529" t="s">
+      <c r="A13" s="530" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="529"/>
-      <c r="C13" s="529"/>
-      <c r="D13" s="529"/>
-      <c r="E13" s="529"/>
-      <c r="F13" s="529"/>
-      <c r="G13" s="529"/>
-      <c r="H13" s="529"/>
-      <c r="I13" s="529"/>
-      <c r="J13" s="529"/>
-      <c r="K13" s="529"/>
-      <c r="L13" s="529"/>
-      <c r="M13" s="529"/>
-      <c r="N13" s="529"/>
-      <c r="O13" s="529"/>
-      <c r="P13" s="529"/>
-      <c r="Q13" s="529"/>
-      <c r="R13" s="529"/>
-      <c r="S13" s="529"/>
-      <c r="T13" s="529"/>
-      <c r="U13" s="529"/>
-      <c r="V13" s="529"/>
-      <c r="W13" s="529"/>
-      <c r="X13" s="529"/>
-      <c r="Y13" s="529"/>
-      <c r="Z13" s="529"/>
-      <c r="AA13" s="529"/>
-      <c r="AB13" s="529"/>
-      <c r="AC13" s="529"/>
-      <c r="AD13" s="529"/>
-      <c r="AE13" s="529"/>
+      <c r="B13" s="530"/>
+      <c r="C13" s="530"/>
+      <c r="D13" s="530"/>
+      <c r="E13" s="530"/>
+      <c r="F13" s="530"/>
+      <c r="G13" s="530"/>
+      <c r="H13" s="530"/>
+      <c r="I13" s="530"/>
+      <c r="J13" s="530"/>
+      <c r="K13" s="530"/>
+      <c r="L13" s="530"/>
+      <c r="M13" s="530"/>
+      <c r="N13" s="530"/>
+      <c r="O13" s="530"/>
+      <c r="P13" s="530"/>
+      <c r="Q13" s="530"/>
+      <c r="R13" s="530"/>
+      <c r="S13" s="530"/>
+      <c r="T13" s="530"/>
+      <c r="U13" s="530"/>
+      <c r="V13" s="530"/>
+      <c r="W13" s="530"/>
+      <c r="X13" s="530"/>
+      <c r="Y13" s="530"/>
+      <c r="Z13" s="530"/>
+      <c r="AA13" s="530"/>
+      <c r="AB13" s="530"/>
+      <c r="AC13" s="530"/>
+      <c r="AD13" s="530"/>
+      <c r="AE13" s="530"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="517" t="s">
+      <c r="A14" s="518" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="530" t="s">
+      <c r="B14" s="531" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="531"/>
-      <c r="D14" s="531"/>
-      <c r="E14" s="531"/>
-      <c r="F14" s="531"/>
-      <c r="G14" s="531"/>
-      <c r="H14" s="531"/>
-      <c r="I14" s="531"/>
-      <c r="J14" s="531"/>
-      <c r="K14" s="531"/>
-      <c r="L14" s="531"/>
-      <c r="M14" s="531"/>
-      <c r="N14" s="531"/>
-      <c r="O14" s="531"/>
-      <c r="P14" s="531"/>
-      <c r="Q14" s="531"/>
-      <c r="R14" s="531"/>
-      <c r="S14" s="531"/>
-      <c r="T14" s="531"/>
-      <c r="U14" s="531"/>
-      <c r="V14" s="531"/>
-      <c r="W14" s="532"/>
-      <c r="X14" s="530" t="s">
+      <c r="C14" s="532"/>
+      <c r="D14" s="532"/>
+      <c r="E14" s="532"/>
+      <c r="F14" s="532"/>
+      <c r="G14" s="532"/>
+      <c r="H14" s="532"/>
+      <c r="I14" s="532"/>
+      <c r="J14" s="532"/>
+      <c r="K14" s="532"/>
+      <c r="L14" s="532"/>
+      <c r="M14" s="532"/>
+      <c r="N14" s="532"/>
+      <c r="O14" s="532"/>
+      <c r="P14" s="532"/>
+      <c r="Q14" s="532"/>
+      <c r="R14" s="532"/>
+      <c r="S14" s="532"/>
+      <c r="T14" s="532"/>
+      <c r="U14" s="532"/>
+      <c r="V14" s="532"/>
+      <c r="W14" s="533"/>
+      <c r="X14" s="531" t="s">
         <v>27</v>
       </c>
-      <c r="Y14" s="531"/>
-      <c r="Z14" s="531"/>
-      <c r="AA14" s="531"/>
-      <c r="AB14" s="531"/>
-      <c r="AC14" s="531"/>
-      <c r="AD14" s="532"/>
-      <c r="AE14" s="533" t="s">
+      <c r="Y14" s="532"/>
+      <c r="Z14" s="532"/>
+      <c r="AA14" s="532"/>
+      <c r="AB14" s="532"/>
+      <c r="AC14" s="532"/>
+      <c r="AD14" s="533"/>
+      <c r="AE14" s="534" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="518"/>
-      <c r="B15" s="530" t="s">
+      <c r="A15" s="519"/>
+      <c r="B15" s="531" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="531"/>
-      <c r="D15" s="532"/>
-      <c r="E15" s="530" t="s">
+      <c r="C15" s="532"/>
+      <c r="D15" s="533"/>
+      <c r="E15" s="531" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="531"/>
-      <c r="G15" s="531"/>
-      <c r="H15" s="531"/>
-      <c r="I15" s="531"/>
-      <c r="J15" s="531"/>
-      <c r="K15" s="531"/>
-      <c r="L15" s="531"/>
-      <c r="M15" s="531"/>
-      <c r="N15" s="531"/>
-      <c r="O15" s="531"/>
-      <c r="P15" s="531"/>
-      <c r="Q15" s="531"/>
-      <c r="R15" s="532"/>
+      <c r="F15" s="532"/>
+      <c r="G15" s="532"/>
+      <c r="H15" s="532"/>
+      <c r="I15" s="532"/>
+      <c r="J15" s="532"/>
+      <c r="K15" s="532"/>
+      <c r="L15" s="532"/>
+      <c r="M15" s="532"/>
+      <c r="N15" s="532"/>
+      <c r="O15" s="532"/>
+      <c r="P15" s="532"/>
+      <c r="Q15" s="532"/>
+      <c r="R15" s="533"/>
       <c r="S15" s="231"/>
       <c r="T15" s="231"/>
-      <c r="U15" s="536" t="s">
+      <c r="U15" s="537" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="537"/>
-      <c r="W15" s="538"/>
-      <c r="X15" s="520" t="s">
+      <c r="V15" s="538"/>
+      <c r="W15" s="539"/>
+      <c r="X15" s="521" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="522"/>
-      <c r="Z15" s="522"/>
-      <c r="AA15" s="521"/>
-      <c r="AB15" s="520" t="s">
+      <c r="Y15" s="523"/>
+      <c r="Z15" s="523"/>
+      <c r="AA15" s="522"/>
+      <c r="AB15" s="521" t="s">
         <v>65</v>
       </c>
-      <c r="AC15" s="522"/>
-      <c r="AD15" s="521"/>
-      <c r="AE15" s="534"/>
+      <c r="AC15" s="523"/>
+      <c r="AD15" s="522"/>
+      <c r="AE15" s="535"/>
     </row>
     <row r="16" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="518"/>
-      <c r="B16" s="517" t="s">
+      <c r="A16" s="519"/>
+      <c r="B16" s="518" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="517" t="s">
+      <c r="C16" s="518" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="517" t="s">
+      <c r="D16" s="518" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="545" t="s">
+      <c r="E16" s="546" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="546"/>
-      <c r="G16" s="546"/>
-      <c r="H16" s="546"/>
-      <c r="I16" s="546"/>
-      <c r="J16" s="546"/>
-      <c r="K16" s="546"/>
-      <c r="L16" s="546"/>
-      <c r="M16" s="547"/>
-      <c r="N16" s="520"/>
-      <c r="O16" s="522"/>
-      <c r="P16" s="522"/>
-      <c r="Q16" s="522"/>
-      <c r="R16" s="521"/>
+      <c r="F16" s="547"/>
+      <c r="G16" s="547"/>
+      <c r="H16" s="547"/>
+      <c r="I16" s="547"/>
+      <c r="J16" s="547"/>
+      <c r="K16" s="547"/>
+      <c r="L16" s="547"/>
+      <c r="M16" s="548"/>
+      <c r="N16" s="521"/>
+      <c r="O16" s="523"/>
+      <c r="P16" s="523"/>
+      <c r="Q16" s="523"/>
+      <c r="R16" s="522"/>
       <c r="S16" s="231"/>
       <c r="T16" s="231"/>
-      <c r="U16" s="539"/>
-      <c r="V16" s="540"/>
-      <c r="W16" s="541"/>
-      <c r="X16" s="523" t="s">
+      <c r="U16" s="540"/>
+      <c r="V16" s="541"/>
+      <c r="W16" s="542"/>
+      <c r="X16" s="524" t="s">
         <v>31</v>
       </c>
-      <c r="Y16" s="524"/>
-      <c r="Z16" s="525"/>
-      <c r="AA16" s="517" t="s">
+      <c r="Y16" s="525"/>
+      <c r="Z16" s="526"/>
+      <c r="AA16" s="518" t="s">
         <v>32</v>
       </c>
-      <c r="AB16" s="517" t="s">
+      <c r="AB16" s="518" t="s">
         <v>31</v>
       </c>
-      <c r="AC16" s="517" t="s">
+      <c r="AC16" s="518" t="s">
         <v>84</v>
       </c>
-      <c r="AD16" s="517" t="s">
+      <c r="AD16" s="518" t="s">
         <v>32</v>
       </c>
-      <c r="AE16" s="534"/>
+      <c r="AE16" s="535"/>
     </row>
     <row r="17" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="518"/>
-      <c r="B17" s="518"/>
-      <c r="C17" s="518"/>
-      <c r="D17" s="518"/>
-      <c r="E17" s="520" t="s">
+      <c r="A17" s="519"/>
+      <c r="B17" s="519"/>
+      <c r="C17" s="519"/>
+      <c r="D17" s="519"/>
+      <c r="E17" s="521" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="521"/>
-      <c r="G17" s="520" t="s">
+      <c r="F17" s="522"/>
+      <c r="G17" s="521" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="521"/>
-      <c r="I17" s="520" t="s">
+      <c r="H17" s="522"/>
+      <c r="I17" s="521" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="522"/>
-      <c r="K17" s="521"/>
+      <c r="J17" s="523"/>
+      <c r="K17" s="522"/>
       <c r="L17" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="517" t="s">
+      <c r="M17" s="518" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="520" t="s">
+      <c r="N17" s="521" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="522"/>
-      <c r="P17" s="522"/>
-      <c r="Q17" s="521"/>
+      <c r="O17" s="523"/>
+      <c r="P17" s="523"/>
+      <c r="Q17" s="522"/>
       <c r="R17" s="233" t="s">
         <v>47</v>
       </c>
@@ -10377,23 +10378,23 @@
       <c r="T17" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="U17" s="542"/>
-      <c r="V17" s="543"/>
-      <c r="W17" s="544"/>
-      <c r="X17" s="526"/>
-      <c r="Y17" s="527"/>
-      <c r="Z17" s="528"/>
-      <c r="AA17" s="518"/>
-      <c r="AB17" s="518"/>
-      <c r="AC17" s="518"/>
-      <c r="AD17" s="518"/>
-      <c r="AE17" s="534"/>
+      <c r="U17" s="543"/>
+      <c r="V17" s="544"/>
+      <c r="W17" s="545"/>
+      <c r="X17" s="527"/>
+      <c r="Y17" s="528"/>
+      <c r="Z17" s="529"/>
+      <c r="AA17" s="519"/>
+      <c r="AB17" s="519"/>
+      <c r="AC17" s="519"/>
+      <c r="AD17" s="519"/>
+      <c r="AE17" s="535"/>
     </row>
     <row r="18" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A18" s="519"/>
-      <c r="B18" s="519"/>
-      <c r="C18" s="519"/>
-      <c r="D18" s="519"/>
+      <c r="A18" s="520"/>
+      <c r="B18" s="520"/>
+      <c r="C18" s="520"/>
+      <c r="D18" s="520"/>
       <c r="E18" s="233" t="s">
         <v>61</v>
       </c>
@@ -10416,7 +10417,7 @@
         <v>83</v>
       </c>
       <c r="L18" s="233"/>
-      <c r="M18" s="519"/>
+      <c r="M18" s="520"/>
       <c r="N18" s="233" t="s">
         <v>151</v>
       </c>
@@ -10456,11 +10457,11 @@
       <c r="Z18" s="233" t="s">
         <v>150</v>
       </c>
-      <c r="AA18" s="519"/>
-      <c r="AB18" s="519"/>
-      <c r="AC18" s="519"/>
-      <c r="AD18" s="519"/>
-      <c r="AE18" s="535"/>
+      <c r="AA18" s="520"/>
+      <c r="AB18" s="520"/>
+      <c r="AC18" s="520"/>
+      <c r="AD18" s="520"/>
+      <c r="AE18" s="536"/>
     </row>
     <row r="19" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="214" t="s">
@@ -12414,14 +12415,14 @@
         <v>0</v>
       </c>
       <c r="K38" s="218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="218">
         <v>1</v>
       </c>
       <c r="M38" s="219">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N38" s="220">
         <v>3</v>
@@ -12450,11 +12451,11 @@
       </c>
       <c r="V38" s="222">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38" s="222">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X38" s="216">
         <v>2</v>
@@ -12524,7 +12525,7 @@
       </c>
       <c r="K39" s="262">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L39" s="262">
         <f t="shared" si="9"/>
@@ -12532,7 +12533,7 @@
       </c>
       <c r="M39" s="262">
         <f t="shared" si="9"/>
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N39" s="262">
         <f t="shared" si="9"/>
@@ -12568,11 +12569,11 @@
       </c>
       <c r="V39" s="262">
         <f t="shared" si="9"/>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W39" s="262">
         <f t="shared" si="9"/>
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X39" s="262">
         <f t="shared" si="9"/>
@@ -12649,7 +12650,7 @@
       </c>
       <c r="K40" s="264">
         <f t="shared" si="10"/>
-        <v>1.2</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="L40" s="264">
         <f t="shared" si="10"/>
@@ -12657,7 +12658,7 @@
       </c>
       <c r="M40" s="264">
         <f t="shared" si="10"/>
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="N40" s="264">
         <f t="shared" si="10"/>
@@ -12693,11 +12694,11 @@
       </c>
       <c r="V40" s="264">
         <f t="shared" si="10"/>
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="W40" s="264">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>12.95</v>
       </c>
       <c r="X40" s="264">
         <f t="shared" si="10"/>
@@ -13056,107 +13057,107 @@
       <c r="AE46" s="195"/>
     </row>
     <row r="47" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="491" t="s">
+      <c r="A47" s="492" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="492"/>
-      <c r="C47" s="492"/>
-      <c r="D47" s="492"/>
-      <c r="E47" s="492"/>
-      <c r="F47" s="492"/>
-      <c r="G47" s="493"/>
-      <c r="H47" s="494" t="s">
+      <c r="B47" s="493"/>
+      <c r="C47" s="493"/>
+      <c r="D47" s="493"/>
+      <c r="E47" s="493"/>
+      <c r="F47" s="493"/>
+      <c r="G47" s="494"/>
+      <c r="H47" s="495" t="s">
         <v>171</v>
       </c>
-      <c r="I47" s="494"/>
-      <c r="J47" s="515" t="s">
+      <c r="I47" s="495"/>
+      <c r="J47" s="516" t="s">
         <v>212</v>
       </c>
-      <c r="K47" s="460" t="s">
+      <c r="K47" s="461" t="s">
         <v>220</v>
       </c>
       <c r="L47" s="196"/>
       <c r="M47" s="196"/>
-      <c r="N47" s="495" t="s">
+      <c r="N47" s="496" t="s">
         <v>251</v>
       </c>
-      <c r="O47" s="495"/>
-      <c r="P47" s="495"/>
-      <c r="Q47" s="495"/>
-      <c r="R47" s="495"/>
-      <c r="S47" s="495"/>
-      <c r="T47" s="495"/>
-      <c r="U47" s="495"/>
-      <c r="V47" s="495"/>
-      <c r="W47" s="495"/>
-      <c r="X47" s="495"/>
-      <c r="Y47" s="495"/>
-      <c r="Z47" s="495"/>
-      <c r="AA47" s="495"/>
+      <c r="O47" s="496"/>
+      <c r="P47" s="496"/>
+      <c r="Q47" s="496"/>
+      <c r="R47" s="496"/>
+      <c r="S47" s="496"/>
+      <c r="T47" s="496"/>
+      <c r="U47" s="496"/>
+      <c r="V47" s="496"/>
+      <c r="W47" s="496"/>
+      <c r="X47" s="496"/>
+      <c r="Y47" s="496"/>
+      <c r="Z47" s="496"/>
+      <c r="AA47" s="496"/>
       <c r="AB47" s="105"/>
       <c r="AC47" s="105"/>
       <c r="AD47" s="105"/>
       <c r="AE47" s="197"/>
     </row>
     <row r="48" spans="1:31" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="491"/>
-      <c r="B48" s="493"/>
-      <c r="C48" s="496" t="s">
+      <c r="A48" s="492"/>
+      <c r="B48" s="494"/>
+      <c r="C48" s="497" t="s">
         <v>85</v>
       </c>
-      <c r="D48" s="497"/>
-      <c r="E48" s="496" t="s">
+      <c r="D48" s="498"/>
+      <c r="E48" s="497" t="s">
         <v>86</v>
       </c>
-      <c r="F48" s="497"/>
+      <c r="F48" s="498"/>
       <c r="G48" s="198"/>
-      <c r="H48" s="494"/>
-      <c r="I48" s="494"/>
-      <c r="J48" s="516"/>
-      <c r="K48" s="461"/>
+      <c r="H48" s="495"/>
+      <c r="I48" s="495"/>
+      <c r="J48" s="517"/>
+      <c r="K48" s="462"/>
       <c r="L48" s="196"/>
       <c r="M48" s="196"/>
-      <c r="N48" s="498" t="s">
+      <c r="N48" s="499" t="s">
         <v>52</v>
       </c>
-      <c r="O48" s="499"/>
-      <c r="P48" s="500"/>
-      <c r="Q48" s="507" t="s">
+      <c r="O48" s="500"/>
+      <c r="P48" s="501"/>
+      <c r="Q48" s="508" t="s">
         <v>51</v>
       </c>
-      <c r="R48" s="508"/>
-      <c r="S48" s="508"/>
-      <c r="T48" s="508"/>
-      <c r="U48" s="508"/>
-      <c r="V48" s="508"/>
-      <c r="W48" s="508"/>
-      <c r="X48" s="508"/>
-      <c r="Y48" s="508"/>
-      <c r="Z48" s="508"/>
-      <c r="AA48" s="509"/>
+      <c r="R48" s="509"/>
+      <c r="S48" s="509"/>
+      <c r="T48" s="509"/>
+      <c r="U48" s="509"/>
+      <c r="V48" s="509"/>
+      <c r="W48" s="509"/>
+      <c r="X48" s="509"/>
+      <c r="Y48" s="509"/>
+      <c r="Z48" s="509"/>
+      <c r="AA48" s="510"/>
       <c r="AB48" s="105"/>
       <c r="AC48" s="105"/>
       <c r="AD48" s="105"/>
       <c r="AE48" s="197"/>
     </row>
     <row r="49" spans="1:31" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="510" t="s">
+      <c r="A49" s="511" t="s">
         <v>152</v>
       </c>
-      <c r="B49" s="511"/>
-      <c r="C49" s="485">
+      <c r="B49" s="512"/>
+      <c r="C49" s="486">
         <v>26</v>
       </c>
-      <c r="D49" s="486"/>
-      <c r="E49" s="485">
+      <c r="D49" s="487"/>
+      <c r="E49" s="486">
         <v>5</v>
       </c>
-      <c r="F49" s="486"/>
+      <c r="F49" s="487"/>
       <c r="G49" s="199"/>
-      <c r="H49" s="487">
+      <c r="H49" s="488">
         <v>26</v>
       </c>
-      <c r="I49" s="487"/>
+      <c r="I49" s="488"/>
       <c r="J49" s="198">
         <v>8</v>
       </c>
@@ -13165,38 +13166,38 @@
       </c>
       <c r="L49" s="196"/>
       <c r="M49" s="196"/>
-      <c r="N49" s="501"/>
-      <c r="O49" s="502"/>
-      <c r="P49" s="503"/>
-      <c r="Q49" s="488" t="s">
+      <c r="N49" s="502"/>
+      <c r="O49" s="503"/>
+      <c r="P49" s="504"/>
+      <c r="Q49" s="489" t="s">
         <v>40</v>
       </c>
-      <c r="R49" s="489"/>
-      <c r="S49" s="489"/>
-      <c r="T49" s="489"/>
-      <c r="U49" s="490"/>
-      <c r="V49" s="488" t="s">
+      <c r="R49" s="490"/>
+      <c r="S49" s="490"/>
+      <c r="T49" s="490"/>
+      <c r="U49" s="491"/>
+      <c r="V49" s="489" t="s">
         <v>41</v>
       </c>
-      <c r="W49" s="490"/>
-      <c r="X49" s="488" t="s">
+      <c r="W49" s="491"/>
+      <c r="X49" s="489" t="s">
         <v>37</v>
       </c>
-      <c r="Y49" s="489"/>
-      <c r="Z49" s="489"/>
-      <c r="AA49" s="490"/>
+      <c r="Y49" s="490"/>
+      <c r="Z49" s="490"/>
+      <c r="AA49" s="491"/>
       <c r="AB49" s="105"/>
       <c r="AC49" s="105"/>
       <c r="AD49" s="105"/>
       <c r="AE49" s="197"/>
     </row>
     <row r="50" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="512"/>
-      <c r="B50" s="512"/>
-      <c r="C50" s="512"/>
-      <c r="D50" s="512"/>
-      <c r="E50" s="512"/>
-      <c r="F50" s="512"/>
+      <c r="A50" s="513"/>
+      <c r="B50" s="513"/>
+      <c r="C50" s="513"/>
+      <c r="D50" s="513"/>
+      <c r="E50" s="513"/>
+      <c r="F50" s="513"/>
       <c r="G50" s="200"/>
       <c r="H50" s="196"/>
       <c r="I50" s="196"/>
@@ -13204,15 +13205,15 @@
       <c r="K50" s="196"/>
       <c r="L50" s="196"/>
       <c r="M50" s="196"/>
-      <c r="N50" s="504"/>
-      <c r="O50" s="505"/>
-      <c r="P50" s="506"/>
-      <c r="Q50" s="488" t="s">
+      <c r="N50" s="505"/>
+      <c r="O50" s="506"/>
+      <c r="P50" s="507"/>
+      <c r="Q50" s="489" t="s">
         <v>42</v>
       </c>
-      <c r="R50" s="489"/>
-      <c r="S50" s="489"/>
-      <c r="T50" s="490"/>
+      <c r="R50" s="490"/>
+      <c r="S50" s="490"/>
+      <c r="T50" s="491"/>
       <c r="U50" s="184" t="s">
         <v>43</v>
       </c>
@@ -13222,10 +13223,10 @@
       <c r="W50" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="X50" s="513" t="s">
+      <c r="X50" s="514" t="s">
         <v>42</v>
       </c>
-      <c r="Y50" s="514"/>
+      <c r="Y50" s="515"/>
       <c r="Z50" s="202"/>
       <c r="AA50" s="201" t="s">
         <v>43</v>
@@ -13236,35 +13237,35 @@
       <c r="AE50" s="197"/>
     </row>
     <row r="51" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="478"/>
-      <c r="B51" s="478"/>
-      <c r="C51" s="479"/>
-      <c r="D51" s="479"/>
-      <c r="E51" s="479"/>
+      <c r="A51" s="479"/>
+      <c r="B51" s="479"/>
+      <c r="C51" s="480"/>
+      <c r="D51" s="480"/>
+      <c r="E51" s="480"/>
       <c r="F51" s="203"/>
       <c r="G51" s="204"/>
-      <c r="H51" s="470" t="s">
+      <c r="H51" s="471" t="s">
         <v>44</v>
       </c>
-      <c r="I51" s="471"/>
-      <c r="J51" s="471"/>
-      <c r="K51" s="471"/>
-      <c r="L51" s="471"/>
-      <c r="M51" s="472"/>
-      <c r="N51" s="480">
+      <c r="I51" s="472"/>
+      <c r="J51" s="472"/>
+      <c r="K51" s="472"/>
+      <c r="L51" s="472"/>
+      <c r="M51" s="473"/>
+      <c r="N51" s="481">
         <f>16.81-7.24</f>
         <v>9.5699999999999985</v>
       </c>
-      <c r="O51" s="481"/>
-      <c r="P51" s="482"/>
-      <c r="Q51" s="483">
-        <v>13</v>
-      </c>
-      <c r="R51" s="484"/>
-      <c r="S51" s="484"/>
-      <c r="T51" s="484"/>
+      <c r="O51" s="482"/>
+      <c r="P51" s="483"/>
+      <c r="Q51" s="484">
+        <v>12</v>
+      </c>
+      <c r="R51" s="485"/>
+      <c r="S51" s="485"/>
+      <c r="T51" s="485"/>
       <c r="U51" s="205">
-        <v>8.3000000000000007</v>
+        <v>7.2</v>
       </c>
       <c r="V51" s="206">
         <v>16</v>
@@ -13272,15 +13273,15 @@
       <c r="W51" s="207">
         <v>8.75</v>
       </c>
-      <c r="X51" s="464">
+      <c r="X51" s="465">
         <f>Q51+V51</f>
-        <v>29</v>
-      </c>
-      <c r="Y51" s="465"/>
+        <v>28</v>
+      </c>
+      <c r="Y51" s="466"/>
       <c r="Z51" s="208"/>
       <c r="AA51" s="207">
         <f>U51+W51</f>
-        <v>17.05</v>
+        <v>15.95</v>
       </c>
       <c r="AB51" s="105"/>
       <c r="AC51" s="105"/>
@@ -13288,33 +13289,33 @@
       <c r="AE51" s="197"/>
     </row>
     <row r="52" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="468"/>
-      <c r="B52" s="468"/>
-      <c r="C52" s="469"/>
-      <c r="D52" s="469"/>
-      <c r="E52" s="469"/>
-      <c r="F52" s="469"/>
+      <c r="A52" s="469"/>
+      <c r="B52" s="469"/>
+      <c r="C52" s="470"/>
+      <c r="D52" s="470"/>
+      <c r="E52" s="470"/>
+      <c r="F52" s="470"/>
       <c r="G52" s="204"/>
-      <c r="H52" s="470" t="s">
+      <c r="H52" s="471" t="s">
         <v>45</v>
       </c>
-      <c r="I52" s="471"/>
-      <c r="J52" s="471"/>
-      <c r="K52" s="471"/>
-      <c r="L52" s="471"/>
-      <c r="M52" s="472"/>
-      <c r="N52" s="473">
+      <c r="I52" s="472"/>
+      <c r="J52" s="472"/>
+      <c r="K52" s="472"/>
+      <c r="L52" s="472"/>
+      <c r="M52" s="473"/>
+      <c r="N52" s="474">
         <f>3.25-2.2</f>
         <v>1.0499999999999998</v>
       </c>
-      <c r="O52" s="474"/>
-      <c r="P52" s="475"/>
-      <c r="Q52" s="476">
-        <v>0</v>
-      </c>
-      <c r="R52" s="477"/>
-      <c r="S52" s="477"/>
-      <c r="T52" s="477"/>
+      <c r="O52" s="475"/>
+      <c r="P52" s="476"/>
+      <c r="Q52" s="477">
+        <v>0</v>
+      </c>
+      <c r="R52" s="478"/>
+      <c r="S52" s="478"/>
+      <c r="T52" s="478"/>
       <c r="U52" s="209">
         <v>0</v>
       </c>
@@ -13324,11 +13325,11 @@
       <c r="W52" s="207">
         <v>1.9</v>
       </c>
-      <c r="X52" s="464">
+      <c r="X52" s="465">
         <f>Q52+V52</f>
         <v>9</v>
       </c>
-      <c r="Y52" s="465"/>
+      <c r="Y52" s="466"/>
       <c r="Z52" s="208"/>
       <c r="AA52" s="207">
         <f>U52+W52</f>
@@ -13340,12 +13341,12 @@
       <c r="AE52" s="197"/>
     </row>
     <row r="53" spans="1:31" ht="20.25" x14ac:dyDescent="0.15">
-      <c r="A53" s="466"/>
-      <c r="B53" s="466"/>
-      <c r="C53" s="467"/>
-      <c r="D53" s="467"/>
-      <c r="E53" s="467"/>
-      <c r="F53" s="467"/>
+      <c r="A53" s="467"/>
+      <c r="B53" s="467"/>
+      <c r="C53" s="468"/>
+      <c r="D53" s="468"/>
+      <c r="E53" s="468"/>
+      <c r="F53" s="468"/>
       <c r="G53" s="173"/>
       <c r="H53" s="172"/>
       <c r="I53" s="172"/>
@@ -13369,29 +13370,29 @@
       <c r="AE54" s="24"/>
     </row>
     <row r="55" spans="1:31" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A55" s="462" t="s">
+      <c r="A55" s="463" t="s">
         <v>153</v>
       </c>
-      <c r="B55" s="462"/>
-      <c r="C55" s="462"/>
-      <c r="D55" s="462"/>
-      <c r="E55" s="462"/>
-      <c r="F55" s="462"/>
-      <c r="G55" s="462"/>
-      <c r="H55" s="462"/>
-      <c r="I55" s="462"/>
-      <c r="J55" s="462"/>
-      <c r="K55" s="462"/>
-      <c r="L55" s="462"/>
-      <c r="M55" s="462"/>
-      <c r="N55" s="463" t="str">
+      <c r="B55" s="463"/>
+      <c r="C55" s="463"/>
+      <c r="D55" s="463"/>
+      <c r="E55" s="463"/>
+      <c r="F55" s="463"/>
+      <c r="G55" s="463"/>
+      <c r="H55" s="463"/>
+      <c r="I55" s="463"/>
+      <c r="J55" s="463"/>
+      <c r="K55" s="463"/>
+      <c r="L55" s="463"/>
+      <c r="M55" s="463"/>
+      <c r="N55" s="464" t="str">
         <f>AB1</f>
         <v>20.09.2026</v>
       </c>
-      <c r="O55" s="463"/>
-      <c r="P55" s="463"/>
-      <c r="Q55" s="463"/>
-      <c r="R55" s="463"/>
+      <c r="O55" s="464"/>
+      <c r="P55" s="464"/>
+      <c r="Q55" s="464"/>
+      <c r="R55" s="464"/>
       <c r="S55" s="183"/>
       <c r="T55" s="183"/>
       <c r="U55" s="36"/>
@@ -13408,29 +13409,29 @@
       <c r="AE56" s="24"/>
     </row>
     <row r="57" spans="1:31" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="462" t="s">
+      <c r="A57" s="463" t="s">
         <v>154</v>
       </c>
-      <c r="B57" s="462"/>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-      <c r="G57" s="462"/>
-      <c r="H57" s="462"/>
-      <c r="I57" s="462"/>
-      <c r="J57" s="462"/>
-      <c r="K57" s="462"/>
-      <c r="L57" s="462"/>
-      <c r="M57" s="462"/>
-      <c r="N57" s="463" t="str">
+      <c r="B57" s="463"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
+      <c r="G57" s="463"/>
+      <c r="H57" s="463"/>
+      <c r="I57" s="463"/>
+      <c r="J57" s="463"/>
+      <c r="K57" s="463"/>
+      <c r="L57" s="463"/>
+      <c r="M57" s="463"/>
+      <c r="N57" s="464" t="str">
         <f>AB1</f>
         <v>20.09.2026</v>
       </c>
-      <c r="O57" s="463"/>
-      <c r="P57" s="463"/>
-      <c r="Q57" s="463"/>
-      <c r="R57" s="463"/>
+      <c r="O57" s="464"/>
+      <c r="P57" s="464"/>
+      <c r="Q57" s="464"/>
+      <c r="R57" s="464"/>
       <c r="S57" s="175"/>
       <c r="T57" s="175"/>
       <c r="U57" s="36"/>

--- a/reports/2026-09-20.xlsx
+++ b/reports/2026-09-20.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D015837D-1BD9-AC46-AF59-ECE15DCF91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AFA522A-CE29-8B44-8390-01C8B3101E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6696,7 +6696,7 @@
       <c r="R59" s="60"/>
       <c r="S59" s="60"/>
     </row>
-    <row r="60" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
       <c r="B60" s="344" t="s">
         <v>249</v>

--- a/reports/2026-09-20.xlsx
+++ b/reports/2026-09-20.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AFA522A-CE29-8B44-8390-01C8B3101E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BE44830-1DA6-F243-B91E-043D62D90042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1650,7 +1650,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1782,6 +1782,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="67">
     <border>
@@ -2632,7 +2638,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="587">
+  <cellXfs count="586">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3541,9 +3547,6 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="46" fillId="21" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3601,9 +3604,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="59" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4330,6 +4330,9 @@
     </xf>
     <xf numFmtId="0" fontId="81" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4744,16 +4747,16 @@
     <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="418" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="418"/>
-      <c r="E1" s="418"/>
-      <c r="F1" s="418"/>
-      <c r="G1" s="418"/>
-      <c r="H1" s="418"/>
-      <c r="I1" s="418"/>
-      <c r="J1" s="418"/>
+      <c r="C1" s="416" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="416"/>
+      <c r="E1" s="416"/>
+      <c r="F1" s="416"/>
+      <c r="G1" s="416"/>
+      <c r="H1" s="416"/>
+      <c r="I1" s="416"/>
+      <c r="J1" s="416"/>
       <c r="K1" s="67" t="s">
         <v>247</v>
       </c>
@@ -4784,11 +4787,11 @@
     <row r="3" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="420" t="s">
+      <c r="C3" s="418" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="421"/>
-      <c r="E3" s="421"/>
+      <c r="D3" s="419"/>
+      <c r="E3" s="419"/>
       <c r="F3" s="89" t="s">
         <v>1</v>
       </c>
@@ -4801,24 +4804,24 @@
       <c r="I3" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="419" t="s">
+      <c r="J3" s="417" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="419"/>
-      <c r="L3" s="419"/>
-      <c r="M3" s="419"/>
-      <c r="N3" s="419"/>
-      <c r="O3" s="419"/>
-      <c r="P3" s="419"/>
+      <c r="K3" s="417"/>
+      <c r="L3" s="417"/>
+      <c r="M3" s="417"/>
+      <c r="N3" s="417"/>
+      <c r="O3" s="417"/>
+      <c r="P3" s="417"/>
     </row>
     <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="334"/>
-      <c r="C4" s="422" t="s">
+      <c r="B4" s="333"/>
+      <c r="C4" s="420" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="423"/>
-      <c r="E4" s="423"/>
+      <c r="D4" s="421"/>
+      <c r="E4" s="421"/>
       <c r="F4" s="91">
         <v>93</v>
       </c>
@@ -4827,10 +4830,10 @@
       </c>
       <c r="H4" s="92"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="427" t="s">
+      <c r="J4" s="425" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="427"/>
+      <c r="K4" s="425"/>
       <c r="L4" s="283" t="s">
         <v>168</v>
       </c>
@@ -4852,12 +4855,12 @@
     </row>
     <row r="5" spans="1:23" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="334"/>
-      <c r="C5" s="358" t="s">
+      <c r="B5" s="333"/>
+      <c r="C5" s="356" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="359"/>
-      <c r="E5" s="359"/>
+      <c r="D5" s="357"/>
+      <c r="E5" s="357"/>
       <c r="F5" s="91">
         <v>284</v>
       </c>
@@ -4868,10 +4871,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="432" t="s">
+      <c r="J5" s="430" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="432"/>
+      <c r="K5" s="430"/>
       <c r="L5" s="292" t="s">
         <v>176</v>
       </c>
@@ -4893,12 +4896,12 @@
     </row>
     <row r="6" spans="1:23" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="334"/>
-      <c r="C6" s="422" t="s">
+      <c r="B6" s="333"/>
+      <c r="C6" s="420" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="423"/>
-      <c r="E6" s="423"/>
+      <c r="D6" s="421"/>
+      <c r="E6" s="421"/>
       <c r="F6" s="91">
         <v>347</v>
       </c>
@@ -4909,10 +4912,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="335" t="s">
+      <c r="J6" s="334" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="335"/>
+      <c r="K6" s="334"/>
       <c r="L6" s="293" t="s">
         <v>177</v>
       </c>
@@ -4934,12 +4937,12 @@
     </row>
     <row r="7" spans="1:23" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="334"/>
-      <c r="C7" s="422" t="s">
+      <c r="B7" s="333"/>
+      <c r="C7" s="420" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="423"/>
-      <c r="E7" s="423"/>
+      <c r="D7" s="421"/>
+      <c r="E7" s="421"/>
       <c r="F7" s="164">
         <f>F4+F5-F6</f>
         <v>30</v>
@@ -4952,10 +4955,10 @@
         <v>7</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="403" t="s">
+      <c r="J7" s="401" t="s">
         <v>57</v>
       </c>
-      <c r="K7" s="403"/>
+      <c r="K7" s="401"/>
       <c r="L7" s="294">
         <v>999.91</v>
       </c>
@@ -4978,11 +4981,11 @@
     <row r="8" spans="1:23" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="430" t="s">
+      <c r="C8" s="428" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="431"/>
-      <c r="E8" s="431"/>
+      <c r="D8" s="429"/>
+      <c r="E8" s="429"/>
       <c r="F8" s="103">
         <v>0</v>
       </c>
@@ -4991,10 +4994,10 @@
       </c>
       <c r="H8" s="95"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="335" t="s">
+      <c r="J8" s="334" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="335"/>
+      <c r="K8" s="334"/>
       <c r="L8" s="294">
         <v>50000</v>
       </c>
@@ -5021,10 +5024,10 @@
       <c r="D9" s="10"/>
       <c r="E9" s="4"/>
       <c r="I9" s="11"/>
-      <c r="J9" s="335" t="s">
+      <c r="J9" s="334" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="335"/>
+      <c r="K9" s="334"/>
       <c r="L9" s="295">
         <f>50000-L8</f>
         <v>0</v>
@@ -5051,12 +5054,12 @@
     </row>
     <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="334"/>
-      <c r="C10" s="424" t="s">
+      <c r="B10" s="333"/>
+      <c r="C10" s="422" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="425"/>
-      <c r="E10" s="426"/>
+      <c r="D10" s="423"/>
+      <c r="E10" s="424"/>
       <c r="F10" s="89" t="s">
         <v>1</v>
       </c>
@@ -5067,14 +5070,14 @@
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="434" t="s">
+      <c r="J10" s="432" t="s">
         <v>144</v>
       </c>
-      <c r="K10" s="435"/>
-      <c r="L10" s="428">
+      <c r="K10" s="433"/>
+      <c r="L10" s="426">
         <v>15700</v>
       </c>
-      <c r="M10" s="429"/>
+      <c r="M10" s="427"/>
       <c r="N10" s="104"/>
       <c r="O10" s="104"/>
       <c r="P10" s="104"/>
@@ -5084,12 +5087,12 @@
     </row>
     <row r="11" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="334"/>
-      <c r="C11" s="360" t="s">
+      <c r="B11" s="333"/>
+      <c r="C11" s="358" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="361"/>
-      <c r="E11" s="362"/>
+      <c r="D11" s="359"/>
+      <c r="E11" s="360"/>
       <c r="F11" s="69">
         <v>105384</v>
       </c>
@@ -5100,29 +5103,29 @@
         <v>170224.48</v>
       </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="436" t="s">
+      <c r="J11" s="434" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="437"/>
-      <c r="L11" s="407">
+      <c r="K11" s="435"/>
+      <c r="L11" s="405">
         <v>13600</v>
       </c>
-      <c r="M11" s="408"/>
+      <c r="M11" s="406"/>
       <c r="N11" s="104"/>
       <c r="O11" s="86"/>
-      <c r="P11" s="433"/>
-      <c r="Q11" s="433"/>
-      <c r="R11" s="433"/>
+      <c r="P11" s="431"/>
+      <c r="Q11" s="431"/>
+      <c r="R11" s="431"/>
       <c r="S11" s="107"/>
     </row>
     <row r="12" spans="1:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="334"/>
-      <c r="C12" s="358" t="s">
+      <c r="B12" s="333"/>
+      <c r="C12" s="356" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="359"/>
-      <c r="E12" s="359"/>
+      <c r="D12" s="357"/>
+      <c r="E12" s="357"/>
       <c r="F12" s="69">
         <f>11169+10878+5590-3759</f>
         <v>23878</v>
@@ -5136,10 +5139,10 @@
       <c r="I12" s="12"/>
       <c r="N12" s="105"/>
       <c r="O12" s="86"/>
-      <c r="T12" s="438" t="s">
+      <c r="T12" s="436" t="s">
         <v>196</v>
       </c>
-      <c r="U12" s="439"/>
+      <c r="U12" s="437"/>
       <c r="V12" s="304" t="s">
         <v>49</v>
       </c>
@@ -5149,12 +5152,12 @@
     </row>
     <row r="13" spans="1:23" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="334"/>
-      <c r="C13" s="360" t="s">
+      <c r="B13" s="333"/>
+      <c r="C13" s="358" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="361"/>
-      <c r="E13" s="362"/>
+      <c r="D13" s="359"/>
+      <c r="E13" s="360"/>
       <c r="F13" s="69">
         <f>21446+11230+4475</f>
         <v>37151</v>
@@ -5166,20 +5169,20 @@
         <v>25355</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="424" t="s">
+      <c r="J13" s="422" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="425"/>
-      <c r="L13" s="425"/>
-      <c r="M13" s="426"/>
+      <c r="K13" s="423"/>
+      <c r="L13" s="423"/>
+      <c r="M13" s="424"/>
       <c r="N13" s="143" t="s">
         <v>95</v>
       </c>
       <c r="O13" s="106"/>
-      <c r="T13" s="438" t="s">
+      <c r="T13" s="436" t="s">
         <v>197</v>
       </c>
-      <c r="U13" s="438"/>
+      <c r="U13" s="436"/>
       <c r="V13" s="299">
         <f>N19+N20</f>
         <v>96700</v>
@@ -5191,12 +5194,12 @@
     </row>
     <row r="14" spans="1:23" s="13" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
-      <c r="B14" s="336"/>
-      <c r="C14" s="363" t="s">
+      <c r="B14" s="335"/>
+      <c r="C14" s="361" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="364"/>
-      <c r="E14" s="365"/>
+      <c r="D14" s="362"/>
+      <c r="E14" s="363"/>
       <c r="F14" s="73">
         <f>F11+F12-F13</f>
         <v>92111</v>
@@ -5210,44 +5213,44 @@
         <v>167849.88</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="380" t="s">
+      <c r="J14" s="378" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="381"/>
-      <c r="L14" s="381"/>
-      <c r="M14" s="328"/>
+      <c r="K14" s="379"/>
+      <c r="L14" s="379"/>
+      <c r="M14" s="327"/>
       <c r="N14" s="144"/>
       <c r="O14" s="16"/>
       <c r="P14" s="291"/>
-      <c r="T14" s="416"/>
-      <c r="U14" s="417"/>
+      <c r="T14" s="414"/>
+      <c r="U14" s="415"/>
       <c r="V14" s="302"/>
       <c r="W14" s="302"/>
     </row>
     <row r="15" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="334"/>
-      <c r="C15" s="404"/>
-      <c r="D15" s="405"/>
-      <c r="E15" s="406"/>
+      <c r="B15" s="333"/>
+      <c r="C15" s="402"/>
+      <c r="D15" s="403"/>
+      <c r="E15" s="404"/>
       <c r="F15" s="75"/>
       <c r="G15" s="76"/>
       <c r="H15" s="76"/>
       <c r="I15" s="17"/>
-      <c r="J15" s="409" t="s">
+      <c r="J15" s="407" t="s">
         <v>137</v>
       </c>
-      <c r="K15" s="410"/>
-      <c r="L15" s="410"/>
-      <c r="M15" s="411"/>
+      <c r="K15" s="408"/>
+      <c r="L15" s="408"/>
+      <c r="M15" s="409"/>
       <c r="N15" s="153">
         <v>102779</v>
       </c>
       <c r="O15" s="18"/>
-      <c r="T15" s="438" t="s">
+      <c r="T15" s="436" t="s">
         <v>198</v>
       </c>
-      <c r="U15" s="438"/>
+      <c r="U15" s="436"/>
       <c r="V15" s="298">
         <f>N31+N32</f>
         <v>48447</v>
@@ -5259,12 +5262,12 @@
     </row>
     <row r="16" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="334"/>
-      <c r="C16" s="394" t="s">
+      <c r="B16" s="333"/>
+      <c r="C16" s="392" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="395"/>
-      <c r="E16" s="396"/>
+      <c r="D16" s="393"/>
+      <c r="E16" s="394"/>
       <c r="F16" s="89" t="s">
         <v>49</v>
       </c>
@@ -5275,12 +5278,12 @@
         <v>3</v>
       </c>
       <c r="I16" s="17"/>
-      <c r="J16" s="412" t="s">
+      <c r="J16" s="410" t="s">
         <v>146</v>
       </c>
-      <c r="K16" s="413"/>
-      <c r="L16" s="413"/>
-      <c r="M16" s="414"/>
+      <c r="K16" s="411"/>
+      <c r="L16" s="411"/>
+      <c r="M16" s="412"/>
       <c r="N16" s="154">
         <v>60361</v>
       </c>
@@ -5288,19 +5291,19 @@
       <c r="Q16" s="65"/>
       <c r="R16" s="65"/>
       <c r="S16" s="65"/>
-      <c r="T16" s="445"/>
-      <c r="U16" s="446"/>
+      <c r="T16" s="443"/>
+      <c r="U16" s="444"/>
       <c r="V16" s="303"/>
       <c r="W16" s="303"/>
     </row>
     <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="334"/>
-      <c r="C17" s="360" t="s">
+      <c r="B17" s="333"/>
+      <c r="C17" s="358" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="361"/>
-      <c r="E17" s="362"/>
+      <c r="D17" s="359"/>
+      <c r="E17" s="360"/>
       <c r="F17" s="71">
         <f>51481+21994</f>
         <v>73475</v>
@@ -5313,12 +5316,12 @@
         <v>60139.519999999997</v>
       </c>
       <c r="I17" s="17"/>
-      <c r="J17" s="366" t="s">
+      <c r="J17" s="364" t="s">
         <v>147</v>
       </c>
-      <c r="K17" s="367"/>
-      <c r="L17" s="367"/>
-      <c r="M17" s="368"/>
+      <c r="K17" s="365"/>
+      <c r="L17" s="365"/>
+      <c r="M17" s="366"/>
       <c r="N17" s="154">
         <v>4272</v>
       </c>
@@ -5326,10 +5329,10 @@
       <c r="Q17" s="65"/>
       <c r="R17" s="65"/>
       <c r="S17" s="65"/>
-      <c r="T17" s="441" t="s">
+      <c r="T17" s="439" t="s">
         <v>222</v>
       </c>
-      <c r="U17" s="442"/>
+      <c r="U17" s="440"/>
       <c r="V17" s="297">
         <f>N41</f>
         <v>0</v>
@@ -5341,12 +5344,12 @@
     </row>
     <row r="18" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="334"/>
-      <c r="C18" s="360" t="s">
+      <c r="B18" s="333"/>
+      <c r="C18" s="358" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="361"/>
-      <c r="E18" s="362"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="360"/>
       <c r="F18" s="71">
         <v>12576</v>
       </c>
@@ -5357,17 +5360,17 @@
         <v>53600.78</v>
       </c>
       <c r="I18" s="17"/>
-      <c r="J18" s="391" t="s">
+      <c r="J18" s="389" t="s">
         <v>94</v>
       </c>
-      <c r="K18" s="392"/>
-      <c r="L18" s="392"/>
-      <c r="M18" s="393"/>
+      <c r="K18" s="390"/>
+      <c r="L18" s="390"/>
+      <c r="M18" s="391"/>
       <c r="N18" s="150"/>
-      <c r="T18" s="443" t="s">
+      <c r="T18" s="441" t="s">
         <v>5</v>
       </c>
-      <c r="U18" s="444"/>
+      <c r="U18" s="442"/>
       <c r="V18" s="309">
         <f>SUM(V13:V17)</f>
         <v>145147</v>
@@ -5379,12 +5382,12 @@
     </row>
     <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="334"/>
-      <c r="C19" s="360" t="s">
+      <c r="B19" s="333"/>
+      <c r="C19" s="358" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="361"/>
-      <c r="E19" s="362"/>
+      <c r="D19" s="359"/>
+      <c r="E19" s="360"/>
       <c r="F19" s="71">
         <v>6060</v>
       </c>
@@ -5395,24 +5398,24 @@
         <v>54109.58</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="366" t="s">
+      <c r="J19" s="364" t="s">
         <v>148</v>
       </c>
-      <c r="K19" s="367"/>
-      <c r="L19" s="367"/>
-      <c r="M19" s="368"/>
+      <c r="K19" s="365"/>
+      <c r="L19" s="365"/>
+      <c r="M19" s="366"/>
       <c r="N19" s="150">
         <v>35740</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="334"/>
-      <c r="C20" s="360" t="s">
+      <c r="B20" s="333"/>
+      <c r="C20" s="358" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="361"/>
-      <c r="E20" s="362"/>
+      <c r="D20" s="359"/>
+      <c r="E20" s="360"/>
       <c r="F20" s="71">
         <v>0</v>
       </c>
@@ -5421,20 +5424,20 @@
       </c>
       <c r="H20" s="69"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="366" t="s">
+      <c r="J20" s="364" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="367"/>
-      <c r="L20" s="367"/>
-      <c r="M20" s="368"/>
+      <c r="K20" s="365"/>
+      <c r="L20" s="365"/>
+      <c r="M20" s="366"/>
       <c r="N20" s="150">
         <v>60960</v>
       </c>
-      <c r="S20" s="440" t="s">
+      <c r="S20" s="438" t="s">
         <v>228</v>
       </c>
-      <c r="T20" s="440"/>
-      <c r="U20" s="440"/>
+      <c r="T20" s="438"/>
+      <c r="U20" s="438"/>
       <c r="V20" s="312">
         <f>V18+W18</f>
         <v>428749</v>
@@ -5442,12 +5445,12 @@
     </row>
     <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="334"/>
-      <c r="C21" s="360" t="s">
+      <c r="B21" s="333"/>
+      <c r="C21" s="358" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="361"/>
-      <c r="E21" s="362"/>
+      <c r="D21" s="359"/>
+      <c r="E21" s="360"/>
       <c r="F21" s="71" t="s">
         <v>117</v>
       </c>
@@ -5456,21 +5459,21 @@
         <v>0</v>
       </c>
       <c r="I21" s="19"/>
-      <c r="J21" s="366"/>
-      <c r="K21" s="367"/>
-      <c r="L21" s="367"/>
-      <c r="M21" s="368"/>
+      <c r="J21" s="364"/>
+      <c r="K21" s="365"/>
+      <c r="L21" s="365"/>
+      <c r="M21" s="366"/>
       <c r="N21" s="150"/>
       <c r="P21" s="288"/>
     </row>
     <row r="22" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="334"/>
-      <c r="C22" s="372" t="s">
+      <c r="B22" s="333"/>
+      <c r="C22" s="370" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="373"/>
-      <c r="E22" s="374"/>
+      <c r="D22" s="371"/>
+      <c r="E22" s="372"/>
       <c r="F22" s="73">
         <f>SUM(F17:F21)</f>
         <v>92111</v>
@@ -5484,12 +5487,12 @@
         <v>167849.88</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="375" t="s">
+      <c r="J22" s="373" t="s">
         <v>141</v>
       </c>
-      <c r="K22" s="376"/>
-      <c r="L22" s="376"/>
-      <c r="M22" s="377"/>
+      <c r="K22" s="374"/>
+      <c r="L22" s="374"/>
+      <c r="M22" s="375"/>
       <c r="N22" s="155">
         <f>SUM(N15:N21)</f>
         <v>264112</v>
@@ -5498,7 +5501,7 @@
     </row>
     <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="334"/>
+      <c r="B23" s="333"/>
       <c r="C23" s="52"/>
       <c r="D23" s="53"/>
       <c r="E23" s="54"/>
@@ -5510,12 +5513,12 @@
     </row>
     <row r="24" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="334"/>
-      <c r="C24" s="394" t="s">
+      <c r="B24" s="333"/>
+      <c r="C24" s="392" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="395"/>
-      <c r="E24" s="396"/>
+      <c r="D24" s="393"/>
+      <c r="E24" s="394"/>
       <c r="F24" s="89" t="s">
         <v>1</v>
       </c>
@@ -5526,17 +5529,17 @@
         <v>3</v>
       </c>
       <c r="I24" s="7"/>
-      <c r="J24" s="385" t="s">
+      <c r="J24" s="383" t="s">
         <v>143</v>
       </c>
-      <c r="K24" s="386"/>
-      <c r="L24" s="386"/>
-      <c r="M24" s="387"/>
+      <c r="K24" s="384"/>
+      <c r="L24" s="384"/>
+      <c r="M24" s="385"/>
       <c r="N24" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="O24" s="378"/>
-      <c r="P24" s="379"/>
+      <c r="O24" s="376"/>
+      <c r="P24" s="377"/>
       <c r="Q24" s="58"/>
       <c r="R24" s="66"/>
       <c r="S24" s="66"/>
@@ -5544,11 +5547,11 @@
     <row r="25" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="360" t="s">
+      <c r="C25" s="358" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="361"/>
-      <c r="E25" s="362"/>
+      <c r="D25" s="359"/>
+      <c r="E25" s="360"/>
       <c r="F25" s="71">
         <f>F13-F26-F28-F29</f>
         <v>21446</v>
@@ -5558,12 +5561,12 @@
         <v>6006</v>
       </c>
       <c r="I25" s="7"/>
-      <c r="J25" s="380" t="s">
+      <c r="J25" s="378" t="s">
         <v>2</v>
       </c>
-      <c r="K25" s="381"/>
-      <c r="L25" s="381"/>
-      <c r="M25" s="328"/>
+      <c r="K25" s="379"/>
+      <c r="L25" s="379"/>
+      <c r="M25" s="327"/>
       <c r="N25" s="145"/>
       <c r="O25" s="58"/>
       <c r="P25" s="58"/>
@@ -5574,11 +5577,11 @@
     <row r="26" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="20"/>
-      <c r="C26" s="360" t="s">
+      <c r="C26" s="358" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="361"/>
-      <c r="E26" s="362"/>
+      <c r="D26" s="359"/>
+      <c r="E26" s="360"/>
       <c r="F26" s="71">
         <v>11230</v>
       </c>
@@ -5588,12 +5591,12 @@
         <v>8722</v>
       </c>
       <c r="I26" s="7"/>
-      <c r="J26" s="345" t="s">
+      <c r="J26" s="343" t="s">
         <v>223</v>
       </c>
-      <c r="K26" s="346"/>
-      <c r="L26" s="346"/>
-      <c r="M26" s="347"/>
+      <c r="K26" s="344"/>
+      <c r="L26" s="344"/>
+      <c r="M26" s="345"/>
       <c r="N26" s="150">
         <v>2546</v>
       </c>
@@ -5612,12 +5615,12 @@
       <c r="G27" s="181"/>
       <c r="H27" s="121"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="345" t="s">
+      <c r="J27" s="343" t="s">
         <v>224</v>
       </c>
-      <c r="K27" s="346"/>
-      <c r="L27" s="346"/>
-      <c r="M27" s="347"/>
+      <c r="K27" s="344"/>
+      <c r="L27" s="344"/>
+      <c r="M27" s="345"/>
       <c r="N27" s="150">
         <v>29272</v>
       </c>
@@ -5629,11 +5632,11 @@
     <row r="28" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="20"/>
-      <c r="C28" s="360" t="s">
+      <c r="C28" s="358" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="361"/>
-      <c r="E28" s="362"/>
+      <c r="D28" s="359"/>
+      <c r="E28" s="360"/>
       <c r="F28" s="71">
         <v>4475</v>
       </c>
@@ -5643,12 +5646,12 @@
         <v>10627</v>
       </c>
       <c r="I28" s="7"/>
-      <c r="J28" s="345" t="s">
+      <c r="J28" s="343" t="s">
         <v>225</v>
       </c>
-      <c r="K28" s="346"/>
-      <c r="L28" s="346"/>
-      <c r="M28" s="347"/>
+      <c r="K28" s="344"/>
+      <c r="L28" s="344"/>
+      <c r="M28" s="345"/>
       <c r="N28" s="150">
         <v>46324</v>
       </c>
@@ -5660,11 +5663,11 @@
     <row r="29" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="360" t="s">
+      <c r="C29" s="358" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="361"/>
-      <c r="E29" s="362"/>
+      <c r="D29" s="359"/>
+      <c r="E29" s="360"/>
       <c r="F29" s="71">
         <v>0</v>
       </c>
@@ -5673,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="7"/>
-      <c r="J29" s="345"/>
-      <c r="K29" s="346"/>
-      <c r="L29" s="346"/>
-      <c r="M29" s="347"/>
+      <c r="J29" s="343"/>
+      <c r="K29" s="344"/>
+      <c r="L29" s="344"/>
+      <c r="M29" s="345"/>
       <c r="N29" s="150"/>
       <c r="P29" s="58"/>
       <c r="Q29" s="58"/>
@@ -5686,23 +5689,23 @@
     <row r="30" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="20"/>
-      <c r="C30" s="360" t="s">
+      <c r="C30" s="358" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="361"/>
-      <c r="E30" s="362"/>
+      <c r="D30" s="359"/>
+      <c r="E30" s="360"/>
       <c r="F30" s="71"/>
       <c r="G30" s="102"/>
       <c r="H30" s="123">
         <v>0</v>
       </c>
       <c r="I30" s="7"/>
-      <c r="J30" s="391" t="s">
+      <c r="J30" s="389" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="392"/>
-      <c r="L30" s="392"/>
-      <c r="M30" s="393"/>
+      <c r="K30" s="390"/>
+      <c r="L30" s="390"/>
+      <c r="M30" s="391"/>
       <c r="N30" s="151"/>
       <c r="P30" s="58"/>
       <c r="Q30" s="58"/>
@@ -5712,23 +5715,23 @@
     <row r="31" spans="1:23" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="360" t="s">
+      <c r="C31" s="358" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="361"/>
-      <c r="E31" s="362"/>
+      <c r="D31" s="359"/>
+      <c r="E31" s="360"/>
       <c r="F31" s="71"/>
       <c r="G31" s="99"/>
       <c r="H31" s="121">
         <v>0</v>
       </c>
       <c r="I31" s="7"/>
-      <c r="J31" s="382" t="s">
+      <c r="J31" s="380" t="s">
         <v>226</v>
       </c>
-      <c r="K31" s="383"/>
-      <c r="L31" s="383"/>
-      <c r="M31" s="384"/>
+      <c r="K31" s="381"/>
+      <c r="L31" s="381"/>
+      <c r="M31" s="382"/>
       <c r="N31" s="150">
         <f>46433+500</f>
         <v>46933</v>
@@ -5741,11 +5744,11 @@
     <row r="32" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="20"/>
-      <c r="C32" s="372" t="s">
+      <c r="C32" s="370" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="373"/>
-      <c r="E32" s="374"/>
+      <c r="D32" s="371"/>
+      <c r="E32" s="372"/>
       <c r="F32" s="71">
         <f>SUM(F25:F31)</f>
         <v>37151</v>
@@ -5759,12 +5762,12 @@
         <v>25355</v>
       </c>
       <c r="I32" s="7"/>
-      <c r="J32" s="382" t="s">
+      <c r="J32" s="380" t="s">
         <v>227</v>
       </c>
-      <c r="K32" s="383"/>
-      <c r="L32" s="383"/>
-      <c r="M32" s="384"/>
+      <c r="K32" s="381"/>
+      <c r="L32" s="381"/>
+      <c r="M32" s="382"/>
       <c r="N32" s="150">
         <v>1514</v>
       </c>
@@ -5777,10 +5780,10 @@
       <c r="A33" s="3"/>
       <c r="B33" s="20"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="382"/>
-      <c r="K33" s="383"/>
-      <c r="L33" s="383"/>
-      <c r="M33" s="384"/>
+      <c r="J33" s="380"/>
+      <c r="K33" s="381"/>
+      <c r="L33" s="381"/>
+      <c r="M33" s="382"/>
       <c r="N33" s="152"/>
       <c r="O33" s="61"/>
       <c r="P33" s="61"/>
@@ -5791,11 +5794,11 @@
     <row r="34" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="20"/>
-      <c r="C34" s="397" t="s">
+      <c r="C34" s="395" t="s">
         <v>103</v>
       </c>
-      <c r="D34" s="398"/>
-      <c r="E34" s="399"/>
+      <c r="D34" s="396"/>
+      <c r="E34" s="397"/>
       <c r="F34" s="77" t="str">
         <f>K1</f>
         <v>20.09.2026</v>
@@ -5807,12 +5810,12 @@
         <v>250</v>
       </c>
       <c r="I34" s="7"/>
-      <c r="J34" s="400" t="s">
+      <c r="J34" s="398" t="s">
         <v>140</v>
       </c>
-      <c r="K34" s="401"/>
-      <c r="L34" s="401"/>
-      <c r="M34" s="402"/>
+      <c r="K34" s="399"/>
+      <c r="L34" s="399"/>
+      <c r="M34" s="400"/>
       <c r="N34" s="163">
         <f>SUM(N26:N33)</f>
         <v>126589</v>
@@ -5871,11 +5874,11 @@
         <v>0</v>
       </c>
       <c r="I36" s="7"/>
-      <c r="J36" s="338" t="s">
+      <c r="J36" s="337" t="s">
         <v>156</v>
       </c>
-      <c r="K36" s="339"/>
-      <c r="L36" s="340"/>
+      <c r="K36" s="338"/>
+      <c r="L36" s="339"/>
       <c r="M36" s="112" t="s">
         <v>115</v>
       </c>
@@ -5888,10 +5891,10 @@
       <c r="P36" s="165" t="s">
         <v>138</v>
       </c>
-      <c r="Q36" s="447" t="s">
+      <c r="Q36" s="445" t="s">
         <v>149</v>
       </c>
-      <c r="R36" s="448"/>
+      <c r="R36" s="446"/>
       <c r="S36" s="61"/>
     </row>
     <row r="37" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5910,11 +5913,11 @@
       <c r="G37" s="134"/>
       <c r="H37" s="134"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="341" t="s">
+      <c r="J37" s="340" t="s">
         <v>229</v>
       </c>
-      <c r="K37" s="342"/>
-      <c r="L37" s="343"/>
+      <c r="K37" s="341"/>
+      <c r="L37" s="342"/>
       <c r="M37" s="149">
         <v>75204</v>
       </c>
@@ -5927,10 +5930,10 @@
       <c r="P37" s="256" t="s">
         <v>240</v>
       </c>
-      <c r="Q37" s="456" t="s">
+      <c r="Q37" s="454" t="s">
         <v>241</v>
       </c>
-      <c r="R37" s="456"/>
+      <c r="R37" s="454"/>
       <c r="S37" s="61"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5952,11 +5955,11 @@
       </c>
       <c r="H38" s="134"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="341" t="s">
+      <c r="J38" s="340" t="s">
         <v>213</v>
       </c>
-      <c r="K38" s="342"/>
-      <c r="L38" s="343"/>
+      <c r="K38" s="341"/>
+      <c r="L38" s="342"/>
       <c r="M38" s="149">
         <v>79700</v>
       </c>
@@ -5969,10 +5972,10 @@
       <c r="P38" s="256" t="s">
         <v>263</v>
       </c>
-      <c r="Q38" s="456" t="s">
+      <c r="Q38" s="454" t="s">
         <v>247</v>
       </c>
-      <c r="R38" s="456"/>
+      <c r="R38" s="454"/>
       <c r="S38" s="61"/>
     </row>
     <row r="39" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5994,11 +5997,11 @@
       </c>
       <c r="H39" s="134"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="341" t="s">
+      <c r="J39" s="340" t="s">
         <v>245</v>
       </c>
-      <c r="K39" s="342"/>
-      <c r="L39" s="343"/>
+      <c r="K39" s="341"/>
+      <c r="L39" s="342"/>
       <c r="M39" s="149">
         <v>75203</v>
       </c>
@@ -6009,10 +6012,10 @@
       <c r="P39" s="256" t="s">
         <v>216</v>
       </c>
-      <c r="Q39" s="456" t="s">
+      <c r="Q39" s="454" t="s">
         <v>246</v>
       </c>
-      <c r="R39" s="456"/>
+      <c r="R39" s="454"/>
       <c r="S39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6025,15 +6028,15 @@
       <c r="G40" s="134"/>
       <c r="H40" s="134"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="341"/>
-      <c r="K40" s="342"/>
-      <c r="L40" s="343"/>
+      <c r="J40" s="340"/>
+      <c r="K40" s="341"/>
+      <c r="L40" s="342"/>
       <c r="M40" s="149"/>
       <c r="N40" s="149"/>
       <c r="O40" s="265"/>
       <c r="P40" s="256"/>
-      <c r="Q40" s="451"/>
-      <c r="R40" s="452"/>
+      <c r="Q40" s="449"/>
+      <c r="R40" s="450"/>
       <c r="S40" s="61"/>
     </row>
     <row r="41" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6046,11 +6049,11 @@
       <c r="G41" s="134"/>
       <c r="H41" s="134"/>
       <c r="I41" s="7"/>
-      <c r="J41" s="455" t="s">
+      <c r="J41" s="453" t="s">
         <v>208</v>
       </c>
-      <c r="K41" s="455"/>
-      <c r="L41" s="455"/>
+      <c r="K41" s="453"/>
+      <c r="L41" s="453"/>
       <c r="M41" s="149">
         <v>59695</v>
       </c>
@@ -6063,10 +6066,10 @@
       <c r="P41" s="256" t="s">
         <v>306</v>
       </c>
-      <c r="Q41" s="456" t="s">
+      <c r="Q41" s="454" t="s">
         <v>215</v>
       </c>
-      <c r="R41" s="456"/>
+      <c r="R41" s="454"/>
       <c r="S41" s="61"/>
     </row>
     <row r="42" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6079,11 +6082,11 @@
       <c r="G42" s="134"/>
       <c r="H42" s="134"/>
       <c r="I42" s="7"/>
-      <c r="J42" s="455" t="s">
+      <c r="J42" s="453" t="s">
         <v>237</v>
       </c>
-      <c r="K42" s="455"/>
-      <c r="L42" s="455"/>
+      <c r="K42" s="453"/>
+      <c r="L42" s="453"/>
       <c r="M42" s="149">
         <v>53000</v>
       </c>
@@ -6094,10 +6097,10 @@
       <c r="P42" s="256" t="s">
         <v>216</v>
       </c>
-      <c r="Q42" s="456" t="s">
+      <c r="Q42" s="454" t="s">
         <v>239</v>
       </c>
-      <c r="R42" s="456"/>
+      <c r="R42" s="454"/>
       <c r="S42" s="61"/>
     </row>
     <row r="43" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6121,20 +6124,20 @@
         <v>0</v>
       </c>
       <c r="I43" s="7"/>
-      <c r="J43" s="457" t="s">
+      <c r="J43" s="455" t="s">
         <v>98</v>
       </c>
-      <c r="K43" s="458"/>
-      <c r="L43" s="458"/>
-      <c r="M43" s="458"/>
+      <c r="K43" s="456"/>
+      <c r="L43" s="456"/>
+      <c r="M43" s="456"/>
       <c r="N43" s="166"/>
       <c r="O43" s="167">
         <f>SUM(N37:N42)</f>
         <v>38048</v>
       </c>
       <c r="P43" s="254"/>
-      <c r="Q43" s="449"/>
-      <c r="R43" s="449"/>
+      <c r="Q43" s="447"/>
+      <c r="R43" s="447"/>
       <c r="S43" s="61"/>
     </row>
     <row r="44" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6148,25 +6151,25 @@
       </c>
       <c r="E44" s="129"/>
       <c r="F44" s="129"/>
-      <c r="G44" s="325">
+      <c r="G44" s="135">
         <v>1</v>
       </c>
       <c r="H44" s="136"/>
       <c r="I44" s="7"/>
-      <c r="J44" s="388" t="s">
+      <c r="J44" s="386" t="s">
         <v>99</v>
       </c>
-      <c r="K44" s="389"/>
-      <c r="L44" s="389"/>
-      <c r="M44" s="389"/>
-      <c r="N44" s="390"/>
+      <c r="K44" s="387"/>
+      <c r="L44" s="387"/>
+      <c r="M44" s="387"/>
+      <c r="N44" s="388"/>
       <c r="O44" s="148">
         <f>N22+N34+O43</f>
         <v>428749</v>
       </c>
       <c r="P44" s="255"/>
-      <c r="Q44" s="450"/>
-      <c r="R44" s="450"/>
+      <c r="Q44" s="448"/>
+      <c r="R44" s="448"/>
       <c r="S44" s="61"/>
     </row>
     <row r="45" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6211,15 +6214,15 @@
       </c>
       <c r="F46" s="129"/>
       <c r="G46" s="135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="134">
         <v>5</v>
       </c>
-      <c r="J46" s="459" t="s">
+      <c r="J46" s="457" t="s">
         <v>102</v>
       </c>
-      <c r="K46" s="460"/>
+      <c r="K46" s="458"/>
       <c r="L46" s="116" t="s">
         <v>1</v>
       </c>
@@ -6248,19 +6251,21 @@
       <c r="C47" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="130"/>
+      <c r="D47" s="130">
+        <v>2</v>
+      </c>
       <c r="E47" s="130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F47" s="130"/>
       <c r="G47" s="137"/>
       <c r="H47" s="134">
         <v>2</v>
       </c>
-      <c r="J47" s="355" t="s">
+      <c r="J47" s="353" t="s">
         <v>15</v>
       </c>
-      <c r="K47" s="356"/>
+      <c r="K47" s="354"/>
       <c r="L47" s="156">
         <v>48.71</v>
       </c>
@@ -6294,11 +6299,11 @@
       </c>
       <c r="D48" s="131">
         <f>SUM(D36:D47)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E48" s="131">
         <f>SUM(E36:E47)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F48" s="131">
         <f t="shared" si="1"/>
@@ -6306,16 +6311,16 @@
       </c>
       <c r="G48" s="138">
         <f>SUM(G36:G47)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H48" s="139">
         <f>SUM(H36:H47)</f>
         <v>7</v>
       </c>
-      <c r="J48" s="355" t="s">
+      <c r="J48" s="353" t="s">
         <v>16</v>
       </c>
-      <c r="K48" s="356"/>
+      <c r="K48" s="354"/>
       <c r="L48" s="156">
         <v>45.113999999999997</v>
       </c>
@@ -6351,10 +6356,10 @@
       <c r="F49" s="80"/>
       <c r="G49" s="84"/>
       <c r="H49" s="85"/>
-      <c r="J49" s="355" t="s">
+      <c r="J49" s="353" t="s">
         <v>17</v>
       </c>
-      <c r="K49" s="356"/>
+      <c r="K49" s="354"/>
       <c r="L49" s="156">
         <f>(L47-L48)/L47*100</f>
         <v>7.3824676657770549</v>
@@ -6401,10 +6406,10 @@
         <v>3</v>
       </c>
       <c r="I50" s="64"/>
-      <c r="J50" s="369" t="s">
+      <c r="J50" s="367" t="s">
         <v>18</v>
       </c>
-      <c r="K50" s="370"/>
+      <c r="K50" s="368"/>
       <c r="L50" s="156">
         <f>F13/L47/1000</f>
         <v>0.76269759802915216</v>
@@ -6452,17 +6457,17 @@
       </c>
       <c r="J51" s="140"/>
       <c r="K51" s="141"/>
-      <c r="L51" s="355" t="s">
+      <c r="L51" s="353" t="s">
         <v>145</v>
       </c>
-      <c r="M51" s="356"/>
-      <c r="N51" s="357"/>
+      <c r="M51" s="354"/>
+      <c r="N51" s="355"/>
       <c r="O51" s="158">
         <v>240.27</v>
       </c>
       <c r="P51" s="142"/>
-      <c r="Q51" s="453"/>
-      <c r="R51" s="454"/>
+      <c r="Q51" s="451"/>
+      <c r="R51" s="452"/>
       <c r="S51" s="109"/>
     </row>
     <row r="52" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6482,24 +6487,24 @@
     </row>
     <row r="53" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="B53" s="352" t="s">
+      <c r="B53" s="350" t="s">
         <v>134</v>
       </c>
-      <c r="C53" s="353"/>
-      <c r="D53" s="353"/>
-      <c r="E53" s="353"/>
-      <c r="F53" s="353"/>
-      <c r="G53" s="354"/>
+      <c r="C53" s="351"/>
+      <c r="D53" s="351"/>
+      <c r="E53" s="351"/>
+      <c r="F53" s="351"/>
+      <c r="G53" s="352"/>
       <c r="H53" s="68"/>
-      <c r="J53" s="352" t="s">
+      <c r="J53" s="350" t="s">
         <v>135</v>
       </c>
-      <c r="K53" s="353"/>
-      <c r="L53" s="353"/>
-      <c r="M53" s="353"/>
-      <c r="N53" s="353"/>
-      <c r="O53" s="353"/>
-      <c r="P53" s="354"/>
+      <c r="K53" s="351"/>
+      <c r="L53" s="351"/>
+      <c r="M53" s="351"/>
+      <c r="N53" s="351"/>
+      <c r="O53" s="351"/>
+      <c r="P53" s="352"/>
       <c r="Q53" s="60"/>
       <c r="R53" s="60"/>
       <c r="S53" s="60"/>
@@ -6509,33 +6514,33 @@
       <c r="B54" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="348" t="s">
+      <c r="C54" s="346" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="349"/>
+      <c r="D54" s="347"/>
       <c r="E54" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F54" s="327" t="s">
+      <c r="F54" s="326" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="329"/>
+      <c r="G54" s="328"/>
       <c r="H54" s="60"/>
       <c r="J54" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="K54" s="371" t="s">
+      <c r="K54" s="369" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="371"/>
-      <c r="M54" s="371"/>
+      <c r="L54" s="369"/>
+      <c r="M54" s="369"/>
       <c r="N54" s="159" t="s">
         <v>142</v>
       </c>
-      <c r="O54" s="350" t="s">
+      <c r="O54" s="348" t="s">
         <v>22</v>
       </c>
-      <c r="P54" s="351"/>
+      <c r="P54" s="349"/>
       <c r="Q54" s="60"/>
       <c r="R54" s="60"/>
       <c r="S54" s="60"/>
@@ -6545,33 +6550,33 @@
       <c r="B55" s="182">
         <v>1</v>
       </c>
-      <c r="C55" s="327" t="s">
+      <c r="C55" s="326" t="s">
         <v>255</v>
       </c>
-      <c r="D55" s="328"/>
+      <c r="D55" s="327"/>
       <c r="E55" s="258" t="s">
         <v>254</v>
       </c>
-      <c r="F55" s="327" t="s">
+      <c r="F55" s="326" t="s">
         <v>248</v>
       </c>
-      <c r="G55" s="329"/>
+      <c r="G55" s="328"/>
       <c r="H55" s="44"/>
       <c r="J55" s="257">
         <v>1</v>
       </c>
-      <c r="K55" s="330" t="s">
+      <c r="K55" s="329" t="s">
         <v>194</v>
       </c>
-      <c r="L55" s="330"/>
-      <c r="M55" s="330"/>
+      <c r="L55" s="329"/>
+      <c r="M55" s="329"/>
       <c r="N55" s="258" t="s">
         <v>256</v>
       </c>
-      <c r="O55" s="330" t="s">
+      <c r="O55" s="329" t="s">
         <v>304</v>
       </c>
-      <c r="P55" s="330"/>
+      <c r="P55" s="329"/>
       <c r="Q55" s="60"/>
       <c r="R55" s="60"/>
       <c r="S55" s="60"/>
@@ -6581,33 +6586,33 @@
       <c r="B56" s="305">
         <v>2</v>
       </c>
-      <c r="C56" s="327" t="s">
+      <c r="C56" s="326" t="s">
         <v>252</v>
       </c>
-      <c r="D56" s="328"/>
+      <c r="D56" s="327"/>
       <c r="E56" s="169" t="s">
         <v>253</v>
       </c>
-      <c r="F56" s="327" t="s">
+      <c r="F56" s="326" t="s">
         <v>248</v>
       </c>
-      <c r="G56" s="329"/>
+      <c r="G56" s="328"/>
       <c r="H56" s="44"/>
       <c r="J56" s="306">
         <v>2</v>
       </c>
-      <c r="K56" s="330" t="s">
+      <c r="K56" s="329" t="s">
         <v>194</v>
       </c>
-      <c r="L56" s="330"/>
-      <c r="M56" s="330"/>
+      <c r="L56" s="329"/>
+      <c r="M56" s="329"/>
       <c r="N56" s="258" t="s">
         <v>257</v>
       </c>
-      <c r="O56" s="330" t="s">
+      <c r="O56" s="329" t="s">
         <v>305</v>
       </c>
-      <c r="P56" s="330"/>
+      <c r="P56" s="329"/>
       <c r="Q56" s="60"/>
       <c r="R56" s="60"/>
       <c r="S56" s="60"/>
@@ -6617,33 +6622,33 @@
       <c r="B57" s="316">
         <v>3</v>
       </c>
-      <c r="C57" s="327" t="s">
+      <c r="C57" s="326" t="s">
         <v>259</v>
       </c>
-      <c r="D57" s="328"/>
+      <c r="D57" s="327"/>
       <c r="E57" s="169" t="s">
         <v>260</v>
       </c>
-      <c r="F57" s="327" t="s">
+      <c r="F57" s="326" t="s">
         <v>307</v>
       </c>
-      <c r="G57" s="329"/>
+      <c r="G57" s="328"/>
       <c r="H57" s="44"/>
       <c r="J57" s="315">
         <v>3</v>
       </c>
-      <c r="K57" s="330" t="s">
+      <c r="K57" s="329" t="s">
         <v>261</v>
       </c>
-      <c r="L57" s="330"/>
-      <c r="M57" s="330"/>
+      <c r="L57" s="329"/>
+      <c r="M57" s="329"/>
       <c r="N57" s="258" t="s">
         <v>262</v>
       </c>
-      <c r="O57" s="330" t="s">
+      <c r="O57" s="329" t="s">
         <v>233</v>
       </c>
-      <c r="P57" s="330"/>
+      <c r="P57" s="329"/>
       <c r="Q57" s="60"/>
       <c r="R57" s="60"/>
       <c r="S57" s="60"/>
@@ -6653,17 +6658,17 @@
       <c r="B58" s="324">
         <v>4</v>
       </c>
-      <c r="C58" s="327" t="s">
+      <c r="C58" s="326" t="s">
         <v>302</v>
       </c>
-      <c r="D58" s="328"/>
+      <c r="D58" s="327"/>
       <c r="E58" s="169" t="s">
         <v>303</v>
       </c>
-      <c r="F58" s="327" t="s">
+      <c r="F58" s="326" t="s">
         <v>233</v>
       </c>
-      <c r="G58" s="329"/>
+      <c r="G58" s="328"/>
       <c r="H58" s="44"/>
       <c r="J58" s="275"/>
       <c r="K58" s="275"/>
@@ -6696,27 +6701,27 @@
       <c r="R59" s="60"/>
       <c r="S59" s="60"/>
     </row>
-    <row r="60" spans="1:19" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
-      <c r="B60" s="344" t="s">
+      <c r="B60" s="585" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="344"/>
-      <c r="D60" s="344"/>
-      <c r="E60" s="344"/>
-      <c r="F60" s="344"/>
-      <c r="G60" s="344"/>
-      <c r="H60" s="344"/>
-      <c r="I60" s="344"/>
-      <c r="J60" s="344"/>
-      <c r="K60" s="344"/>
-      <c r="L60" s="344"/>
-      <c r="M60" s="344"/>
-      <c r="N60" s="344"/>
-      <c r="O60" s="344"/>
-      <c r="P60" s="344"/>
-    </row>
-    <row r="61" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="585"/>
+      <c r="D60" s="585"/>
+      <c r="E60" s="585"/>
+      <c r="F60" s="585"/>
+      <c r="G60" s="585"/>
+      <c r="H60" s="585"/>
+      <c r="I60" s="585"/>
+      <c r="J60" s="585"/>
+      <c r="K60" s="585"/>
+      <c r="L60" s="585"/>
+      <c r="M60" s="585"/>
+      <c r="N60" s="585"/>
+      <c r="O60" s="585"/>
+      <c r="P60" s="585"/>
+    </row>
+    <row r="61" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
       <c r="B61" s="253"/>
       <c r="C61" s="253"/>
@@ -6736,46 +6741,46 @@
     </row>
     <row r="62" spans="1:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="3"/>
-      <c r="C62" s="326" t="s">
+      <c r="C62" s="325" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="326"/>
-      <c r="E62" s="326"/>
-      <c r="F62" s="326"/>
+      <c r="D62" s="325"/>
+      <c r="E62" s="325"/>
+      <c r="F62" s="325"/>
       <c r="G62" s="40"/>
       <c r="H62" s="40"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="326" t="s">
+      <c r="J62" s="325" t="s">
         <v>89</v>
       </c>
-      <c r="K62" s="326"/>
-      <c r="L62" s="326"/>
-      <c r="M62" s="326"/>
-      <c r="N62" s="326"/>
+      <c r="K62" s="325"/>
+      <c r="L62" s="325"/>
+      <c r="M62" s="325"/>
+      <c r="N62" s="325"/>
       <c r="O62" s="42"/>
     </row>
     <row r="63" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B63" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="337" t="s">
+      <c r="C63" s="336" t="s">
         <v>78</v>
       </c>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
       <c r="G63" s="40"/>
       <c r="H63" s="40"/>
       <c r="I63" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="J63" s="337" t="s">
+      <c r="J63" s="336" t="s">
         <v>78</v>
       </c>
-      <c r="K63" s="337"/>
-      <c r="L63" s="337"/>
-      <c r="M63" s="337"/>
-      <c r="N63" s="337"/>
+      <c r="K63" s="336"/>
+      <c r="L63" s="336"/>
+      <c r="M63" s="336"/>
+      <c r="N63" s="336"/>
       <c r="O63" s="42"/>
     </row>
     <row r="64" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
@@ -7235,11 +7240,11 @@
       <c r="G83" s="290"/>
       <c r="H83" s="279"/>
       <c r="I83" s="271"/>
-      <c r="J83" s="415"/>
-      <c r="K83" s="415"/>
-      <c r="L83" s="415"/>
-      <c r="M83" s="415"/>
-      <c r="N83" s="415"/>
+      <c r="J83" s="413"/>
+      <c r="K83" s="413"/>
+      <c r="L83" s="413"/>
+      <c r="M83" s="413"/>
+      <c r="N83" s="413"/>
       <c r="O83" s="281"/>
     </row>
     <row r="84" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7255,11 +7260,11 @@
       <c r="G84" s="290"/>
       <c r="H84" s="279"/>
       <c r="I84" s="271"/>
-      <c r="J84" s="415"/>
-      <c r="K84" s="415"/>
-      <c r="L84" s="415"/>
-      <c r="M84" s="415"/>
-      <c r="N84" s="415"/>
+      <c r="J84" s="413"/>
+      <c r="K84" s="413"/>
+      <c r="L84" s="413"/>
+      <c r="M84" s="413"/>
+      <c r="N84" s="413"/>
       <c r="O84" s="287"/>
     </row>
     <row r="85" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7319,14 +7324,14 @@
       <c r="I87" s="271">
         <v>1</v>
       </c>
-      <c r="J87" s="332" t="s">
+      <c r="J87" s="331" t="s">
         <v>264</v>
       </c>
-      <c r="K87" s="332"/>
-      <c r="L87" s="332"/>
-      <c r="M87" s="332"/>
-      <c r="N87" s="332"/>
-      <c r="O87" s="332"/>
+      <c r="K87" s="331"/>
+      <c r="L87" s="331"/>
+      <c r="M87" s="331"/>
+      <c r="N87" s="331"/>
+      <c r="O87" s="331"/>
     </row>
     <row r="88" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="111">
@@ -7343,14 +7348,14 @@
       <c r="I88" s="271">
         <v>2</v>
       </c>
-      <c r="J88" s="332" t="s">
+      <c r="J88" s="331" t="s">
         <v>265</v>
       </c>
-      <c r="K88" s="332"/>
-      <c r="L88" s="332"/>
-      <c r="M88" s="332"/>
-      <c r="N88" s="332"/>
-      <c r="O88" s="332"/>
+      <c r="K88" s="331"/>
+      <c r="L88" s="331"/>
+      <c r="M88" s="331"/>
+      <c r="N88" s="331"/>
+      <c r="O88" s="331"/>
     </row>
     <row r="89" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="111">
@@ -7367,14 +7372,14 @@
       <c r="I89" s="271">
         <v>3</v>
       </c>
-      <c r="J89" s="332" t="s">
+      <c r="J89" s="331" t="s">
         <v>268</v>
       </c>
-      <c r="K89" s="332"/>
-      <c r="L89" s="332"/>
-      <c r="M89" s="332"/>
-      <c r="N89" s="332"/>
-      <c r="O89" s="332"/>
+      <c r="K89" s="331"/>
+      <c r="L89" s="331"/>
+      <c r="M89" s="331"/>
+      <c r="N89" s="331"/>
+      <c r="O89" s="331"/>
     </row>
     <row r="90" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="111"/>
@@ -7386,14 +7391,14 @@
       <c r="I90" s="271">
         <v>4</v>
       </c>
-      <c r="J90" s="332" t="s">
+      <c r="J90" s="331" t="s">
         <v>268</v>
       </c>
-      <c r="K90" s="332"/>
-      <c r="L90" s="332"/>
-      <c r="M90" s="332"/>
-      <c r="N90" s="332"/>
-      <c r="O90" s="332"/>
+      <c r="K90" s="331"/>
+      <c r="L90" s="331"/>
+      <c r="M90" s="331"/>
+      <c r="N90" s="331"/>
+      <c r="O90" s="331"/>
     </row>
     <row r="91" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="111"/>
@@ -7402,14 +7407,14 @@
       <c r="I91" s="271">
         <v>5</v>
       </c>
-      <c r="J91" s="332" t="s">
+      <c r="J91" s="331" t="s">
         <v>266</v>
       </c>
-      <c r="K91" s="332"/>
-      <c r="L91" s="332"/>
-      <c r="M91" s="332"/>
-      <c r="N91" s="332"/>
-      <c r="O91" s="332"/>
+      <c r="K91" s="331"/>
+      <c r="L91" s="331"/>
+      <c r="M91" s="331"/>
+      <c r="N91" s="331"/>
+      <c r="O91" s="331"/>
     </row>
     <row r="92" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="111"/>
@@ -7421,14 +7426,14 @@
       <c r="I92" s="271">
         <v>6</v>
       </c>
-      <c r="J92" s="332" t="s">
+      <c r="J92" s="331" t="s">
         <v>267</v>
       </c>
-      <c r="K92" s="332"/>
-      <c r="L92" s="332"/>
-      <c r="M92" s="332"/>
-      <c r="N92" s="332"/>
-      <c r="O92" s="332"/>
+      <c r="K92" s="331"/>
+      <c r="L92" s="331"/>
+      <c r="M92" s="331"/>
+      <c r="N92" s="331"/>
+      <c r="O92" s="331"/>
       <c r="P92" s="266"/>
     </row>
     <row r="93" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7440,12 +7445,12 @@
       <c r="G93" s="289"/>
       <c r="H93" s="279"/>
       <c r="I93" s="271"/>
-      <c r="J93" s="332"/>
-      <c r="K93" s="332"/>
-      <c r="L93" s="332"/>
-      <c r="M93" s="332"/>
-      <c r="N93" s="332"/>
-      <c r="O93" s="332"/>
+      <c r="J93" s="331"/>
+      <c r="K93" s="331"/>
+      <c r="L93" s="331"/>
+      <c r="M93" s="331"/>
+      <c r="N93" s="331"/>
+      <c r="O93" s="331"/>
     </row>
     <row r="94" spans="2:16" ht="24" x14ac:dyDescent="0.15">
       <c r="B94" s="111"/>
@@ -7456,12 +7461,12 @@
       <c r="G94" s="289"/>
       <c r="H94" s="279"/>
       <c r="I94" s="271"/>
-      <c r="J94" s="332"/>
-      <c r="K94" s="332"/>
-      <c r="L94" s="332"/>
-      <c r="M94" s="332"/>
-      <c r="N94" s="332"/>
-      <c r="O94" s="332"/>
+      <c r="J94" s="331"/>
+      <c r="K94" s="331"/>
+      <c r="L94" s="331"/>
+      <c r="M94" s="331"/>
+      <c r="N94" s="331"/>
+      <c r="O94" s="331"/>
     </row>
     <row r="95" spans="2:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B95" s="111"/>
@@ -7472,12 +7477,12 @@
       <c r="G95" s="290"/>
       <c r="H95" s="279"/>
       <c r="I95" s="271"/>
-      <c r="J95" s="332"/>
-      <c r="K95" s="332"/>
-      <c r="L95" s="332"/>
-      <c r="M95" s="332"/>
-      <c r="N95" s="332"/>
-      <c r="O95" s="332"/>
+      <c r="J95" s="331"/>
+      <c r="K95" s="331"/>
+      <c r="L95" s="331"/>
+      <c r="M95" s="331"/>
+      <c r="N95" s="331"/>
+      <c r="O95" s="331"/>
     </row>
     <row r="96" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="111"/>
@@ -7487,11 +7492,11 @@
       <c r="G96" s="290"/>
       <c r="H96" s="279"/>
       <c r="I96" s="266"/>
-      <c r="J96" s="331"/>
-      <c r="K96" s="331"/>
-      <c r="L96" s="331"/>
-      <c r="M96" s="331"/>
-      <c r="N96" s="331"/>
+      <c r="J96" s="330"/>
+      <c r="K96" s="330"/>
+      <c r="L96" s="330"/>
+      <c r="M96" s="330"/>
+      <c r="N96" s="330"/>
       <c r="O96" s="39"/>
     </row>
     <row r="97" spans="2:15" ht="24" x14ac:dyDescent="0.2">
@@ -7501,11 +7506,11 @@
       <c r="F97" s="290"/>
       <c r="G97" s="290"/>
       <c r="H97" s="279"/>
-      <c r="J97" s="331"/>
-      <c r="K97" s="331"/>
-      <c r="L97" s="331"/>
-      <c r="M97" s="331"/>
-      <c r="N97" s="331"/>
+      <c r="J97" s="330"/>
+      <c r="K97" s="330"/>
+      <c r="L97" s="330"/>
+      <c r="M97" s="330"/>
+      <c r="N97" s="330"/>
       <c r="O97" s="39"/>
     </row>
     <row r="98" spans="2:15" ht="24" x14ac:dyDescent="0.2">
@@ -7515,11 +7520,11 @@
       <c r="F98" s="279"/>
       <c r="G98" s="279"/>
       <c r="H98" s="279"/>
-      <c r="J98" s="331"/>
-      <c r="K98" s="331"/>
-      <c r="L98" s="331"/>
-      <c r="M98" s="331"/>
-      <c r="N98" s="331"/>
+      <c r="J98" s="330"/>
+      <c r="K98" s="330"/>
+      <c r="L98" s="330"/>
+      <c r="M98" s="330"/>
+      <c r="N98" s="330"/>
       <c r="O98" s="39"/>
     </row>
     <row r="99" spans="2:15" ht="24" x14ac:dyDescent="0.15">
@@ -7530,11 +7535,11 @@
       <c r="F99" s="267"/>
       <c r="G99" s="267"/>
       <c r="H99" s="267"/>
-      <c r="J99" s="331"/>
-      <c r="K99" s="331"/>
-      <c r="L99" s="331"/>
-      <c r="M99" s="331"/>
-      <c r="N99" s="331"/>
+      <c r="J99" s="330"/>
+      <c r="K99" s="330"/>
+      <c r="L99" s="330"/>
+      <c r="M99" s="330"/>
+      <c r="N99" s="330"/>
       <c r="O99" s="39"/>
     </row>
     <row r="100" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7561,11 +7566,11 @@
       <c r="F101" s="251"/>
       <c r="G101" s="251"/>
       <c r="H101" s="251"/>
-      <c r="J101" s="331"/>
-      <c r="K101" s="331"/>
-      <c r="L101" s="331"/>
-      <c r="M101" s="331"/>
-      <c r="N101" s="331"/>
+      <c r="J101" s="330"/>
+      <c r="K101" s="330"/>
+      <c r="L101" s="330"/>
+      <c r="M101" s="330"/>
+      <c r="N101" s="330"/>
       <c r="O101" s="39"/>
     </row>
     <row r="102" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7576,11 +7581,11 @@
       <c r="F102" s="251"/>
       <c r="G102" s="251"/>
       <c r="H102" s="251"/>
-      <c r="J102" s="331"/>
-      <c r="K102" s="331"/>
-      <c r="L102" s="331"/>
-      <c r="M102" s="331"/>
-      <c r="N102" s="331"/>
+      <c r="J102" s="330"/>
+      <c r="K102" s="330"/>
+      <c r="L102" s="330"/>
+      <c r="M102" s="330"/>
+      <c r="N102" s="330"/>
       <c r="O102" s="39"/>
     </row>
     <row r="103" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7591,1251 +7596,1251 @@
       <c r="F103" s="251"/>
       <c r="G103" s="251"/>
       <c r="H103" s="251"/>
-      <c r="J103" s="331"/>
-      <c r="K103" s="331"/>
-      <c r="L103" s="331"/>
-      <c r="M103" s="331"/>
-      <c r="N103" s="331"/>
+      <c r="J103" s="330"/>
+      <c r="K103" s="330"/>
+      <c r="L103" s="330"/>
+      <c r="M103" s="330"/>
+      <c r="N103" s="330"/>
       <c r="O103" s="39"/>
     </row>
     <row r="104" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C104" s="333"/>
-      <c r="D104" s="333"/>
-      <c r="E104" s="333"/>
-      <c r="F104" s="333"/>
-      <c r="G104" s="333"/>
-      <c r="H104" s="333"/>
-      <c r="J104" s="331"/>
-      <c r="K104" s="331"/>
-      <c r="L104" s="331"/>
-      <c r="M104" s="331"/>
-      <c r="N104" s="331"/>
+      <c r="C104" s="332"/>
+      <c r="D104" s="332"/>
+      <c r="E104" s="332"/>
+      <c r="F104" s="332"/>
+      <c r="G104" s="332"/>
+      <c r="H104" s="332"/>
+      <c r="J104" s="330"/>
+      <c r="K104" s="330"/>
+      <c r="L104" s="330"/>
+      <c r="M104" s="330"/>
+      <c r="N104" s="330"/>
       <c r="O104" s="39"/>
     </row>
     <row r="105" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C105" s="333"/>
-      <c r="D105" s="333"/>
-      <c r="E105" s="333"/>
-      <c r="F105" s="333"/>
-      <c r="G105" s="333"/>
-      <c r="H105" s="333"/>
-      <c r="J105" s="331"/>
-      <c r="K105" s="331"/>
-      <c r="L105" s="331"/>
-      <c r="M105" s="331"/>
-      <c r="N105" s="331"/>
+      <c r="C105" s="332"/>
+      <c r="D105" s="332"/>
+      <c r="E105" s="332"/>
+      <c r="F105" s="332"/>
+      <c r="G105" s="332"/>
+      <c r="H105" s="332"/>
+      <c r="J105" s="330"/>
+      <c r="K105" s="330"/>
+      <c r="L105" s="330"/>
+      <c r="M105" s="330"/>
+      <c r="N105" s="330"/>
       <c r="O105" s="39"/>
     </row>
     <row r="106" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C106" s="333"/>
-      <c r="D106" s="333"/>
-      <c r="E106" s="333"/>
-      <c r="F106" s="333"/>
-      <c r="G106" s="333"/>
-      <c r="H106" s="333"/>
-      <c r="J106" s="331"/>
-      <c r="K106" s="331"/>
-      <c r="L106" s="331"/>
-      <c r="M106" s="331"/>
-      <c r="N106" s="331"/>
+      <c r="C106" s="332"/>
+      <c r="D106" s="332"/>
+      <c r="E106" s="332"/>
+      <c r="F106" s="332"/>
+      <c r="G106" s="332"/>
+      <c r="H106" s="332"/>
+      <c r="J106" s="330"/>
+      <c r="K106" s="330"/>
+      <c r="L106" s="330"/>
+      <c r="M106" s="330"/>
+      <c r="N106" s="330"/>
       <c r="O106" s="39"/>
     </row>
     <row r="107" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C107" s="333"/>
-      <c r="D107" s="333"/>
-      <c r="E107" s="333"/>
-      <c r="F107" s="333"/>
-      <c r="G107" s="333"/>
-      <c r="H107" s="333"/>
-      <c r="J107" s="331"/>
-      <c r="K107" s="331"/>
-      <c r="L107" s="331"/>
-      <c r="M107" s="331"/>
-      <c r="N107" s="331"/>
+      <c r="C107" s="332"/>
+      <c r="D107" s="332"/>
+      <c r="E107" s="332"/>
+      <c r="F107" s="332"/>
+      <c r="G107" s="332"/>
+      <c r="H107" s="332"/>
+      <c r="J107" s="330"/>
+      <c r="K107" s="330"/>
+      <c r="L107" s="330"/>
+      <c r="M107" s="330"/>
+      <c r="N107" s="330"/>
       <c r="O107" s="39"/>
     </row>
     <row r="108" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C108" s="333"/>
-      <c r="D108" s="333"/>
-      <c r="E108" s="333"/>
-      <c r="F108" s="333"/>
-      <c r="G108" s="333"/>
-      <c r="H108" s="333"/>
-      <c r="J108" s="331"/>
-      <c r="K108" s="331"/>
-      <c r="L108" s="331"/>
-      <c r="M108" s="331"/>
-      <c r="N108" s="331"/>
+      <c r="C108" s="332"/>
+      <c r="D108" s="332"/>
+      <c r="E108" s="332"/>
+      <c r="F108" s="332"/>
+      <c r="G108" s="332"/>
+      <c r="H108" s="332"/>
+      <c r="J108" s="330"/>
+      <c r="K108" s="330"/>
+      <c r="L108" s="330"/>
+      <c r="M108" s="330"/>
+      <c r="N108" s="330"/>
       <c r="O108" s="39"/>
     </row>
     <row r="109" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C109" s="333"/>
-      <c r="D109" s="333"/>
-      <c r="E109" s="333"/>
-      <c r="F109" s="333"/>
-      <c r="G109" s="333"/>
-      <c r="H109" s="333"/>
-      <c r="J109" s="331"/>
-      <c r="K109" s="331"/>
-      <c r="L109" s="331"/>
-      <c r="M109" s="331"/>
-      <c r="N109" s="331"/>
+      <c r="C109" s="332"/>
+      <c r="D109" s="332"/>
+      <c r="E109" s="332"/>
+      <c r="F109" s="332"/>
+      <c r="G109" s="332"/>
+      <c r="H109" s="332"/>
+      <c r="J109" s="330"/>
+      <c r="K109" s="330"/>
+      <c r="L109" s="330"/>
+      <c r="M109" s="330"/>
+      <c r="N109" s="330"/>
       <c r="O109" s="39"/>
     </row>
     <row r="110" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C110" s="333"/>
-      <c r="D110" s="333"/>
-      <c r="E110" s="333"/>
-      <c r="F110" s="333"/>
-      <c r="G110" s="333"/>
-      <c r="H110" s="333"/>
-      <c r="J110" s="331"/>
-      <c r="K110" s="331"/>
-      <c r="L110" s="331"/>
-      <c r="M110" s="331"/>
-      <c r="N110" s="331"/>
+      <c r="C110" s="332"/>
+      <c r="D110" s="332"/>
+      <c r="E110" s="332"/>
+      <c r="F110" s="332"/>
+      <c r="G110" s="332"/>
+      <c r="H110" s="332"/>
+      <c r="J110" s="330"/>
+      <c r="K110" s="330"/>
+      <c r="L110" s="330"/>
+      <c r="M110" s="330"/>
+      <c r="N110" s="330"/>
       <c r="O110" s="39"/>
     </row>
     <row r="111" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C111" s="333"/>
-      <c r="D111" s="333"/>
-      <c r="E111" s="333"/>
-      <c r="F111" s="333"/>
-      <c r="G111" s="333"/>
-      <c r="H111" s="333"/>
-      <c r="J111" s="331"/>
-      <c r="K111" s="331"/>
-      <c r="L111" s="331"/>
-      <c r="M111" s="331"/>
-      <c r="N111" s="331"/>
+      <c r="C111" s="332"/>
+      <c r="D111" s="332"/>
+      <c r="E111" s="332"/>
+      <c r="F111" s="332"/>
+      <c r="G111" s="332"/>
+      <c r="H111" s="332"/>
+      <c r="J111" s="330"/>
+      <c r="K111" s="330"/>
+      <c r="L111" s="330"/>
+      <c r="M111" s="330"/>
+      <c r="N111" s="330"/>
       <c r="O111" s="39"/>
     </row>
     <row r="112" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C112" s="333"/>
-      <c r="D112" s="333"/>
-      <c r="E112" s="333"/>
-      <c r="F112" s="333"/>
-      <c r="G112" s="333"/>
-      <c r="H112" s="333"/>
-      <c r="J112" s="331"/>
-      <c r="K112" s="331"/>
-      <c r="L112" s="331"/>
-      <c r="M112" s="331"/>
-      <c r="N112" s="331"/>
+      <c r="C112" s="332"/>
+      <c r="D112" s="332"/>
+      <c r="E112" s="332"/>
+      <c r="F112" s="332"/>
+      <c r="G112" s="332"/>
+      <c r="H112" s="332"/>
+      <c r="J112" s="330"/>
+      <c r="K112" s="330"/>
+      <c r="L112" s="330"/>
+      <c r="M112" s="330"/>
+      <c r="N112" s="330"/>
       <c r="O112" s="39"/>
     </row>
     <row r="113" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C113" s="333"/>
-      <c r="D113" s="333"/>
-      <c r="E113" s="333"/>
-      <c r="F113" s="333"/>
-      <c r="G113" s="333"/>
-      <c r="H113" s="333"/>
-      <c r="J113" s="331"/>
-      <c r="K113" s="331"/>
-      <c r="L113" s="331"/>
-      <c r="M113" s="331"/>
-      <c r="N113" s="331"/>
+      <c r="C113" s="332"/>
+      <c r="D113" s="332"/>
+      <c r="E113" s="332"/>
+      <c r="F113" s="332"/>
+      <c r="G113" s="332"/>
+      <c r="H113" s="332"/>
+      <c r="J113" s="330"/>
+      <c r="K113" s="330"/>
+      <c r="L113" s="330"/>
+      <c r="M113" s="330"/>
+      <c r="N113" s="330"/>
       <c r="O113" s="39"/>
     </row>
     <row r="114" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C114" s="333"/>
-      <c r="D114" s="333"/>
-      <c r="E114" s="333"/>
-      <c r="F114" s="333"/>
-      <c r="G114" s="333"/>
-      <c r="H114" s="333"/>
-      <c r="J114" s="331"/>
-      <c r="K114" s="331"/>
-      <c r="L114" s="331"/>
-      <c r="M114" s="331"/>
-      <c r="N114" s="331"/>
+      <c r="C114" s="332"/>
+      <c r="D114" s="332"/>
+      <c r="E114" s="332"/>
+      <c r="F114" s="332"/>
+      <c r="G114" s="332"/>
+      <c r="H114" s="332"/>
+      <c r="J114" s="330"/>
+      <c r="K114" s="330"/>
+      <c r="L114" s="330"/>
+      <c r="M114" s="330"/>
+      <c r="N114" s="330"/>
       <c r="O114" s="39"/>
     </row>
     <row r="115" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C115" s="333"/>
-      <c r="D115" s="333"/>
-      <c r="E115" s="333"/>
-      <c r="F115" s="333"/>
-      <c r="G115" s="333"/>
-      <c r="H115" s="333"/>
-      <c r="J115" s="331"/>
-      <c r="K115" s="331"/>
-      <c r="L115" s="331"/>
-      <c r="M115" s="331"/>
-      <c r="N115" s="331"/>
+      <c r="C115" s="332"/>
+      <c r="D115" s="332"/>
+      <c r="E115" s="332"/>
+      <c r="F115" s="332"/>
+      <c r="G115" s="332"/>
+      <c r="H115" s="332"/>
+      <c r="J115" s="330"/>
+      <c r="K115" s="330"/>
+      <c r="L115" s="330"/>
+      <c r="M115" s="330"/>
+      <c r="N115" s="330"/>
       <c r="O115" s="39"/>
     </row>
     <row r="116" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C116" s="333"/>
-      <c r="D116" s="333"/>
-      <c r="E116" s="333"/>
-      <c r="F116" s="333"/>
-      <c r="G116" s="333"/>
-      <c r="H116" s="333"/>
-      <c r="J116" s="331"/>
-      <c r="K116" s="331"/>
-      <c r="L116" s="331"/>
-      <c r="M116" s="331"/>
-      <c r="N116" s="331"/>
+      <c r="C116" s="332"/>
+      <c r="D116" s="332"/>
+      <c r="E116" s="332"/>
+      <c r="F116" s="332"/>
+      <c r="G116" s="332"/>
+      <c r="H116" s="332"/>
+      <c r="J116" s="330"/>
+      <c r="K116" s="330"/>
+      <c r="L116" s="330"/>
+      <c r="M116" s="330"/>
+      <c r="N116" s="330"/>
       <c r="O116" s="39"/>
     </row>
     <row r="117" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C117" s="333"/>
-      <c r="D117" s="333"/>
-      <c r="E117" s="333"/>
-      <c r="F117" s="333"/>
-      <c r="G117" s="333"/>
-      <c r="H117" s="333"/>
-      <c r="J117" s="331"/>
-      <c r="K117" s="331"/>
-      <c r="L117" s="331"/>
-      <c r="M117" s="331"/>
-      <c r="N117" s="331"/>
+      <c r="C117" s="332"/>
+      <c r="D117" s="332"/>
+      <c r="E117" s="332"/>
+      <c r="F117" s="332"/>
+      <c r="G117" s="332"/>
+      <c r="H117" s="332"/>
+      <c r="J117" s="330"/>
+      <c r="K117" s="330"/>
+      <c r="L117" s="330"/>
+      <c r="M117" s="330"/>
+      <c r="N117" s="330"/>
       <c r="O117" s="39"/>
     </row>
     <row r="118" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C118" s="333"/>
-      <c r="D118" s="333"/>
-      <c r="E118" s="333"/>
-      <c r="F118" s="333"/>
-      <c r="G118" s="333"/>
-      <c r="H118" s="333"/>
-      <c r="J118" s="331"/>
-      <c r="K118" s="331"/>
-      <c r="L118" s="331"/>
-      <c r="M118" s="331"/>
-      <c r="N118" s="331"/>
+      <c r="C118" s="332"/>
+      <c r="D118" s="332"/>
+      <c r="E118" s="332"/>
+      <c r="F118" s="332"/>
+      <c r="G118" s="332"/>
+      <c r="H118" s="332"/>
+      <c r="J118" s="330"/>
+      <c r="K118" s="330"/>
+      <c r="L118" s="330"/>
+      <c r="M118" s="330"/>
+      <c r="N118" s="330"/>
       <c r="O118" s="39"/>
     </row>
     <row r="119" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C119" s="333"/>
-      <c r="D119" s="333"/>
-      <c r="E119" s="333"/>
-      <c r="F119" s="333"/>
-      <c r="G119" s="333"/>
-      <c r="H119" s="333"/>
-      <c r="J119" s="331"/>
-      <c r="K119" s="331"/>
-      <c r="L119" s="331"/>
-      <c r="M119" s="331"/>
-      <c r="N119" s="331"/>
+      <c r="C119" s="332"/>
+      <c r="D119" s="332"/>
+      <c r="E119" s="332"/>
+      <c r="F119" s="332"/>
+      <c r="G119" s="332"/>
+      <c r="H119" s="332"/>
+      <c r="J119" s="330"/>
+      <c r="K119" s="330"/>
+      <c r="L119" s="330"/>
+      <c r="M119" s="330"/>
+      <c r="N119" s="330"/>
       <c r="O119" s="39"/>
     </row>
     <row r="120" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C120" s="333"/>
-      <c r="D120" s="333"/>
-      <c r="E120" s="333"/>
-      <c r="F120" s="333"/>
-      <c r="G120" s="333"/>
-      <c r="H120" s="333"/>
-      <c r="J120" s="331"/>
-      <c r="K120" s="331"/>
-      <c r="L120" s="331"/>
-      <c r="M120" s="331"/>
-      <c r="N120" s="331"/>
+      <c r="C120" s="332"/>
+      <c r="D120" s="332"/>
+      <c r="E120" s="332"/>
+      <c r="F120" s="332"/>
+      <c r="G120" s="332"/>
+      <c r="H120" s="332"/>
+      <c r="J120" s="330"/>
+      <c r="K120" s="330"/>
+      <c r="L120" s="330"/>
+      <c r="M120" s="330"/>
+      <c r="N120" s="330"/>
       <c r="O120" s="39"/>
     </row>
     <row r="121" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C121" s="333"/>
-      <c r="D121" s="333"/>
-      <c r="E121" s="333"/>
-      <c r="F121" s="333"/>
-      <c r="G121" s="333"/>
-      <c r="H121" s="333"/>
-      <c r="J121" s="331"/>
-      <c r="K121" s="331"/>
-      <c r="L121" s="331"/>
-      <c r="M121" s="331"/>
-      <c r="N121" s="331"/>
+      <c r="C121" s="332"/>
+      <c r="D121" s="332"/>
+      <c r="E121" s="332"/>
+      <c r="F121" s="332"/>
+      <c r="G121" s="332"/>
+      <c r="H121" s="332"/>
+      <c r="J121" s="330"/>
+      <c r="K121" s="330"/>
+      <c r="L121" s="330"/>
+      <c r="M121" s="330"/>
+      <c r="N121" s="330"/>
       <c r="O121" s="39"/>
     </row>
     <row r="122" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C122" s="333"/>
-      <c r="D122" s="333"/>
-      <c r="E122" s="333"/>
-      <c r="F122" s="333"/>
-      <c r="G122" s="333"/>
-      <c r="H122" s="333"/>
-      <c r="J122" s="331"/>
-      <c r="K122" s="331"/>
-      <c r="L122" s="331"/>
-      <c r="M122" s="331"/>
-      <c r="N122" s="331"/>
+      <c r="C122" s="332"/>
+      <c r="D122" s="332"/>
+      <c r="E122" s="332"/>
+      <c r="F122" s="332"/>
+      <c r="G122" s="332"/>
+      <c r="H122" s="332"/>
+      <c r="J122" s="330"/>
+      <c r="K122" s="330"/>
+      <c r="L122" s="330"/>
+      <c r="M122" s="330"/>
+      <c r="N122" s="330"/>
       <c r="O122" s="39"/>
     </row>
     <row r="123" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C123" s="333"/>
-      <c r="D123" s="333"/>
-      <c r="E123" s="333"/>
-      <c r="F123" s="333"/>
-      <c r="G123" s="333"/>
-      <c r="H123" s="333"/>
-      <c r="J123" s="331"/>
-      <c r="K123" s="331"/>
-      <c r="L123" s="331"/>
-      <c r="M123" s="331"/>
-      <c r="N123" s="331"/>
+      <c r="C123" s="332"/>
+      <c r="D123" s="332"/>
+      <c r="E123" s="332"/>
+      <c r="F123" s="332"/>
+      <c r="G123" s="332"/>
+      <c r="H123" s="332"/>
+      <c r="J123" s="330"/>
+      <c r="K123" s="330"/>
+      <c r="L123" s="330"/>
+      <c r="M123" s="330"/>
+      <c r="N123" s="330"/>
       <c r="O123" s="39"/>
     </row>
     <row r="124" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C124" s="333"/>
-      <c r="D124" s="333"/>
-      <c r="E124" s="333"/>
-      <c r="F124" s="333"/>
-      <c r="G124" s="333"/>
-      <c r="H124" s="333"/>
-      <c r="J124" s="331"/>
-      <c r="K124" s="331"/>
-      <c r="L124" s="331"/>
-      <c r="M124" s="331"/>
-      <c r="N124" s="331"/>
+      <c r="C124" s="332"/>
+      <c r="D124" s="332"/>
+      <c r="E124" s="332"/>
+      <c r="F124" s="332"/>
+      <c r="G124" s="332"/>
+      <c r="H124" s="332"/>
+      <c r="J124" s="330"/>
+      <c r="K124" s="330"/>
+      <c r="L124" s="330"/>
+      <c r="M124" s="330"/>
+      <c r="N124" s="330"/>
       <c r="O124" s="39"/>
     </row>
     <row r="125" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C125" s="333"/>
-      <c r="D125" s="333"/>
-      <c r="E125" s="333"/>
-      <c r="F125" s="333"/>
-      <c r="G125" s="333"/>
-      <c r="H125" s="333"/>
-      <c r="J125" s="331"/>
-      <c r="K125" s="331"/>
-      <c r="L125" s="331"/>
-      <c r="M125" s="331"/>
-      <c r="N125" s="331"/>
+      <c r="C125" s="332"/>
+      <c r="D125" s="332"/>
+      <c r="E125" s="332"/>
+      <c r="F125" s="332"/>
+      <c r="G125" s="332"/>
+      <c r="H125" s="332"/>
+      <c r="J125" s="330"/>
+      <c r="K125" s="330"/>
+      <c r="L125" s="330"/>
+      <c r="M125" s="330"/>
+      <c r="N125" s="330"/>
       <c r="O125" s="39"/>
     </row>
     <row r="126" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C126" s="333"/>
-      <c r="D126" s="333"/>
-      <c r="E126" s="333"/>
-      <c r="F126" s="333"/>
-      <c r="G126" s="333"/>
-      <c r="H126" s="333"/>
-      <c r="J126" s="331"/>
-      <c r="K126" s="331"/>
-      <c r="L126" s="331"/>
-      <c r="M126" s="331"/>
-      <c r="N126" s="331"/>
+      <c r="C126" s="332"/>
+      <c r="D126" s="332"/>
+      <c r="E126" s="332"/>
+      <c r="F126" s="332"/>
+      <c r="G126" s="332"/>
+      <c r="H126" s="332"/>
+      <c r="J126" s="330"/>
+      <c r="K126" s="330"/>
+      <c r="L126" s="330"/>
+      <c r="M126" s="330"/>
+      <c r="N126" s="330"/>
       <c r="O126" s="39"/>
     </row>
     <row r="127" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C127" s="333"/>
-      <c r="D127" s="333"/>
-      <c r="E127" s="333"/>
-      <c r="F127" s="333"/>
-      <c r="G127" s="333"/>
-      <c r="H127" s="333"/>
-      <c r="J127" s="331"/>
-      <c r="K127" s="331"/>
-      <c r="L127" s="331"/>
-      <c r="M127" s="331"/>
-      <c r="N127" s="331"/>
+      <c r="C127" s="332"/>
+      <c r="D127" s="332"/>
+      <c r="E127" s="332"/>
+      <c r="F127" s="332"/>
+      <c r="G127" s="332"/>
+      <c r="H127" s="332"/>
+      <c r="J127" s="330"/>
+      <c r="K127" s="330"/>
+      <c r="L127" s="330"/>
+      <c r="M127" s="330"/>
+      <c r="N127" s="330"/>
       <c r="O127" s="39"/>
     </row>
     <row r="128" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C128" s="333"/>
-      <c r="D128" s="333"/>
-      <c r="E128" s="333"/>
-      <c r="F128" s="333"/>
-      <c r="G128" s="333"/>
-      <c r="H128" s="333"/>
-      <c r="J128" s="331"/>
-      <c r="K128" s="331"/>
-      <c r="L128" s="331"/>
-      <c r="M128" s="331"/>
-      <c r="N128" s="331"/>
+      <c r="C128" s="332"/>
+      <c r="D128" s="332"/>
+      <c r="E128" s="332"/>
+      <c r="F128" s="332"/>
+      <c r="G128" s="332"/>
+      <c r="H128" s="332"/>
+      <c r="J128" s="330"/>
+      <c r="K128" s="330"/>
+      <c r="L128" s="330"/>
+      <c r="M128" s="330"/>
+      <c r="N128" s="330"/>
       <c r="O128" s="39"/>
     </row>
     <row r="129" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C129" s="333"/>
-      <c r="D129" s="333"/>
-      <c r="E129" s="333"/>
-      <c r="F129" s="333"/>
-      <c r="G129" s="333"/>
-      <c r="H129" s="333"/>
-      <c r="J129" s="331"/>
-      <c r="K129" s="331"/>
-      <c r="L129" s="331"/>
-      <c r="M129" s="331"/>
-      <c r="N129" s="331"/>
+      <c r="C129" s="332"/>
+      <c r="D129" s="332"/>
+      <c r="E129" s="332"/>
+      <c r="F129" s="332"/>
+      <c r="G129" s="332"/>
+      <c r="H129" s="332"/>
+      <c r="J129" s="330"/>
+      <c r="K129" s="330"/>
+      <c r="L129" s="330"/>
+      <c r="M129" s="330"/>
+      <c r="N129" s="330"/>
       <c r="O129" s="39"/>
     </row>
     <row r="130" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C130" s="333"/>
-      <c r="D130" s="333"/>
-      <c r="E130" s="333"/>
-      <c r="F130" s="333"/>
-      <c r="G130" s="333"/>
-      <c r="H130" s="333"/>
-      <c r="J130" s="331"/>
-      <c r="K130" s="331"/>
-      <c r="L130" s="331"/>
-      <c r="M130" s="331"/>
-      <c r="N130" s="331"/>
+      <c r="C130" s="332"/>
+      <c r="D130" s="332"/>
+      <c r="E130" s="332"/>
+      <c r="F130" s="332"/>
+      <c r="G130" s="332"/>
+      <c r="H130" s="332"/>
+      <c r="J130" s="330"/>
+      <c r="K130" s="330"/>
+      <c r="L130" s="330"/>
+      <c r="M130" s="330"/>
+      <c r="N130" s="330"/>
       <c r="O130" s="39"/>
     </row>
     <row r="131" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C131" s="333"/>
-      <c r="D131" s="333"/>
-      <c r="E131" s="333"/>
-      <c r="F131" s="333"/>
-      <c r="G131" s="333"/>
-      <c r="H131" s="333"/>
-      <c r="J131" s="331"/>
-      <c r="K131" s="331"/>
-      <c r="L131" s="331"/>
-      <c r="M131" s="331"/>
-      <c r="N131" s="331"/>
+      <c r="C131" s="332"/>
+      <c r="D131" s="332"/>
+      <c r="E131" s="332"/>
+      <c r="F131" s="332"/>
+      <c r="G131" s="332"/>
+      <c r="H131" s="332"/>
+      <c r="J131" s="330"/>
+      <c r="K131" s="330"/>
+      <c r="L131" s="330"/>
+      <c r="M131" s="330"/>
+      <c r="N131" s="330"/>
       <c r="O131" s="39"/>
     </row>
     <row r="132" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C132" s="333"/>
-      <c r="D132" s="333"/>
-      <c r="E132" s="333"/>
-      <c r="F132" s="333"/>
-      <c r="G132" s="333"/>
-      <c r="H132" s="333"/>
-      <c r="J132" s="331"/>
-      <c r="K132" s="331"/>
-      <c r="L132" s="331"/>
-      <c r="M132" s="331"/>
-      <c r="N132" s="331"/>
+      <c r="C132" s="332"/>
+      <c r="D132" s="332"/>
+      <c r="E132" s="332"/>
+      <c r="F132" s="332"/>
+      <c r="G132" s="332"/>
+      <c r="H132" s="332"/>
+      <c r="J132" s="330"/>
+      <c r="K132" s="330"/>
+      <c r="L132" s="330"/>
+      <c r="M132" s="330"/>
+      <c r="N132" s="330"/>
       <c r="O132" s="39"/>
     </row>
     <row r="133" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C133" s="333"/>
-      <c r="D133" s="333"/>
-      <c r="E133" s="333"/>
-      <c r="F133" s="333"/>
-      <c r="G133" s="333"/>
-      <c r="H133" s="333"/>
-      <c r="J133" s="331"/>
-      <c r="K133" s="331"/>
-      <c r="L133" s="331"/>
-      <c r="M133" s="331"/>
-      <c r="N133" s="331"/>
+      <c r="C133" s="332"/>
+      <c r="D133" s="332"/>
+      <c r="E133" s="332"/>
+      <c r="F133" s="332"/>
+      <c r="G133" s="332"/>
+      <c r="H133" s="332"/>
+      <c r="J133" s="330"/>
+      <c r="K133" s="330"/>
+      <c r="L133" s="330"/>
+      <c r="M133" s="330"/>
+      <c r="N133" s="330"/>
       <c r="O133" s="39"/>
     </row>
     <row r="134" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C134" s="333"/>
-      <c r="D134" s="333"/>
-      <c r="E134" s="333"/>
-      <c r="F134" s="333"/>
-      <c r="G134" s="333"/>
-      <c r="H134" s="333"/>
-      <c r="J134" s="331"/>
-      <c r="K134" s="331"/>
-      <c r="L134" s="331"/>
-      <c r="M134" s="331"/>
-      <c r="N134" s="331"/>
+      <c r="C134" s="332"/>
+      <c r="D134" s="332"/>
+      <c r="E134" s="332"/>
+      <c r="F134" s="332"/>
+      <c r="G134" s="332"/>
+      <c r="H134" s="332"/>
+      <c r="J134" s="330"/>
+      <c r="K134" s="330"/>
+      <c r="L134" s="330"/>
+      <c r="M134" s="330"/>
+      <c r="N134" s="330"/>
       <c r="O134" s="39"/>
     </row>
     <row r="135" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C135" s="333"/>
-      <c r="D135" s="333"/>
-      <c r="E135" s="333"/>
-      <c r="F135" s="333"/>
-      <c r="G135" s="333"/>
-      <c r="H135" s="333"/>
-      <c r="J135" s="331"/>
-      <c r="K135" s="331"/>
-      <c r="L135" s="331"/>
-      <c r="M135" s="331"/>
-      <c r="N135" s="331"/>
+      <c r="C135" s="332"/>
+      <c r="D135" s="332"/>
+      <c r="E135" s="332"/>
+      <c r="F135" s="332"/>
+      <c r="G135" s="332"/>
+      <c r="H135" s="332"/>
+      <c r="J135" s="330"/>
+      <c r="K135" s="330"/>
+      <c r="L135" s="330"/>
+      <c r="M135" s="330"/>
+      <c r="N135" s="330"/>
       <c r="O135" s="39"/>
     </row>
     <row r="136" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C136" s="333"/>
-      <c r="D136" s="333"/>
-      <c r="E136" s="333"/>
-      <c r="F136" s="333"/>
-      <c r="G136" s="333"/>
-      <c r="H136" s="333"/>
-      <c r="J136" s="331"/>
-      <c r="K136" s="331"/>
-      <c r="L136" s="331"/>
-      <c r="M136" s="331"/>
-      <c r="N136" s="331"/>
+      <c r="C136" s="332"/>
+      <c r="D136" s="332"/>
+      <c r="E136" s="332"/>
+      <c r="F136" s="332"/>
+      <c r="G136" s="332"/>
+      <c r="H136" s="332"/>
+      <c r="J136" s="330"/>
+      <c r="K136" s="330"/>
+      <c r="L136" s="330"/>
+      <c r="M136" s="330"/>
+      <c r="N136" s="330"/>
       <c r="O136" s="39"/>
     </row>
     <row r="137" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C137" s="333"/>
-      <c r="D137" s="333"/>
-      <c r="E137" s="333"/>
-      <c r="F137" s="333"/>
-      <c r="G137" s="333"/>
-      <c r="H137" s="333"/>
-      <c r="J137" s="331"/>
-      <c r="K137" s="331"/>
-      <c r="L137" s="331"/>
-      <c r="M137" s="331"/>
-      <c r="N137" s="331"/>
+      <c r="C137" s="332"/>
+      <c r="D137" s="332"/>
+      <c r="E137" s="332"/>
+      <c r="F137" s="332"/>
+      <c r="G137" s="332"/>
+      <c r="H137" s="332"/>
+      <c r="J137" s="330"/>
+      <c r="K137" s="330"/>
+      <c r="L137" s="330"/>
+      <c r="M137" s="330"/>
+      <c r="N137" s="330"/>
       <c r="O137" s="39"/>
     </row>
     <row r="138" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C138" s="333"/>
-      <c r="D138" s="333"/>
-      <c r="E138" s="333"/>
-      <c r="F138" s="333"/>
-      <c r="G138" s="333"/>
-      <c r="H138" s="333"/>
-      <c r="J138" s="331"/>
-      <c r="K138" s="331"/>
-      <c r="L138" s="331"/>
-      <c r="M138" s="331"/>
-      <c r="N138" s="331"/>
+      <c r="C138" s="332"/>
+      <c r="D138" s="332"/>
+      <c r="E138" s="332"/>
+      <c r="F138" s="332"/>
+      <c r="G138" s="332"/>
+      <c r="H138" s="332"/>
+      <c r="J138" s="330"/>
+      <c r="K138" s="330"/>
+      <c r="L138" s="330"/>
+      <c r="M138" s="330"/>
+      <c r="N138" s="330"/>
       <c r="O138" s="39"/>
     </row>
     <row r="139" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C139" s="333"/>
-      <c r="D139" s="333"/>
-      <c r="E139" s="333"/>
-      <c r="F139" s="333"/>
-      <c r="G139" s="333"/>
-      <c r="H139" s="333"/>
-      <c r="J139" s="331"/>
-      <c r="K139" s="331"/>
-      <c r="L139" s="331"/>
-      <c r="M139" s="331"/>
-      <c r="N139" s="331"/>
+      <c r="C139" s="332"/>
+      <c r="D139" s="332"/>
+      <c r="E139" s="332"/>
+      <c r="F139" s="332"/>
+      <c r="G139" s="332"/>
+      <c r="H139" s="332"/>
+      <c r="J139" s="330"/>
+      <c r="K139" s="330"/>
+      <c r="L139" s="330"/>
+      <c r="M139" s="330"/>
+      <c r="N139" s="330"/>
       <c r="O139" s="39"/>
     </row>
     <row r="140" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C140" s="333"/>
-      <c r="D140" s="333"/>
-      <c r="E140" s="333"/>
-      <c r="F140" s="333"/>
-      <c r="G140" s="333"/>
-      <c r="H140" s="333"/>
-      <c r="J140" s="331"/>
-      <c r="K140" s="331"/>
-      <c r="L140" s="331"/>
-      <c r="M140" s="331"/>
-      <c r="N140" s="331"/>
+      <c r="C140" s="332"/>
+      <c r="D140" s="332"/>
+      <c r="E140" s="332"/>
+      <c r="F140" s="332"/>
+      <c r="G140" s="332"/>
+      <c r="H140" s="332"/>
+      <c r="J140" s="330"/>
+      <c r="K140" s="330"/>
+      <c r="L140" s="330"/>
+      <c r="M140" s="330"/>
+      <c r="N140" s="330"/>
       <c r="O140" s="39"/>
     </row>
     <row r="141" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C141" s="333"/>
-      <c r="D141" s="333"/>
-      <c r="E141" s="333"/>
-      <c r="F141" s="333"/>
-      <c r="G141" s="333"/>
-      <c r="H141" s="333"/>
-      <c r="J141" s="331"/>
-      <c r="K141" s="331"/>
-      <c r="L141" s="331"/>
-      <c r="M141" s="331"/>
-      <c r="N141" s="331"/>
+      <c r="C141" s="332"/>
+      <c r="D141" s="332"/>
+      <c r="E141" s="332"/>
+      <c r="F141" s="332"/>
+      <c r="G141" s="332"/>
+      <c r="H141" s="332"/>
+      <c r="J141" s="330"/>
+      <c r="K141" s="330"/>
+      <c r="L141" s="330"/>
+      <c r="M141" s="330"/>
+      <c r="N141" s="330"/>
       <c r="O141" s="39"/>
     </row>
     <row r="142" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C142" s="333"/>
-      <c r="D142" s="333"/>
-      <c r="E142" s="333"/>
-      <c r="F142" s="333"/>
-      <c r="G142" s="333"/>
-      <c r="H142" s="333"/>
-      <c r="J142" s="331"/>
-      <c r="K142" s="331"/>
-      <c r="L142" s="331"/>
-      <c r="M142" s="331"/>
-      <c r="N142" s="331"/>
+      <c r="C142" s="332"/>
+      <c r="D142" s="332"/>
+      <c r="E142" s="332"/>
+      <c r="F142" s="332"/>
+      <c r="G142" s="332"/>
+      <c r="H142" s="332"/>
+      <c r="J142" s="330"/>
+      <c r="K142" s="330"/>
+      <c r="L142" s="330"/>
+      <c r="M142" s="330"/>
+      <c r="N142" s="330"/>
       <c r="O142" s="39"/>
     </row>
     <row r="143" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C143" s="333"/>
-      <c r="D143" s="333"/>
-      <c r="E143" s="333"/>
-      <c r="F143" s="333"/>
-      <c r="G143" s="333"/>
-      <c r="H143" s="333"/>
-      <c r="J143" s="331"/>
-      <c r="K143" s="331"/>
-      <c r="L143" s="331"/>
-      <c r="M143" s="331"/>
-      <c r="N143" s="331"/>
+      <c r="C143" s="332"/>
+      <c r="D143" s="332"/>
+      <c r="E143" s="332"/>
+      <c r="F143" s="332"/>
+      <c r="G143" s="332"/>
+      <c r="H143" s="332"/>
+      <c r="J143" s="330"/>
+      <c r="K143" s="330"/>
+      <c r="L143" s="330"/>
+      <c r="M143" s="330"/>
+      <c r="N143" s="330"/>
       <c r="O143" s="39"/>
     </row>
     <row r="144" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C144" s="333"/>
-      <c r="D144" s="333"/>
-      <c r="E144" s="333"/>
-      <c r="F144" s="333"/>
-      <c r="G144" s="333"/>
-      <c r="H144" s="333"/>
-      <c r="J144" s="331"/>
-      <c r="K144" s="331"/>
-      <c r="L144" s="331"/>
-      <c r="M144" s="331"/>
-      <c r="N144" s="331"/>
+      <c r="C144" s="332"/>
+      <c r="D144" s="332"/>
+      <c r="E144" s="332"/>
+      <c r="F144" s="332"/>
+      <c r="G144" s="332"/>
+      <c r="H144" s="332"/>
+      <c r="J144" s="330"/>
+      <c r="K144" s="330"/>
+      <c r="L144" s="330"/>
+      <c r="M144" s="330"/>
+      <c r="N144" s="330"/>
       <c r="O144" s="39"/>
     </row>
     <row r="145" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C145" s="333"/>
-      <c r="D145" s="333"/>
-      <c r="E145" s="333"/>
-      <c r="F145" s="333"/>
-      <c r="G145" s="333"/>
-      <c r="H145" s="333"/>
-      <c r="J145" s="331"/>
-      <c r="K145" s="331"/>
-      <c r="L145" s="331"/>
-      <c r="M145" s="331"/>
-      <c r="N145" s="331"/>
+      <c r="C145" s="332"/>
+      <c r="D145" s="332"/>
+      <c r="E145" s="332"/>
+      <c r="F145" s="332"/>
+      <c r="G145" s="332"/>
+      <c r="H145" s="332"/>
+      <c r="J145" s="330"/>
+      <c r="K145" s="330"/>
+      <c r="L145" s="330"/>
+      <c r="M145" s="330"/>
+      <c r="N145" s="330"/>
       <c r="O145" s="39"/>
     </row>
     <row r="146" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C146" s="333"/>
-      <c r="D146" s="333"/>
-      <c r="E146" s="333"/>
-      <c r="F146" s="333"/>
-      <c r="G146" s="333"/>
-      <c r="H146" s="333"/>
-      <c r="J146" s="331"/>
-      <c r="K146" s="331"/>
-      <c r="L146" s="331"/>
-      <c r="M146" s="331"/>
-      <c r="N146" s="331"/>
+      <c r="C146" s="332"/>
+      <c r="D146" s="332"/>
+      <c r="E146" s="332"/>
+      <c r="F146" s="332"/>
+      <c r="G146" s="332"/>
+      <c r="H146" s="332"/>
+      <c r="J146" s="330"/>
+      <c r="K146" s="330"/>
+      <c r="L146" s="330"/>
+      <c r="M146" s="330"/>
+      <c r="N146" s="330"/>
       <c r="O146" s="39"/>
     </row>
     <row r="147" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C147" s="333"/>
-      <c r="D147" s="333"/>
-      <c r="E147" s="333"/>
-      <c r="F147" s="333"/>
-      <c r="G147" s="333"/>
-      <c r="H147" s="333"/>
-      <c r="J147" s="331"/>
-      <c r="K147" s="331"/>
-      <c r="L147" s="331"/>
-      <c r="M147" s="331"/>
-      <c r="N147" s="331"/>
+      <c r="C147" s="332"/>
+      <c r="D147" s="332"/>
+      <c r="E147" s="332"/>
+      <c r="F147" s="332"/>
+      <c r="G147" s="332"/>
+      <c r="H147" s="332"/>
+      <c r="J147" s="330"/>
+      <c r="K147" s="330"/>
+      <c r="L147" s="330"/>
+      <c r="M147" s="330"/>
+      <c r="N147" s="330"/>
       <c r="O147" s="39"/>
     </row>
     <row r="148" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C148" s="333"/>
-      <c r="D148" s="333"/>
-      <c r="E148" s="333"/>
-      <c r="F148" s="333"/>
-      <c r="G148" s="333"/>
-      <c r="H148" s="333"/>
-      <c r="J148" s="331"/>
-      <c r="K148" s="331"/>
-      <c r="L148" s="331"/>
-      <c r="M148" s="331"/>
-      <c r="N148" s="331"/>
+      <c r="C148" s="332"/>
+      <c r="D148" s="332"/>
+      <c r="E148" s="332"/>
+      <c r="F148" s="332"/>
+      <c r="G148" s="332"/>
+      <c r="H148" s="332"/>
+      <c r="J148" s="330"/>
+      <c r="K148" s="330"/>
+      <c r="L148" s="330"/>
+      <c r="M148" s="330"/>
+      <c r="N148" s="330"/>
       <c r="O148" s="39"/>
     </row>
     <row r="149" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C149" s="333"/>
-      <c r="D149" s="333"/>
-      <c r="E149" s="333"/>
-      <c r="F149" s="333"/>
-      <c r="G149" s="333"/>
-      <c r="H149" s="333"/>
-      <c r="J149" s="331"/>
-      <c r="K149" s="331"/>
-      <c r="L149" s="331"/>
-      <c r="M149" s="331"/>
-      <c r="N149" s="331"/>
+      <c r="C149" s="332"/>
+      <c r="D149" s="332"/>
+      <c r="E149" s="332"/>
+      <c r="F149" s="332"/>
+      <c r="G149" s="332"/>
+      <c r="H149" s="332"/>
+      <c r="J149" s="330"/>
+      <c r="K149" s="330"/>
+      <c r="L149" s="330"/>
+      <c r="M149" s="330"/>
+      <c r="N149" s="330"/>
       <c r="O149" s="39"/>
     </row>
     <row r="150" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C150" s="333"/>
-      <c r="D150" s="333"/>
-      <c r="E150" s="333"/>
-      <c r="F150" s="333"/>
-      <c r="G150" s="333"/>
-      <c r="H150" s="333"/>
-      <c r="J150" s="331"/>
-      <c r="K150" s="331"/>
-      <c r="L150" s="331"/>
-      <c r="M150" s="331"/>
-      <c r="N150" s="331"/>
+      <c r="C150" s="332"/>
+      <c r="D150" s="332"/>
+      <c r="E150" s="332"/>
+      <c r="F150" s="332"/>
+      <c r="G150" s="332"/>
+      <c r="H150" s="332"/>
+      <c r="J150" s="330"/>
+      <c r="K150" s="330"/>
+      <c r="L150" s="330"/>
+      <c r="M150" s="330"/>
+      <c r="N150" s="330"/>
       <c r="O150" s="39"/>
     </row>
     <row r="151" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C151" s="333"/>
-      <c r="D151" s="333"/>
-      <c r="E151" s="333"/>
-      <c r="F151" s="333"/>
-      <c r="G151" s="333"/>
-      <c r="H151" s="333"/>
-      <c r="J151" s="331"/>
-      <c r="K151" s="331"/>
-      <c r="L151" s="331"/>
-      <c r="M151" s="331"/>
-      <c r="N151" s="331"/>
+      <c r="C151" s="332"/>
+      <c r="D151" s="332"/>
+      <c r="E151" s="332"/>
+      <c r="F151" s="332"/>
+      <c r="G151" s="332"/>
+      <c r="H151" s="332"/>
+      <c r="J151" s="330"/>
+      <c r="K151" s="330"/>
+      <c r="L151" s="330"/>
+      <c r="M151" s="330"/>
+      <c r="N151" s="330"/>
       <c r="O151" s="39"/>
     </row>
     <row r="152" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C152" s="333"/>
-      <c r="D152" s="333"/>
-      <c r="E152" s="333"/>
-      <c r="F152" s="333"/>
-      <c r="G152" s="333"/>
-      <c r="H152" s="333"/>
-      <c r="J152" s="331"/>
-      <c r="K152" s="331"/>
-      <c r="L152" s="331"/>
-      <c r="M152" s="331"/>
-      <c r="N152" s="331"/>
+      <c r="C152" s="332"/>
+      <c r="D152" s="332"/>
+      <c r="E152" s="332"/>
+      <c r="F152" s="332"/>
+      <c r="G152" s="332"/>
+      <c r="H152" s="332"/>
+      <c r="J152" s="330"/>
+      <c r="K152" s="330"/>
+      <c r="L152" s="330"/>
+      <c r="M152" s="330"/>
+      <c r="N152" s="330"/>
       <c r="O152" s="39"/>
     </row>
     <row r="153" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C153" s="333"/>
-      <c r="D153" s="333"/>
-      <c r="E153" s="333"/>
-      <c r="F153" s="333"/>
-      <c r="G153" s="333"/>
-      <c r="H153" s="333"/>
-      <c r="J153" s="331"/>
-      <c r="K153" s="331"/>
-      <c r="L153" s="331"/>
-      <c r="M153" s="331"/>
-      <c r="N153" s="331"/>
+      <c r="C153" s="332"/>
+      <c r="D153" s="332"/>
+      <c r="E153" s="332"/>
+      <c r="F153" s="332"/>
+      <c r="G153" s="332"/>
+      <c r="H153" s="332"/>
+      <c r="J153" s="330"/>
+      <c r="K153" s="330"/>
+      <c r="L153" s="330"/>
+      <c r="M153" s="330"/>
+      <c r="N153" s="330"/>
       <c r="O153" s="39"/>
     </row>
     <row r="154" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C154" s="333"/>
-      <c r="D154" s="333"/>
-      <c r="E154" s="333"/>
-      <c r="F154" s="333"/>
-      <c r="G154" s="333"/>
-      <c r="H154" s="333"/>
-      <c r="J154" s="331"/>
-      <c r="K154" s="331"/>
-      <c r="L154" s="331"/>
-      <c r="M154" s="331"/>
-      <c r="N154" s="331"/>
+      <c r="C154" s="332"/>
+      <c r="D154" s="332"/>
+      <c r="E154" s="332"/>
+      <c r="F154" s="332"/>
+      <c r="G154" s="332"/>
+      <c r="H154" s="332"/>
+      <c r="J154" s="330"/>
+      <c r="K154" s="330"/>
+      <c r="L154" s="330"/>
+      <c r="M154" s="330"/>
+      <c r="N154" s="330"/>
       <c r="O154" s="39"/>
     </row>
     <row r="155" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C155" s="333"/>
-      <c r="D155" s="333"/>
-      <c r="E155" s="333"/>
-      <c r="F155" s="333"/>
-      <c r="G155" s="333"/>
-      <c r="H155" s="333"/>
-      <c r="J155" s="331"/>
-      <c r="K155" s="331"/>
-      <c r="L155" s="331"/>
-      <c r="M155" s="331"/>
-      <c r="N155" s="331"/>
+      <c r="C155" s="332"/>
+      <c r="D155" s="332"/>
+      <c r="E155" s="332"/>
+      <c r="F155" s="332"/>
+      <c r="G155" s="332"/>
+      <c r="H155" s="332"/>
+      <c r="J155" s="330"/>
+      <c r="K155" s="330"/>
+      <c r="L155" s="330"/>
+      <c r="M155" s="330"/>
+      <c r="N155" s="330"/>
       <c r="O155" s="39"/>
     </row>
     <row r="156" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C156" s="333"/>
-      <c r="D156" s="333"/>
-      <c r="E156" s="333"/>
-      <c r="F156" s="333"/>
-      <c r="G156" s="333"/>
-      <c r="H156" s="333"/>
-      <c r="J156" s="331"/>
-      <c r="K156" s="331"/>
-      <c r="L156" s="331"/>
-      <c r="M156" s="331"/>
-      <c r="N156" s="331"/>
+      <c r="C156" s="332"/>
+      <c r="D156" s="332"/>
+      <c r="E156" s="332"/>
+      <c r="F156" s="332"/>
+      <c r="G156" s="332"/>
+      <c r="H156" s="332"/>
+      <c r="J156" s="330"/>
+      <c r="K156" s="330"/>
+      <c r="L156" s="330"/>
+      <c r="M156" s="330"/>
+      <c r="N156" s="330"/>
       <c r="O156" s="39"/>
     </row>
     <row r="157" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C157" s="333"/>
-      <c r="D157" s="333"/>
-      <c r="E157" s="333"/>
-      <c r="F157" s="333"/>
-      <c r="G157" s="333"/>
-      <c r="H157" s="333"/>
-      <c r="J157" s="331"/>
-      <c r="K157" s="331"/>
-      <c r="L157" s="331"/>
-      <c r="M157" s="331"/>
-      <c r="N157" s="331"/>
+      <c r="C157" s="332"/>
+      <c r="D157" s="332"/>
+      <c r="E157" s="332"/>
+      <c r="F157" s="332"/>
+      <c r="G157" s="332"/>
+      <c r="H157" s="332"/>
+      <c r="J157" s="330"/>
+      <c r="K157" s="330"/>
+      <c r="L157" s="330"/>
+      <c r="M157" s="330"/>
+      <c r="N157" s="330"/>
       <c r="O157" s="39"/>
     </row>
     <row r="158" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C158" s="333"/>
-      <c r="D158" s="333"/>
-      <c r="E158" s="333"/>
-      <c r="F158" s="333"/>
-      <c r="G158" s="333"/>
-      <c r="H158" s="333"/>
-      <c r="J158" s="331"/>
-      <c r="K158" s="331"/>
-      <c r="L158" s="331"/>
-      <c r="M158" s="331"/>
-      <c r="N158" s="331"/>
+      <c r="C158" s="332"/>
+      <c r="D158" s="332"/>
+      <c r="E158" s="332"/>
+      <c r="F158" s="332"/>
+      <c r="G158" s="332"/>
+      <c r="H158" s="332"/>
+      <c r="J158" s="330"/>
+      <c r="K158" s="330"/>
+      <c r="L158" s="330"/>
+      <c r="M158" s="330"/>
+      <c r="N158" s="330"/>
       <c r="O158" s="39"/>
     </row>
     <row r="159" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C159" s="333"/>
-      <c r="D159" s="333"/>
-      <c r="E159" s="333"/>
-      <c r="F159" s="333"/>
-      <c r="G159" s="333"/>
-      <c r="H159" s="333"/>
-      <c r="J159" s="331"/>
-      <c r="K159" s="331"/>
-      <c r="L159" s="331"/>
-      <c r="M159" s="331"/>
-      <c r="N159" s="331"/>
+      <c r="C159" s="332"/>
+      <c r="D159" s="332"/>
+      <c r="E159" s="332"/>
+      <c r="F159" s="332"/>
+      <c r="G159" s="332"/>
+      <c r="H159" s="332"/>
+      <c r="J159" s="330"/>
+      <c r="K159" s="330"/>
+      <c r="L159" s="330"/>
+      <c r="M159" s="330"/>
+      <c r="N159" s="330"/>
       <c r="O159" s="39"/>
     </row>
     <row r="160" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C160" s="333"/>
-      <c r="D160" s="333"/>
-      <c r="E160" s="333"/>
-      <c r="F160" s="333"/>
-      <c r="G160" s="333"/>
-      <c r="H160" s="333"/>
-      <c r="J160" s="331"/>
-      <c r="K160" s="331"/>
-      <c r="L160" s="331"/>
-      <c r="M160" s="331"/>
-      <c r="N160" s="331"/>
+      <c r="C160" s="332"/>
+      <c r="D160" s="332"/>
+      <c r="E160" s="332"/>
+      <c r="F160" s="332"/>
+      <c r="G160" s="332"/>
+      <c r="H160" s="332"/>
+      <c r="J160" s="330"/>
+      <c r="K160" s="330"/>
+      <c r="L160" s="330"/>
+      <c r="M160" s="330"/>
+      <c r="N160" s="330"/>
       <c r="O160" s="39"/>
     </row>
     <row r="161" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C161" s="333"/>
-      <c r="D161" s="333"/>
-      <c r="E161" s="333"/>
-      <c r="F161" s="333"/>
-      <c r="G161" s="333"/>
-      <c r="H161" s="333"/>
-      <c r="J161" s="331"/>
-      <c r="K161" s="331"/>
-      <c r="L161" s="331"/>
-      <c r="M161" s="331"/>
-      <c r="N161" s="331"/>
+      <c r="C161" s="332"/>
+      <c r="D161" s="332"/>
+      <c r="E161" s="332"/>
+      <c r="F161" s="332"/>
+      <c r="G161" s="332"/>
+      <c r="H161" s="332"/>
+      <c r="J161" s="330"/>
+      <c r="K161" s="330"/>
+      <c r="L161" s="330"/>
+      <c r="M161" s="330"/>
+      <c r="N161" s="330"/>
       <c r="O161" s="39"/>
     </row>
     <row r="162" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C162" s="333"/>
-      <c r="D162" s="333"/>
-      <c r="E162" s="333"/>
-      <c r="F162" s="333"/>
-      <c r="G162" s="333"/>
-      <c r="H162" s="333"/>
-      <c r="J162" s="331"/>
-      <c r="K162" s="331"/>
-      <c r="L162" s="331"/>
-      <c r="M162" s="331"/>
-      <c r="N162" s="331"/>
+      <c r="C162" s="332"/>
+      <c r="D162" s="332"/>
+      <c r="E162" s="332"/>
+      <c r="F162" s="332"/>
+      <c r="G162" s="332"/>
+      <c r="H162" s="332"/>
+      <c r="J162" s="330"/>
+      <c r="K162" s="330"/>
+      <c r="L162" s="330"/>
+      <c r="M162" s="330"/>
+      <c r="N162" s="330"/>
       <c r="O162" s="39"/>
     </row>
     <row r="163" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C163" s="333"/>
-      <c r="D163" s="333"/>
-      <c r="E163" s="333"/>
-      <c r="F163" s="333"/>
-      <c r="G163" s="333"/>
-      <c r="H163" s="333"/>
-      <c r="J163" s="331"/>
-      <c r="K163" s="331"/>
-      <c r="L163" s="331"/>
-      <c r="M163" s="331"/>
-      <c r="N163" s="331"/>
+      <c r="C163" s="332"/>
+      <c r="D163" s="332"/>
+      <c r="E163" s="332"/>
+      <c r="F163" s="332"/>
+      <c r="G163" s="332"/>
+      <c r="H163" s="332"/>
+      <c r="J163" s="330"/>
+      <c r="K163" s="330"/>
+      <c r="L163" s="330"/>
+      <c r="M163" s="330"/>
+      <c r="N163" s="330"/>
       <c r="O163" s="39"/>
     </row>
     <row r="164" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C164" s="333"/>
-      <c r="D164" s="333"/>
-      <c r="E164" s="333"/>
-      <c r="F164" s="333"/>
-      <c r="G164" s="333"/>
-      <c r="H164" s="333"/>
-      <c r="J164" s="331"/>
-      <c r="K164" s="331"/>
-      <c r="L164" s="331"/>
-      <c r="M164" s="331"/>
-      <c r="N164" s="331"/>
+      <c r="C164" s="332"/>
+      <c r="D164" s="332"/>
+      <c r="E164" s="332"/>
+      <c r="F164" s="332"/>
+      <c r="G164" s="332"/>
+      <c r="H164" s="332"/>
+      <c r="J164" s="330"/>
+      <c r="K164" s="330"/>
+      <c r="L164" s="330"/>
+      <c r="M164" s="330"/>
+      <c r="N164" s="330"/>
       <c r="O164" s="39"/>
     </row>
     <row r="165" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C165" s="333"/>
-      <c r="D165" s="333"/>
-      <c r="E165" s="333"/>
-      <c r="F165" s="333"/>
-      <c r="G165" s="333"/>
-      <c r="H165" s="333"/>
-      <c r="J165" s="331"/>
-      <c r="K165" s="331"/>
-      <c r="L165" s="331"/>
-      <c r="M165" s="331"/>
-      <c r="N165" s="331"/>
+      <c r="C165" s="332"/>
+      <c r="D165" s="332"/>
+      <c r="E165" s="332"/>
+      <c r="F165" s="332"/>
+      <c r="G165" s="332"/>
+      <c r="H165" s="332"/>
+      <c r="J165" s="330"/>
+      <c r="K165" s="330"/>
+      <c r="L165" s="330"/>
+      <c r="M165" s="330"/>
+      <c r="N165" s="330"/>
       <c r="O165" s="39"/>
     </row>
     <row r="166" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C166" s="333"/>
-      <c r="D166" s="333"/>
-      <c r="E166" s="333"/>
-      <c r="F166" s="333"/>
-      <c r="G166" s="333"/>
-      <c r="H166" s="333"/>
-      <c r="J166" s="331"/>
-      <c r="K166" s="331"/>
-      <c r="L166" s="331"/>
-      <c r="M166" s="331"/>
-      <c r="N166" s="331"/>
+      <c r="C166" s="332"/>
+      <c r="D166" s="332"/>
+      <c r="E166" s="332"/>
+      <c r="F166" s="332"/>
+      <c r="G166" s="332"/>
+      <c r="H166" s="332"/>
+      <c r="J166" s="330"/>
+      <c r="K166" s="330"/>
+      <c r="L166" s="330"/>
+      <c r="M166" s="330"/>
+      <c r="N166" s="330"/>
       <c r="O166" s="39"/>
     </row>
     <row r="167" spans="3:15" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C167" s="333"/>
-      <c r="D167" s="333"/>
-      <c r="E167" s="333"/>
-      <c r="F167" s="333"/>
-      <c r="G167" s="333"/>
-      <c r="H167" s="333"/>
-      <c r="J167" s="331"/>
-      <c r="K167" s="331"/>
-      <c r="L167" s="331"/>
-      <c r="M167" s="331"/>
-      <c r="N167" s="331"/>
+      <c r="C167" s="332"/>
+      <c r="D167" s="332"/>
+      <c r="E167" s="332"/>
+      <c r="F167" s="332"/>
+      <c r="G167" s="332"/>
+      <c r="H167" s="332"/>
+      <c r="J167" s="330"/>
+      <c r="K167" s="330"/>
+      <c r="L167" s="330"/>
+      <c r="M167" s="330"/>
+      <c r="N167" s="330"/>
       <c r="O167" s="39"/>
     </row>
     <row r="168" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C168" s="333"/>
-      <c r="D168" s="333"/>
-      <c r="E168" s="333"/>
-      <c r="F168" s="333"/>
-      <c r="G168" s="333"/>
-      <c r="H168" s="333"/>
-      <c r="J168" s="331"/>
-      <c r="K168" s="331"/>
-      <c r="L168" s="331"/>
-      <c r="M168" s="331"/>
-      <c r="N168" s="331"/>
+      <c r="C168" s="332"/>
+      <c r="D168" s="332"/>
+      <c r="E168" s="332"/>
+      <c r="F168" s="332"/>
+      <c r="G168" s="332"/>
+      <c r="H168" s="332"/>
+      <c r="J168" s="330"/>
+      <c r="K168" s="330"/>
+      <c r="L168" s="330"/>
+      <c r="M168" s="330"/>
+      <c r="N168" s="330"/>
       <c r="O168" s="39"/>
     </row>
     <row r="169" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C169" s="333"/>
-      <c r="D169" s="333"/>
-      <c r="E169" s="333"/>
-      <c r="F169" s="333"/>
-      <c r="G169" s="333"/>
-      <c r="H169" s="333"/>
-      <c r="J169" s="331"/>
-      <c r="K169" s="331"/>
-      <c r="L169" s="331"/>
-      <c r="M169" s="331"/>
-      <c r="N169" s="331"/>
+      <c r="C169" s="332"/>
+      <c r="D169" s="332"/>
+      <c r="E169" s="332"/>
+      <c r="F169" s="332"/>
+      <c r="G169" s="332"/>
+      <c r="H169" s="332"/>
+      <c r="J169" s="330"/>
+      <c r="K169" s="330"/>
+      <c r="L169" s="330"/>
+      <c r="M169" s="330"/>
+      <c r="N169" s="330"/>
       <c r="O169" s="39"/>
     </row>
     <row r="170" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C170" s="333"/>
-      <c r="D170" s="333"/>
-      <c r="E170" s="333"/>
-      <c r="F170" s="333"/>
-      <c r="G170" s="333"/>
-      <c r="H170" s="333"/>
-      <c r="J170" s="331"/>
-      <c r="K170" s="331"/>
-      <c r="L170" s="331"/>
-      <c r="M170" s="331"/>
-      <c r="N170" s="331"/>
+      <c r="C170" s="332"/>
+      <c r="D170" s="332"/>
+      <c r="E170" s="332"/>
+      <c r="F170" s="332"/>
+      <c r="G170" s="332"/>
+      <c r="H170" s="332"/>
+      <c r="J170" s="330"/>
+      <c r="K170" s="330"/>
+      <c r="L170" s="330"/>
+      <c r="M170" s="330"/>
+      <c r="N170" s="330"/>
       <c r="O170" s="39"/>
     </row>
     <row r="171" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C171" s="333"/>
-      <c r="D171" s="333"/>
-      <c r="E171" s="333"/>
-      <c r="F171" s="333"/>
-      <c r="G171" s="333"/>
-      <c r="H171" s="333"/>
-      <c r="J171" s="331"/>
-      <c r="K171" s="331"/>
-      <c r="L171" s="331"/>
-      <c r="M171" s="331"/>
-      <c r="N171" s="331"/>
+      <c r="C171" s="332"/>
+      <c r="D171" s="332"/>
+      <c r="E171" s="332"/>
+      <c r="F171" s="332"/>
+      <c r="G171" s="332"/>
+      <c r="H171" s="332"/>
+      <c r="J171" s="330"/>
+      <c r="K171" s="330"/>
+      <c r="L171" s="330"/>
+      <c r="M171" s="330"/>
+      <c r="N171" s="330"/>
       <c r="O171" s="39"/>
     </row>
     <row r="172" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C172" s="333"/>
-      <c r="D172" s="333"/>
-      <c r="E172" s="333"/>
-      <c r="F172" s="333"/>
-      <c r="G172" s="333"/>
-      <c r="H172" s="333"/>
-      <c r="J172" s="331"/>
-      <c r="K172" s="331"/>
-      <c r="L172" s="331"/>
-      <c r="M172" s="331"/>
-      <c r="N172" s="331"/>
+      <c r="C172" s="332"/>
+      <c r="D172" s="332"/>
+      <c r="E172" s="332"/>
+      <c r="F172" s="332"/>
+      <c r="G172" s="332"/>
+      <c r="H172" s="332"/>
+      <c r="J172" s="330"/>
+      <c r="K172" s="330"/>
+      <c r="L172" s="330"/>
+      <c r="M172" s="330"/>
+      <c r="N172" s="330"/>
       <c r="O172" s="39"/>
     </row>
     <row r="173" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C173" s="333"/>
-      <c r="D173" s="333"/>
-      <c r="E173" s="333"/>
-      <c r="F173" s="333"/>
-      <c r="G173" s="333"/>
-      <c r="H173" s="333"/>
-      <c r="J173" s="331"/>
-      <c r="K173" s="331"/>
-      <c r="L173" s="331"/>
-      <c r="M173" s="331"/>
-      <c r="N173" s="331"/>
+      <c r="C173" s="332"/>
+      <c r="D173" s="332"/>
+      <c r="E173" s="332"/>
+      <c r="F173" s="332"/>
+      <c r="G173" s="332"/>
+      <c r="H173" s="332"/>
+      <c r="J173" s="330"/>
+      <c r="K173" s="330"/>
+      <c r="L173" s="330"/>
+      <c r="M173" s="330"/>
+      <c r="N173" s="330"/>
       <c r="O173" s="39"/>
     </row>
     <row r="174" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C174" s="333"/>
-      <c r="D174" s="333"/>
-      <c r="E174" s="333"/>
-      <c r="F174" s="333"/>
-      <c r="G174" s="333"/>
-      <c r="H174" s="333"/>
-      <c r="J174" s="331"/>
-      <c r="K174" s="331"/>
-      <c r="L174" s="331"/>
-      <c r="M174" s="331"/>
-      <c r="N174" s="331"/>
+      <c r="C174" s="332"/>
+      <c r="D174" s="332"/>
+      <c r="E174" s="332"/>
+      <c r="F174" s="332"/>
+      <c r="G174" s="332"/>
+      <c r="H174" s="332"/>
+      <c r="J174" s="330"/>
+      <c r="K174" s="330"/>
+      <c r="L174" s="330"/>
+      <c r="M174" s="330"/>
+      <c r="N174" s="330"/>
       <c r="O174" s="39"/>
     </row>
     <row r="175" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C175" s="333"/>
-      <c r="D175" s="333"/>
-      <c r="E175" s="333"/>
-      <c r="F175" s="333"/>
-      <c r="G175" s="333"/>
-      <c r="H175" s="333"/>
-      <c r="J175" s="331"/>
-      <c r="K175" s="331"/>
-      <c r="L175" s="331"/>
-      <c r="M175" s="331"/>
-      <c r="N175" s="331"/>
+      <c r="C175" s="332"/>
+      <c r="D175" s="332"/>
+      <c r="E175" s="332"/>
+      <c r="F175" s="332"/>
+      <c r="G175" s="332"/>
+      <c r="H175" s="332"/>
+      <c r="J175" s="330"/>
+      <c r="K175" s="330"/>
+      <c r="L175" s="330"/>
+      <c r="M175" s="330"/>
+      <c r="N175" s="330"/>
       <c r="O175" s="39"/>
     </row>
     <row r="176" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C176" s="333"/>
-      <c r="D176" s="333"/>
-      <c r="E176" s="333"/>
-      <c r="F176" s="333"/>
-      <c r="G176" s="333"/>
-      <c r="H176" s="333"/>
-      <c r="J176" s="331"/>
-      <c r="K176" s="331"/>
-      <c r="L176" s="331"/>
-      <c r="M176" s="331"/>
-      <c r="N176" s="331"/>
+      <c r="C176" s="332"/>
+      <c r="D176" s="332"/>
+      <c r="E176" s="332"/>
+      <c r="F176" s="332"/>
+      <c r="G176" s="332"/>
+      <c r="H176" s="332"/>
+      <c r="J176" s="330"/>
+      <c r="K176" s="330"/>
+      <c r="L176" s="330"/>
+      <c r="M176" s="330"/>
+      <c r="N176" s="330"/>
       <c r="O176" s="39"/>
     </row>
     <row r="177" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C177" s="333"/>
-      <c r="D177" s="333"/>
-      <c r="E177" s="333"/>
-      <c r="F177" s="333"/>
-      <c r="G177" s="333"/>
-      <c r="H177" s="333"/>
-      <c r="J177" s="331"/>
-      <c r="K177" s="331"/>
-      <c r="L177" s="331"/>
-      <c r="M177" s="331"/>
-      <c r="N177" s="331"/>
+      <c r="C177" s="332"/>
+      <c r="D177" s="332"/>
+      <c r="E177" s="332"/>
+      <c r="F177" s="332"/>
+      <c r="G177" s="332"/>
+      <c r="H177" s="332"/>
+      <c r="J177" s="330"/>
+      <c r="K177" s="330"/>
+      <c r="L177" s="330"/>
+      <c r="M177" s="330"/>
+      <c r="N177" s="330"/>
       <c r="O177" s="39"/>
     </row>
     <row r="178" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C178" s="333"/>
-      <c r="D178" s="333"/>
-      <c r="E178" s="333"/>
-      <c r="F178" s="333"/>
-      <c r="G178" s="333"/>
-      <c r="H178" s="333"/>
-      <c r="J178" s="331"/>
-      <c r="K178" s="331"/>
-      <c r="L178" s="331"/>
-      <c r="M178" s="331"/>
-      <c r="N178" s="331"/>
+      <c r="C178" s="332"/>
+      <c r="D178" s="332"/>
+      <c r="E178" s="332"/>
+      <c r="F178" s="332"/>
+      <c r="G178" s="332"/>
+      <c r="H178" s="332"/>
+      <c r="J178" s="330"/>
+      <c r="K178" s="330"/>
+      <c r="L178" s="330"/>
+      <c r="M178" s="330"/>
+      <c r="N178" s="330"/>
       <c r="O178" s="39"/>
     </row>
     <row r="179" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C179" s="333"/>
-      <c r="D179" s="333"/>
-      <c r="E179" s="333"/>
-      <c r="F179" s="333"/>
-      <c r="G179" s="333"/>
-      <c r="H179" s="333"/>
-      <c r="J179" s="331"/>
-      <c r="K179" s="331"/>
-      <c r="L179" s="331"/>
-      <c r="M179" s="331"/>
-      <c r="N179" s="331"/>
+      <c r="C179" s="332"/>
+      <c r="D179" s="332"/>
+      <c r="E179" s="332"/>
+      <c r="F179" s="332"/>
+      <c r="G179" s="332"/>
+      <c r="H179" s="332"/>
+      <c r="J179" s="330"/>
+      <c r="K179" s="330"/>
+      <c r="L179" s="330"/>
+      <c r="M179" s="330"/>
+      <c r="N179" s="330"/>
       <c r="O179" s="39"/>
     </row>
     <row r="180" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C180" s="333"/>
-      <c r="D180" s="333"/>
-      <c r="E180" s="333"/>
-      <c r="F180" s="333"/>
-      <c r="G180" s="333"/>
-      <c r="H180" s="333"/>
-      <c r="J180" s="331"/>
-      <c r="K180" s="331"/>
-      <c r="L180" s="331"/>
-      <c r="M180" s="331"/>
-      <c r="N180" s="331"/>
+      <c r="C180" s="332"/>
+      <c r="D180" s="332"/>
+      <c r="E180" s="332"/>
+      <c r="F180" s="332"/>
+      <c r="G180" s="332"/>
+      <c r="H180" s="332"/>
+      <c r="J180" s="330"/>
+      <c r="K180" s="330"/>
+      <c r="L180" s="330"/>
+      <c r="M180" s="330"/>
+      <c r="N180" s="330"/>
       <c r="O180" s="39"/>
     </row>
     <row r="181" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C181" s="333"/>
-      <c r="D181" s="333"/>
-      <c r="E181" s="333"/>
-      <c r="F181" s="333"/>
-      <c r="G181" s="333"/>
-      <c r="H181" s="333"/>
-      <c r="J181" s="331"/>
-      <c r="K181" s="331"/>
-      <c r="L181" s="331"/>
-      <c r="M181" s="331"/>
-      <c r="N181" s="331"/>
+      <c r="C181" s="332"/>
+      <c r="D181" s="332"/>
+      <c r="E181" s="332"/>
+      <c r="F181" s="332"/>
+      <c r="G181" s="332"/>
+      <c r="H181" s="332"/>
+      <c r="J181" s="330"/>
+      <c r="K181" s="330"/>
+      <c r="L181" s="330"/>
+      <c r="M181" s="330"/>
+      <c r="N181" s="330"/>
       <c r="O181" s="39"/>
     </row>
     <row r="182" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C182" s="333"/>
-      <c r="D182" s="333"/>
-      <c r="E182" s="333"/>
-      <c r="F182" s="333"/>
-      <c r="G182" s="333"/>
-      <c r="H182" s="333"/>
-      <c r="J182" s="331"/>
-      <c r="K182" s="331"/>
-      <c r="L182" s="331"/>
-      <c r="M182" s="331"/>
-      <c r="N182" s="331"/>
+      <c r="C182" s="332"/>
+      <c r="D182" s="332"/>
+      <c r="E182" s="332"/>
+      <c r="F182" s="332"/>
+      <c r="G182" s="332"/>
+      <c r="H182" s="332"/>
+      <c r="J182" s="330"/>
+      <c r="K182" s="330"/>
+      <c r="L182" s="330"/>
+      <c r="M182" s="330"/>
+      <c r="N182" s="330"/>
       <c r="O182" s="39"/>
     </row>
     <row r="183" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C183" s="333"/>
-      <c r="D183" s="333"/>
-      <c r="E183" s="333"/>
-      <c r="F183" s="333"/>
-      <c r="G183" s="333"/>
-      <c r="H183" s="333"/>
-      <c r="J183" s="331"/>
-      <c r="K183" s="331"/>
-      <c r="L183" s="331"/>
-      <c r="M183" s="331"/>
-      <c r="N183" s="331"/>
+      <c r="C183" s="332"/>
+      <c r="D183" s="332"/>
+      <c r="E183" s="332"/>
+      <c r="F183" s="332"/>
+      <c r="G183" s="332"/>
+      <c r="H183" s="332"/>
+      <c r="J183" s="330"/>
+      <c r="K183" s="330"/>
+      <c r="L183" s="330"/>
+      <c r="M183" s="330"/>
+      <c r="N183" s="330"/>
       <c r="O183" s="39"/>
     </row>
     <row r="184" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C184" s="333"/>
-      <c r="D184" s="333"/>
-      <c r="E184" s="333"/>
-      <c r="F184" s="333"/>
-      <c r="G184" s="333"/>
-      <c r="H184" s="333"/>
-      <c r="J184" s="331"/>
-      <c r="K184" s="331"/>
-      <c r="L184" s="331"/>
-      <c r="M184" s="331"/>
-      <c r="N184" s="331"/>
+      <c r="C184" s="332"/>
+      <c r="D184" s="332"/>
+      <c r="E184" s="332"/>
+      <c r="F184" s="332"/>
+      <c r="G184" s="332"/>
+      <c r="H184" s="332"/>
+      <c r="J184" s="330"/>
+      <c r="K184" s="330"/>
+      <c r="L184" s="330"/>
+      <c r="M184" s="330"/>
+      <c r="N184" s="330"/>
       <c r="O184" s="39"/>
     </row>
     <row r="185" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C185" s="333"/>
-      <c r="D185" s="333"/>
-      <c r="E185" s="333"/>
-      <c r="F185" s="333"/>
-      <c r="G185" s="333"/>
-      <c r="H185" s="333"/>
-      <c r="J185" s="331"/>
-      <c r="K185" s="331"/>
-      <c r="L185" s="331"/>
-      <c r="M185" s="331"/>
-      <c r="N185" s="331"/>
+      <c r="C185" s="332"/>
+      <c r="D185" s="332"/>
+      <c r="E185" s="332"/>
+      <c r="F185" s="332"/>
+      <c r="G185" s="332"/>
+      <c r="H185" s="332"/>
+      <c r="J185" s="330"/>
+      <c r="K185" s="330"/>
+      <c r="L185" s="330"/>
+      <c r="M185" s="330"/>
+      <c r="N185" s="330"/>
       <c r="O185" s="39"/>
     </row>
     <row r="186" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C186" s="333"/>
-      <c r="D186" s="333"/>
-      <c r="E186" s="333"/>
-      <c r="F186" s="333"/>
-      <c r="G186" s="333"/>
-      <c r="H186" s="333"/>
-      <c r="J186" s="331"/>
-      <c r="K186" s="331"/>
-      <c r="L186" s="331"/>
-      <c r="M186" s="331"/>
-      <c r="N186" s="331"/>
+      <c r="C186" s="332"/>
+      <c r="D186" s="332"/>
+      <c r="E186" s="332"/>
+      <c r="F186" s="332"/>
+      <c r="G186" s="332"/>
+      <c r="H186" s="332"/>
+      <c r="J186" s="330"/>
+      <c r="K186" s="330"/>
+      <c r="L186" s="330"/>
+      <c r="M186" s="330"/>
+      <c r="N186" s="330"/>
       <c r="O186" s="39"/>
     </row>
     <row r="187" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C187" s="333"/>
-      <c r="D187" s="333"/>
-      <c r="E187" s="333"/>
-      <c r="F187" s="333"/>
-      <c r="G187" s="333"/>
-      <c r="H187" s="333"/>
-      <c r="J187" s="331"/>
-      <c r="K187" s="331"/>
-      <c r="L187" s="331"/>
-      <c r="M187" s="331"/>
-      <c r="N187" s="331"/>
+      <c r="C187" s="332"/>
+      <c r="D187" s="332"/>
+      <c r="E187" s="332"/>
+      <c r="F187" s="332"/>
+      <c r="G187" s="332"/>
+      <c r="H187" s="332"/>
+      <c r="J187" s="330"/>
+      <c r="K187" s="330"/>
+      <c r="L187" s="330"/>
+      <c r="M187" s="330"/>
+      <c r="N187" s="330"/>
       <c r="O187" s="39"/>
     </row>
     <row r="188" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C188" s="333"/>
-      <c r="D188" s="333"/>
-      <c r="E188" s="333"/>
-      <c r="F188" s="333"/>
-      <c r="G188" s="333"/>
-      <c r="H188" s="333"/>
-      <c r="J188" s="331"/>
-      <c r="K188" s="331"/>
-      <c r="L188" s="331"/>
-      <c r="M188" s="331"/>
-      <c r="N188" s="331"/>
+      <c r="C188" s="332"/>
+      <c r="D188" s="332"/>
+      <c r="E188" s="332"/>
+      <c r="F188" s="332"/>
+      <c r="G188" s="332"/>
+      <c r="H188" s="332"/>
+      <c r="J188" s="330"/>
+      <c r="K188" s="330"/>
+      <c r="L188" s="330"/>
+      <c r="M188" s="330"/>
+      <c r="N188" s="330"/>
       <c r="O188" s="39"/>
     </row>
     <row r="189" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C189" s="333"/>
-      <c r="D189" s="333"/>
-      <c r="E189" s="333"/>
-      <c r="F189" s="333"/>
-      <c r="G189" s="333"/>
-      <c r="H189" s="333"/>
-      <c r="J189" s="331"/>
-      <c r="K189" s="331"/>
-      <c r="L189" s="331"/>
-      <c r="M189" s="331"/>
-      <c r="N189" s="331"/>
+      <c r="C189" s="332"/>
+      <c r="D189" s="332"/>
+      <c r="E189" s="332"/>
+      <c r="F189" s="332"/>
+      <c r="G189" s="332"/>
+      <c r="H189" s="332"/>
+      <c r="J189" s="330"/>
+      <c r="K189" s="330"/>
+      <c r="L189" s="330"/>
+      <c r="M189" s="330"/>
+      <c r="N189" s="330"/>
       <c r="O189" s="39"/>
     </row>
     <row r="190" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C190" s="333"/>
-      <c r="D190" s="333"/>
-      <c r="E190" s="333"/>
-      <c r="F190" s="333"/>
-      <c r="G190" s="333"/>
-      <c r="H190" s="333"/>
-      <c r="J190" s="331"/>
-      <c r="K190" s="331"/>
-      <c r="L190" s="331"/>
-      <c r="M190" s="331"/>
-      <c r="N190" s="331"/>
+      <c r="C190" s="332"/>
+      <c r="D190" s="332"/>
+      <c r="E190" s="332"/>
+      <c r="F190" s="332"/>
+      <c r="G190" s="332"/>
+      <c r="H190" s="332"/>
+      <c r="J190" s="330"/>
+      <c r="K190" s="330"/>
+      <c r="L190" s="330"/>
+      <c r="M190" s="330"/>
+      <c r="N190" s="330"/>
       <c r="O190" s="39"/>
     </row>
     <row r="191" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C191" s="333"/>
-      <c r="D191" s="333"/>
-      <c r="E191" s="333"/>
-      <c r="F191" s="333"/>
-      <c r="G191" s="333"/>
-      <c r="H191" s="333"/>
-      <c r="J191" s="331"/>
-      <c r="K191" s="331"/>
-      <c r="L191" s="331"/>
-      <c r="M191" s="331"/>
-      <c r="N191" s="331"/>
+      <c r="C191" s="332"/>
+      <c r="D191" s="332"/>
+      <c r="E191" s="332"/>
+      <c r="F191" s="332"/>
+      <c r="G191" s="332"/>
+      <c r="H191" s="332"/>
+      <c r="J191" s="330"/>
+      <c r="K191" s="330"/>
+      <c r="L191" s="330"/>
+      <c r="M191" s="330"/>
+      <c r="N191" s="330"/>
       <c r="O191" s="39"/>
     </row>
     <row r="192" spans="3:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="J192" s="331"/>
-      <c r="K192" s="331"/>
-      <c r="L192" s="331"/>
-      <c r="M192" s="331"/>
-      <c r="N192" s="331"/>
+      <c r="J192" s="330"/>
+      <c r="K192" s="330"/>
+      <c r="L192" s="330"/>
+      <c r="M192" s="330"/>
+      <c r="N192" s="330"/>
       <c r="O192" s="39"/>
     </row>
   </sheetData>
@@ -9245,204 +9250,204 @@
   <sheetData>
     <row r="1" spans="1:31" ht="21.75" x14ac:dyDescent="0.25">
       <c r="A1" s="211"/>
-      <c r="B1" s="563" t="s">
+      <c r="B1" s="561" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="563"/>
-      <c r="D1" s="563"/>
-      <c r="E1" s="563"/>
-      <c r="F1" s="563"/>
-      <c r="G1" s="563"/>
-      <c r="H1" s="563"/>
-      <c r="I1" s="563"/>
-      <c r="J1" s="563"/>
-      <c r="K1" s="563"/>
-      <c r="L1" s="563"/>
-      <c r="M1" s="563"/>
-      <c r="N1" s="563"/>
-      <c r="O1" s="563"/>
-      <c r="P1" s="563"/>
-      <c r="Q1" s="563"/>
-      <c r="R1" s="563"/>
-      <c r="S1" s="563"/>
-      <c r="T1" s="563"/>
-      <c r="U1" s="563"/>
-      <c r="V1" s="563"/>
-      <c r="W1" s="563"/>
-      <c r="X1" s="563"/>
+      <c r="C1" s="561"/>
+      <c r="D1" s="561"/>
+      <c r="E1" s="561"/>
+      <c r="F1" s="561"/>
+      <c r="G1" s="561"/>
+      <c r="H1" s="561"/>
+      <c r="I1" s="561"/>
+      <c r="J1" s="561"/>
+      <c r="K1" s="561"/>
+      <c r="L1" s="561"/>
+      <c r="M1" s="561"/>
+      <c r="N1" s="561"/>
+      <c r="O1" s="561"/>
+      <c r="P1" s="561"/>
+      <c r="Q1" s="561"/>
+      <c r="R1" s="561"/>
+      <c r="S1" s="561"/>
+      <c r="T1" s="561"/>
+      <c r="U1" s="561"/>
+      <c r="V1" s="561"/>
+      <c r="W1" s="561"/>
+      <c r="X1" s="561"/>
       <c r="Y1" s="212"/>
       <c r="Z1" s="212"/>
       <c r="AA1" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="564" t="s">
+      <c r="AB1" s="562" t="s">
         <v>247</v>
       </c>
-      <c r="AC1" s="564"/>
-      <c r="AD1" s="564"/>
-      <c r="AE1" s="564"/>
+      <c r="AC1" s="562"/>
+      <c r="AD1" s="562"/>
+      <c r="AE1" s="562"/>
     </row>
     <row r="2" spans="1:31" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="552" t="s">
+      <c r="A2" s="550" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="566" t="s">
+      <c r="B2" s="564" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="567"/>
-      <c r="D2" s="567"/>
-      <c r="E2" s="567"/>
-      <c r="F2" s="567"/>
-      <c r="G2" s="567"/>
-      <c r="H2" s="567"/>
-      <c r="I2" s="567"/>
-      <c r="J2" s="567"/>
-      <c r="K2" s="567"/>
-      <c r="L2" s="567"/>
-      <c r="M2" s="567"/>
-      <c r="N2" s="567"/>
-      <c r="O2" s="567"/>
-      <c r="P2" s="567"/>
-      <c r="Q2" s="567"/>
-      <c r="R2" s="567"/>
-      <c r="S2" s="567"/>
-      <c r="T2" s="567"/>
-      <c r="U2" s="567"/>
-      <c r="V2" s="567"/>
-      <c r="W2" s="568"/>
-      <c r="X2" s="569"/>
-      <c r="Y2" s="570"/>
-      <c r="Z2" s="570"/>
-      <c r="AA2" s="570"/>
-      <c r="AB2" s="570"/>
-      <c r="AC2" s="570"/>
-      <c r="AD2" s="571"/>
-      <c r="AE2" s="572" t="s">
+      <c r="C2" s="565"/>
+      <c r="D2" s="565"/>
+      <c r="E2" s="565"/>
+      <c r="F2" s="565"/>
+      <c r="G2" s="565"/>
+      <c r="H2" s="565"/>
+      <c r="I2" s="565"/>
+      <c r="J2" s="565"/>
+      <c r="K2" s="565"/>
+      <c r="L2" s="565"/>
+      <c r="M2" s="565"/>
+      <c r="N2" s="565"/>
+      <c r="O2" s="565"/>
+      <c r="P2" s="565"/>
+      <c r="Q2" s="565"/>
+      <c r="R2" s="565"/>
+      <c r="S2" s="565"/>
+      <c r="T2" s="565"/>
+      <c r="U2" s="565"/>
+      <c r="V2" s="565"/>
+      <c r="W2" s="566"/>
+      <c r="X2" s="567"/>
+      <c r="Y2" s="568"/>
+      <c r="Z2" s="568"/>
+      <c r="AA2" s="568"/>
+      <c r="AB2" s="568"/>
+      <c r="AC2" s="568"/>
+      <c r="AD2" s="569"/>
+      <c r="AE2" s="570" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="565"/>
-      <c r="B3" s="549" t="s">
+      <c r="A3" s="563"/>
+      <c r="B3" s="547" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="551"/>
-      <c r="D3" s="550"/>
-      <c r="E3" s="549" t="s">
+      <c r="C3" s="549"/>
+      <c r="D3" s="548"/>
+      <c r="E3" s="547" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="551"/>
-      <c r="G3" s="551"/>
-      <c r="H3" s="551"/>
-      <c r="I3" s="551"/>
-      <c r="J3" s="551"/>
-      <c r="K3" s="551"/>
-      <c r="L3" s="551"/>
-      <c r="M3" s="551"/>
-      <c r="N3" s="551"/>
-      <c r="O3" s="551"/>
-      <c r="P3" s="551"/>
-      <c r="Q3" s="551"/>
-      <c r="R3" s="550"/>
+      <c r="F3" s="549"/>
+      <c r="G3" s="549"/>
+      <c r="H3" s="549"/>
+      <c r="I3" s="549"/>
+      <c r="J3" s="549"/>
+      <c r="K3" s="549"/>
+      <c r="L3" s="549"/>
+      <c r="M3" s="549"/>
+      <c r="N3" s="549"/>
+      <c r="O3" s="549"/>
+      <c r="P3" s="549"/>
+      <c r="Q3" s="549"/>
+      <c r="R3" s="548"/>
       <c r="S3" s="225"/>
       <c r="T3" s="225"/>
-      <c r="U3" s="575" t="s">
+      <c r="U3" s="573" t="s">
         <v>62</v>
       </c>
-      <c r="V3" s="576"/>
-      <c r="W3" s="577"/>
-      <c r="X3" s="584" t="s">
+      <c r="V3" s="574"/>
+      <c r="W3" s="575"/>
+      <c r="X3" s="582" t="s">
         <v>64</v>
       </c>
-      <c r="Y3" s="585"/>
-      <c r="Z3" s="585"/>
-      <c r="AA3" s="586"/>
-      <c r="AB3" s="584" t="s">
+      <c r="Y3" s="583"/>
+      <c r="Z3" s="583"/>
+      <c r="AA3" s="584"/>
+      <c r="AB3" s="582" t="s">
         <v>65</v>
       </c>
-      <c r="AC3" s="585"/>
-      <c r="AD3" s="586"/>
-      <c r="AE3" s="573"/>
+      <c r="AC3" s="583"/>
+      <c r="AD3" s="584"/>
+      <c r="AE3" s="571"/>
     </row>
     <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="565"/>
-      <c r="B4" s="552" t="s">
+      <c r="A4" s="563"/>
+      <c r="B4" s="550" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="552" t="s">
+      <c r="C4" s="550" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="552" t="s">
+      <c r="D4" s="550" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="549" t="s">
+      <c r="E4" s="547" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="551"/>
-      <c r="G4" s="551"/>
-      <c r="H4" s="551"/>
-      <c r="I4" s="551"/>
-      <c r="J4" s="551"/>
-      <c r="K4" s="551"/>
-      <c r="L4" s="551"/>
-      <c r="M4" s="550"/>
-      <c r="N4" s="549"/>
-      <c r="O4" s="551"/>
-      <c r="P4" s="551"/>
-      <c r="Q4" s="551"/>
-      <c r="R4" s="550"/>
+      <c r="F4" s="549"/>
+      <c r="G4" s="549"/>
+      <c r="H4" s="549"/>
+      <c r="I4" s="549"/>
+      <c r="J4" s="549"/>
+      <c r="K4" s="549"/>
+      <c r="L4" s="549"/>
+      <c r="M4" s="548"/>
+      <c r="N4" s="547"/>
+      <c r="O4" s="549"/>
+      <c r="P4" s="549"/>
+      <c r="Q4" s="549"/>
+      <c r="R4" s="548"/>
       <c r="S4" s="226"/>
       <c r="T4" s="226"/>
-      <c r="U4" s="578"/>
-      <c r="V4" s="579"/>
-      <c r="W4" s="580"/>
-      <c r="X4" s="554" t="s">
+      <c r="U4" s="576"/>
+      <c r="V4" s="577"/>
+      <c r="W4" s="578"/>
+      <c r="X4" s="552" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="555"/>
-      <c r="Z4" s="556"/>
-      <c r="AA4" s="560" t="s">
+      <c r="Y4" s="553"/>
+      <c r="Z4" s="554"/>
+      <c r="AA4" s="558" t="s">
         <v>32</v>
       </c>
-      <c r="AB4" s="560" t="s">
+      <c r="AB4" s="558" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="560" t="s">
+      <c r="AC4" s="558" t="s">
         <v>84</v>
       </c>
-      <c r="AD4" s="560" t="s">
+      <c r="AD4" s="558" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="573"/>
+      <c r="AE4" s="571"/>
     </row>
     <row r="5" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="565"/>
-      <c r="B5" s="565"/>
-      <c r="C5" s="565"/>
-      <c r="D5" s="565"/>
-      <c r="E5" s="549" t="s">
+      <c r="A5" s="563"/>
+      <c r="B5" s="563"/>
+      <c r="C5" s="563"/>
+      <c r="D5" s="563"/>
+      <c r="E5" s="547" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="550"/>
-      <c r="G5" s="549" t="s">
+      <c r="F5" s="548"/>
+      <c r="G5" s="547" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="550"/>
-      <c r="I5" s="549" t="s">
+      <c r="H5" s="548"/>
+      <c r="I5" s="547" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="551"/>
-      <c r="K5" s="550"/>
+      <c r="J5" s="549"/>
+      <c r="K5" s="548"/>
       <c r="L5" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="552" t="s">
+      <c r="M5" s="550" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="549"/>
-      <c r="O5" s="551"/>
-      <c r="P5" s="551"/>
-      <c r="Q5" s="550"/>
+      <c r="N5" s="547"/>
+      <c r="O5" s="549"/>
+      <c r="P5" s="549"/>
+      <c r="Q5" s="548"/>
       <c r="R5" s="228" t="s">
         <v>47</v>
       </c>
@@ -9452,23 +9457,23 @@
       <c r="T5" s="228" t="s">
         <v>76</v>
       </c>
-      <c r="U5" s="581"/>
-      <c r="V5" s="582"/>
-      <c r="W5" s="583"/>
-      <c r="X5" s="557"/>
-      <c r="Y5" s="558"/>
-      <c r="Z5" s="559"/>
-      <c r="AA5" s="561"/>
-      <c r="AB5" s="561"/>
-      <c r="AC5" s="561"/>
-      <c r="AD5" s="561"/>
-      <c r="AE5" s="573"/>
+      <c r="U5" s="579"/>
+      <c r="V5" s="580"/>
+      <c r="W5" s="581"/>
+      <c r="X5" s="555"/>
+      <c r="Y5" s="556"/>
+      <c r="Z5" s="557"/>
+      <c r="AA5" s="559"/>
+      <c r="AB5" s="559"/>
+      <c r="AC5" s="559"/>
+      <c r="AD5" s="559"/>
+      <c r="AE5" s="571"/>
     </row>
     <row r="6" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="553"/>
-      <c r="B6" s="553"/>
-      <c r="C6" s="553"/>
-      <c r="D6" s="553"/>
+      <c r="A6" s="551"/>
+      <c r="B6" s="551"/>
+      <c r="C6" s="551"/>
+      <c r="D6" s="551"/>
       <c r="E6" s="228" t="s">
         <v>61</v>
       </c>
@@ -9493,7 +9498,7 @@
       <c r="L6" s="228" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="553"/>
+      <c r="M6" s="551"/>
       <c r="N6" s="228" t="s">
         <v>36</v>
       </c>
@@ -9533,11 +9538,11 @@
       <c r="Z6" s="230" t="s">
         <v>150</v>
       </c>
-      <c r="AA6" s="562"/>
-      <c r="AB6" s="562"/>
-      <c r="AC6" s="562"/>
-      <c r="AD6" s="562"/>
-      <c r="AE6" s="574"/>
+      <c r="AA6" s="560"/>
+      <c r="AB6" s="560"/>
+      <c r="AC6" s="560"/>
+      <c r="AD6" s="560"/>
+      <c r="AE6" s="572"/>
     </row>
     <row r="7" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="236">
@@ -10170,205 +10175,205 @@
       </c>
     </row>
     <row r="13" spans="1:31" ht="21.75" x14ac:dyDescent="0.15">
-      <c r="A13" s="530" t="s">
+      <c r="A13" s="528" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="530"/>
-      <c r="C13" s="530"/>
-      <c r="D13" s="530"/>
-      <c r="E13" s="530"/>
-      <c r="F13" s="530"/>
-      <c r="G13" s="530"/>
-      <c r="H13" s="530"/>
-      <c r="I13" s="530"/>
-      <c r="J13" s="530"/>
-      <c r="K13" s="530"/>
-      <c r="L13" s="530"/>
-      <c r="M13" s="530"/>
-      <c r="N13" s="530"/>
-      <c r="O13" s="530"/>
-      <c r="P13" s="530"/>
-      <c r="Q13" s="530"/>
-      <c r="R13" s="530"/>
-      <c r="S13" s="530"/>
-      <c r="T13" s="530"/>
-      <c r="U13" s="530"/>
-      <c r="V13" s="530"/>
-      <c r="W13" s="530"/>
-      <c r="X13" s="530"/>
-      <c r="Y13" s="530"/>
-      <c r="Z13" s="530"/>
-      <c r="AA13" s="530"/>
-      <c r="AB13" s="530"/>
-      <c r="AC13" s="530"/>
-      <c r="AD13" s="530"/>
-      <c r="AE13" s="530"/>
+      <c r="B13" s="528"/>
+      <c r="C13" s="528"/>
+      <c r="D13" s="528"/>
+      <c r="E13" s="528"/>
+      <c r="F13" s="528"/>
+      <c r="G13" s="528"/>
+      <c r="H13" s="528"/>
+      <c r="I13" s="528"/>
+      <c r="J13" s="528"/>
+      <c r="K13" s="528"/>
+      <c r="L13" s="528"/>
+      <c r="M13" s="528"/>
+      <c r="N13" s="528"/>
+      <c r="O13" s="528"/>
+      <c r="P13" s="528"/>
+      <c r="Q13" s="528"/>
+      <c r="R13" s="528"/>
+      <c r="S13" s="528"/>
+      <c r="T13" s="528"/>
+      <c r="U13" s="528"/>
+      <c r="V13" s="528"/>
+      <c r="W13" s="528"/>
+      <c r="X13" s="528"/>
+      <c r="Y13" s="528"/>
+      <c r="Z13" s="528"/>
+      <c r="AA13" s="528"/>
+      <c r="AB13" s="528"/>
+      <c r="AC13" s="528"/>
+      <c r="AD13" s="528"/>
+      <c r="AE13" s="528"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="518" t="s">
+      <c r="A14" s="516" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="531" t="s">
+      <c r="B14" s="529" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="532"/>
-      <c r="D14" s="532"/>
-      <c r="E14" s="532"/>
-      <c r="F14" s="532"/>
-      <c r="G14" s="532"/>
-      <c r="H14" s="532"/>
-      <c r="I14" s="532"/>
-      <c r="J14" s="532"/>
-      <c r="K14" s="532"/>
-      <c r="L14" s="532"/>
-      <c r="M14" s="532"/>
-      <c r="N14" s="532"/>
-      <c r="O14" s="532"/>
-      <c r="P14" s="532"/>
-      <c r="Q14" s="532"/>
-      <c r="R14" s="532"/>
-      <c r="S14" s="532"/>
-      <c r="T14" s="532"/>
-      <c r="U14" s="532"/>
-      <c r="V14" s="532"/>
-      <c r="W14" s="533"/>
-      <c r="X14" s="531" t="s">
+      <c r="C14" s="530"/>
+      <c r="D14" s="530"/>
+      <c r="E14" s="530"/>
+      <c r="F14" s="530"/>
+      <c r="G14" s="530"/>
+      <c r="H14" s="530"/>
+      <c r="I14" s="530"/>
+      <c r="J14" s="530"/>
+      <c r="K14" s="530"/>
+      <c r="L14" s="530"/>
+      <c r="M14" s="530"/>
+      <c r="N14" s="530"/>
+      <c r="O14" s="530"/>
+      <c r="P14" s="530"/>
+      <c r="Q14" s="530"/>
+      <c r="R14" s="530"/>
+      <c r="S14" s="530"/>
+      <c r="T14" s="530"/>
+      <c r="U14" s="530"/>
+      <c r="V14" s="530"/>
+      <c r="W14" s="531"/>
+      <c r="X14" s="529" t="s">
         <v>27</v>
       </c>
-      <c r="Y14" s="532"/>
-      <c r="Z14" s="532"/>
-      <c r="AA14" s="532"/>
-      <c r="AB14" s="532"/>
-      <c r="AC14" s="532"/>
-      <c r="AD14" s="533"/>
-      <c r="AE14" s="534" t="s">
+      <c r="Y14" s="530"/>
+      <c r="Z14" s="530"/>
+      <c r="AA14" s="530"/>
+      <c r="AB14" s="530"/>
+      <c r="AC14" s="530"/>
+      <c r="AD14" s="531"/>
+      <c r="AE14" s="532" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="519"/>
-      <c r="B15" s="531" t="s">
+      <c r="A15" s="517"/>
+      <c r="B15" s="529" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="532"/>
-      <c r="D15" s="533"/>
-      <c r="E15" s="531" t="s">
+      <c r="C15" s="530"/>
+      <c r="D15" s="531"/>
+      <c r="E15" s="529" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="532"/>
-      <c r="G15" s="532"/>
-      <c r="H15" s="532"/>
-      <c r="I15" s="532"/>
-      <c r="J15" s="532"/>
-      <c r="K15" s="532"/>
-      <c r="L15" s="532"/>
-      <c r="M15" s="532"/>
-      <c r="N15" s="532"/>
-      <c r="O15" s="532"/>
-      <c r="P15" s="532"/>
-      <c r="Q15" s="532"/>
-      <c r="R15" s="533"/>
+      <c r="F15" s="530"/>
+      <c r="G15" s="530"/>
+      <c r="H15" s="530"/>
+      <c r="I15" s="530"/>
+      <c r="J15" s="530"/>
+      <c r="K15" s="530"/>
+      <c r="L15" s="530"/>
+      <c r="M15" s="530"/>
+      <c r="N15" s="530"/>
+      <c r="O15" s="530"/>
+      <c r="P15" s="530"/>
+      <c r="Q15" s="530"/>
+      <c r="R15" s="531"/>
       <c r="S15" s="231"/>
       <c r="T15" s="231"/>
-      <c r="U15" s="537" t="s">
+      <c r="U15" s="535" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="538"/>
-      <c r="W15" s="539"/>
-      <c r="X15" s="521" t="s">
+      <c r="V15" s="536"/>
+      <c r="W15" s="537"/>
+      <c r="X15" s="519" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="523"/>
-      <c r="Z15" s="523"/>
-      <c r="AA15" s="522"/>
-      <c r="AB15" s="521" t="s">
+      <c r="Y15" s="521"/>
+      <c r="Z15" s="521"/>
+      <c r="AA15" s="520"/>
+      <c r="AB15" s="519" t="s">
         <v>65</v>
       </c>
-      <c r="AC15" s="523"/>
-      <c r="AD15" s="522"/>
-      <c r="AE15" s="535"/>
+      <c r="AC15" s="521"/>
+      <c r="AD15" s="520"/>
+      <c r="AE15" s="533"/>
     </row>
     <row r="16" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="519"/>
-      <c r="B16" s="518" t="s">
+      <c r="A16" s="517"/>
+      <c r="B16" s="516" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="518" t="s">
+      <c r="C16" s="516" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="518" t="s">
+      <c r="D16" s="516" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="546" t="s">
+      <c r="E16" s="544" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="547"/>
-      <c r="G16" s="547"/>
-      <c r="H16" s="547"/>
-      <c r="I16" s="547"/>
-      <c r="J16" s="547"/>
-      <c r="K16" s="547"/>
-      <c r="L16" s="547"/>
-      <c r="M16" s="548"/>
-      <c r="N16" s="521"/>
-      <c r="O16" s="523"/>
-      <c r="P16" s="523"/>
-      <c r="Q16" s="523"/>
-      <c r="R16" s="522"/>
+      <c r="F16" s="545"/>
+      <c r="G16" s="545"/>
+      <c r="H16" s="545"/>
+      <c r="I16" s="545"/>
+      <c r="J16" s="545"/>
+      <c r="K16" s="545"/>
+      <c r="L16" s="545"/>
+      <c r="M16" s="546"/>
+      <c r="N16" s="519"/>
+      <c r="O16" s="521"/>
+      <c r="P16" s="521"/>
+      <c r="Q16" s="521"/>
+      <c r="R16" s="520"/>
       <c r="S16" s="231"/>
       <c r="T16" s="231"/>
-      <c r="U16" s="540"/>
-      <c r="V16" s="541"/>
-      <c r="W16" s="542"/>
-      <c r="X16" s="524" t="s">
+      <c r="U16" s="538"/>
+      <c r="V16" s="539"/>
+      <c r="W16" s="540"/>
+      <c r="X16" s="522" t="s">
         <v>31</v>
       </c>
-      <c r="Y16" s="525"/>
-      <c r="Z16" s="526"/>
-      <c r="AA16" s="518" t="s">
+      <c r="Y16" s="523"/>
+      <c r="Z16" s="524"/>
+      <c r="AA16" s="516" t="s">
         <v>32</v>
       </c>
-      <c r="AB16" s="518" t="s">
+      <c r="AB16" s="516" t="s">
         <v>31</v>
       </c>
-      <c r="AC16" s="518" t="s">
+      <c r="AC16" s="516" t="s">
         <v>84</v>
       </c>
-      <c r="AD16" s="518" t="s">
+      <c r="AD16" s="516" t="s">
         <v>32</v>
       </c>
-      <c r="AE16" s="535"/>
+      <c r="AE16" s="533"/>
     </row>
     <row r="17" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="519"/>
-      <c r="B17" s="519"/>
-      <c r="C17" s="519"/>
-      <c r="D17" s="519"/>
-      <c r="E17" s="521" t="s">
+      <c r="A17" s="517"/>
+      <c r="B17" s="517"/>
+      <c r="C17" s="517"/>
+      <c r="D17" s="517"/>
+      <c r="E17" s="519" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="522"/>
-      <c r="G17" s="521" t="s">
+      <c r="F17" s="520"/>
+      <c r="G17" s="519" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="522"/>
-      <c r="I17" s="521" t="s">
+      <c r="H17" s="520"/>
+      <c r="I17" s="519" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="523"/>
-      <c r="K17" s="522"/>
+      <c r="J17" s="521"/>
+      <c r="K17" s="520"/>
       <c r="L17" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="518" t="s">
+      <c r="M17" s="516" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="521" t="s">
+      <c r="N17" s="519" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="523"/>
-      <c r="P17" s="523"/>
-      <c r="Q17" s="522"/>
+      <c r="O17" s="521"/>
+      <c r="P17" s="521"/>
+      <c r="Q17" s="520"/>
       <c r="R17" s="233" t="s">
         <v>47</v>
       </c>
@@ -10378,23 +10383,23 @@
       <c r="T17" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="U17" s="543"/>
-      <c r="V17" s="544"/>
-      <c r="W17" s="545"/>
-      <c r="X17" s="527"/>
-      <c r="Y17" s="528"/>
-      <c r="Z17" s="529"/>
-      <c r="AA17" s="519"/>
-      <c r="AB17" s="519"/>
-      <c r="AC17" s="519"/>
-      <c r="AD17" s="519"/>
-      <c r="AE17" s="535"/>
+      <c r="U17" s="541"/>
+      <c r="V17" s="542"/>
+      <c r="W17" s="543"/>
+      <c r="X17" s="525"/>
+      <c r="Y17" s="526"/>
+      <c r="Z17" s="527"/>
+      <c r="AA17" s="517"/>
+      <c r="AB17" s="517"/>
+      <c r="AC17" s="517"/>
+      <c r="AD17" s="517"/>
+      <c r="AE17" s="533"/>
     </row>
     <row r="18" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A18" s="520"/>
-      <c r="B18" s="520"/>
-      <c r="C18" s="520"/>
-      <c r="D18" s="520"/>
+      <c r="A18" s="518"/>
+      <c r="B18" s="518"/>
+      <c r="C18" s="518"/>
+      <c r="D18" s="518"/>
       <c r="E18" s="233" t="s">
         <v>61</v>
       </c>
@@ -10417,7 +10422,7 @@
         <v>83</v>
       </c>
       <c r="L18" s="233"/>
-      <c r="M18" s="520"/>
+      <c r="M18" s="518"/>
       <c r="N18" s="233" t="s">
         <v>151</v>
       </c>
@@ -10457,11 +10462,11 @@
       <c r="Z18" s="233" t="s">
         <v>150</v>
       </c>
-      <c r="AA18" s="520"/>
-      <c r="AB18" s="520"/>
-      <c r="AC18" s="520"/>
-      <c r="AD18" s="520"/>
-      <c r="AE18" s="536"/>
+      <c r="AA18" s="518"/>
+      <c r="AB18" s="518"/>
+      <c r="AC18" s="518"/>
+      <c r="AD18" s="518"/>
+      <c r="AE18" s="534"/>
     </row>
     <row r="19" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="214" t="s">
@@ -13057,107 +13062,107 @@
       <c r="AE46" s="195"/>
     </row>
     <row r="47" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="492" t="s">
+      <c r="A47" s="490" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="493"/>
-      <c r="C47" s="493"/>
-      <c r="D47" s="493"/>
-      <c r="E47" s="493"/>
-      <c r="F47" s="493"/>
-      <c r="G47" s="494"/>
-      <c r="H47" s="495" t="s">
+      <c r="B47" s="491"/>
+      <c r="C47" s="491"/>
+      <c r="D47" s="491"/>
+      <c r="E47" s="491"/>
+      <c r="F47" s="491"/>
+      <c r="G47" s="492"/>
+      <c r="H47" s="493" t="s">
         <v>171</v>
       </c>
-      <c r="I47" s="495"/>
-      <c r="J47" s="516" t="s">
+      <c r="I47" s="493"/>
+      <c r="J47" s="514" t="s">
         <v>212</v>
       </c>
-      <c r="K47" s="461" t="s">
+      <c r="K47" s="459" t="s">
         <v>220</v>
       </c>
       <c r="L47" s="196"/>
       <c r="M47" s="196"/>
-      <c r="N47" s="496" t="s">
+      <c r="N47" s="494" t="s">
         <v>251</v>
       </c>
-      <c r="O47" s="496"/>
-      <c r="P47" s="496"/>
-      <c r="Q47" s="496"/>
-      <c r="R47" s="496"/>
-      <c r="S47" s="496"/>
-      <c r="T47" s="496"/>
-      <c r="U47" s="496"/>
-      <c r="V47" s="496"/>
-      <c r="W47" s="496"/>
-      <c r="X47" s="496"/>
-      <c r="Y47" s="496"/>
-      <c r="Z47" s="496"/>
-      <c r="AA47" s="496"/>
+      <c r="O47" s="494"/>
+      <c r="P47" s="494"/>
+      <c r="Q47" s="494"/>
+      <c r="R47" s="494"/>
+      <c r="S47" s="494"/>
+      <c r="T47" s="494"/>
+      <c r="U47" s="494"/>
+      <c r="V47" s="494"/>
+      <c r="W47" s="494"/>
+      <c r="X47" s="494"/>
+      <c r="Y47" s="494"/>
+      <c r="Z47" s="494"/>
+      <c r="AA47" s="494"/>
       <c r="AB47" s="105"/>
       <c r="AC47" s="105"/>
       <c r="AD47" s="105"/>
       <c r="AE47" s="197"/>
     </row>
     <row r="48" spans="1:31" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="492"/>
-      <c r="B48" s="494"/>
-      <c r="C48" s="497" t="s">
+      <c r="A48" s="490"/>
+      <c r="B48" s="492"/>
+      <c r="C48" s="495" t="s">
         <v>85</v>
       </c>
-      <c r="D48" s="498"/>
-      <c r="E48" s="497" t="s">
+      <c r="D48" s="496"/>
+      <c r="E48" s="495" t="s">
         <v>86</v>
       </c>
-      <c r="F48" s="498"/>
+      <c r="F48" s="496"/>
       <c r="G48" s="198"/>
-      <c r="H48" s="495"/>
-      <c r="I48" s="495"/>
-      <c r="J48" s="517"/>
-      <c r="K48" s="462"/>
+      <c r="H48" s="493"/>
+      <c r="I48" s="493"/>
+      <c r="J48" s="515"/>
+      <c r="K48" s="460"/>
       <c r="L48" s="196"/>
       <c r="M48" s="196"/>
-      <c r="N48" s="499" t="s">
+      <c r="N48" s="497" t="s">
         <v>52</v>
       </c>
-      <c r="O48" s="500"/>
-      <c r="P48" s="501"/>
-      <c r="Q48" s="508" t="s">
+      <c r="O48" s="498"/>
+      <c r="P48" s="499"/>
+      <c r="Q48" s="506" t="s">
         <v>51</v>
       </c>
-      <c r="R48" s="509"/>
-      <c r="S48" s="509"/>
-      <c r="T48" s="509"/>
-      <c r="U48" s="509"/>
-      <c r="V48" s="509"/>
-      <c r="W48" s="509"/>
-      <c r="X48" s="509"/>
-      <c r="Y48" s="509"/>
-      <c r="Z48" s="509"/>
-      <c r="AA48" s="510"/>
+      <c r="R48" s="507"/>
+      <c r="S48" s="507"/>
+      <c r="T48" s="507"/>
+      <c r="U48" s="507"/>
+      <c r="V48" s="507"/>
+      <c r="W48" s="507"/>
+      <c r="X48" s="507"/>
+      <c r="Y48" s="507"/>
+      <c r="Z48" s="507"/>
+      <c r="AA48" s="508"/>
       <c r="AB48" s="105"/>
       <c r="AC48" s="105"/>
       <c r="AD48" s="105"/>
       <c r="AE48" s="197"/>
     </row>
     <row r="49" spans="1:31" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="511" t="s">
+      <c r="A49" s="509" t="s">
         <v>152</v>
       </c>
-      <c r="B49" s="512"/>
-      <c r="C49" s="486">
+      <c r="B49" s="510"/>
+      <c r="C49" s="484">
         <v>26</v>
       </c>
-      <c r="D49" s="487"/>
-      <c r="E49" s="486">
+      <c r="D49" s="485"/>
+      <c r="E49" s="484">
         <v>5</v>
       </c>
-      <c r="F49" s="487"/>
+      <c r="F49" s="485"/>
       <c r="G49" s="199"/>
-      <c r="H49" s="488">
+      <c r="H49" s="486">
         <v>26</v>
       </c>
-      <c r="I49" s="488"/>
+      <c r="I49" s="486"/>
       <c r="J49" s="198">
         <v>8</v>
       </c>
@@ -13166,38 +13171,38 @@
       </c>
       <c r="L49" s="196"/>
       <c r="M49" s="196"/>
-      <c r="N49" s="502"/>
-      <c r="O49" s="503"/>
-      <c r="P49" s="504"/>
-      <c r="Q49" s="489" t="s">
+      <c r="N49" s="500"/>
+      <c r="O49" s="501"/>
+      <c r="P49" s="502"/>
+      <c r="Q49" s="487" t="s">
         <v>40</v>
       </c>
-      <c r="R49" s="490"/>
-      <c r="S49" s="490"/>
-      <c r="T49" s="490"/>
-      <c r="U49" s="491"/>
-      <c r="V49" s="489" t="s">
+      <c r="R49" s="488"/>
+      <c r="S49" s="488"/>
+      <c r="T49" s="488"/>
+      <c r="U49" s="489"/>
+      <c r="V49" s="487" t="s">
         <v>41</v>
       </c>
-      <c r="W49" s="491"/>
-      <c r="X49" s="489" t="s">
+      <c r="W49" s="489"/>
+      <c r="X49" s="487" t="s">
         <v>37</v>
       </c>
-      <c r="Y49" s="490"/>
-      <c r="Z49" s="490"/>
-      <c r="AA49" s="491"/>
+      <c r="Y49" s="488"/>
+      <c r="Z49" s="488"/>
+      <c r="AA49" s="489"/>
       <c r="AB49" s="105"/>
       <c r="AC49" s="105"/>
       <c r="AD49" s="105"/>
       <c r="AE49" s="197"/>
     </row>
     <row r="50" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="513"/>
-      <c r="B50" s="513"/>
-      <c r="C50" s="513"/>
-      <c r="D50" s="513"/>
-      <c r="E50" s="513"/>
-      <c r="F50" s="513"/>
+      <c r="A50" s="511"/>
+      <c r="B50" s="511"/>
+      <c r="C50" s="511"/>
+      <c r="D50" s="511"/>
+      <c r="E50" s="511"/>
+      <c r="F50" s="511"/>
       <c r="G50" s="200"/>
       <c r="H50" s="196"/>
       <c r="I50" s="196"/>
@@ -13205,15 +13210,15 @@
       <c r="K50" s="196"/>
       <c r="L50" s="196"/>
       <c r="M50" s="196"/>
-      <c r="N50" s="505"/>
-      <c r="O50" s="506"/>
-      <c r="P50" s="507"/>
-      <c r="Q50" s="489" t="s">
+      <c r="N50" s="503"/>
+      <c r="O50" s="504"/>
+      <c r="P50" s="505"/>
+      <c r="Q50" s="487" t="s">
         <v>42</v>
       </c>
-      <c r="R50" s="490"/>
-      <c r="S50" s="490"/>
-      <c r="T50" s="491"/>
+      <c r="R50" s="488"/>
+      <c r="S50" s="488"/>
+      <c r="T50" s="489"/>
       <c r="U50" s="184" t="s">
         <v>43</v>
       </c>
@@ -13223,10 +13228,10 @@
       <c r="W50" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="X50" s="514" t="s">
+      <c r="X50" s="512" t="s">
         <v>42</v>
       </c>
-      <c r="Y50" s="515"/>
+      <c r="Y50" s="513"/>
       <c r="Z50" s="202"/>
       <c r="AA50" s="201" t="s">
         <v>43</v>
@@ -13237,33 +13242,33 @@
       <c r="AE50" s="197"/>
     </row>
     <row r="51" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="479"/>
-      <c r="B51" s="479"/>
-      <c r="C51" s="480"/>
-      <c r="D51" s="480"/>
-      <c r="E51" s="480"/>
+      <c r="A51" s="477"/>
+      <c r="B51" s="477"/>
+      <c r="C51" s="478"/>
+      <c r="D51" s="478"/>
+      <c r="E51" s="478"/>
       <c r="F51" s="203"/>
       <c r="G51" s="204"/>
-      <c r="H51" s="471" t="s">
+      <c r="H51" s="469" t="s">
         <v>44</v>
       </c>
-      <c r="I51" s="472"/>
-      <c r="J51" s="472"/>
-      <c r="K51" s="472"/>
-      <c r="L51" s="472"/>
-      <c r="M51" s="473"/>
-      <c r="N51" s="481">
+      <c r="I51" s="470"/>
+      <c r="J51" s="470"/>
+      <c r="K51" s="470"/>
+      <c r="L51" s="470"/>
+      <c r="M51" s="471"/>
+      <c r="N51" s="479">
         <f>16.81-7.24</f>
         <v>9.5699999999999985</v>
       </c>
-      <c r="O51" s="482"/>
-      <c r="P51" s="483"/>
-      <c r="Q51" s="484">
+      <c r="O51" s="480"/>
+      <c r="P51" s="481"/>
+      <c r="Q51" s="482">
         <v>12</v>
       </c>
-      <c r="R51" s="485"/>
-      <c r="S51" s="485"/>
-      <c r="T51" s="485"/>
+      <c r="R51" s="483"/>
+      <c r="S51" s="483"/>
+      <c r="T51" s="483"/>
       <c r="U51" s="205">
         <v>7.2</v>
       </c>
@@ -13273,11 +13278,11 @@
       <c r="W51" s="207">
         <v>8.75</v>
       </c>
-      <c r="X51" s="465">
+      <c r="X51" s="463">
         <f>Q51+V51</f>
         <v>28</v>
       </c>
-      <c r="Y51" s="466"/>
+      <c r="Y51" s="464"/>
       <c r="Z51" s="208"/>
       <c r="AA51" s="207">
         <f>U51+W51</f>
@@ -13289,33 +13294,33 @@
       <c r="AE51" s="197"/>
     </row>
     <row r="52" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="469"/>
-      <c r="B52" s="469"/>
-      <c r="C52" s="470"/>
-      <c r="D52" s="470"/>
-      <c r="E52" s="470"/>
-      <c r="F52" s="470"/>
+      <c r="A52" s="467"/>
+      <c r="B52" s="467"/>
+      <c r="C52" s="468"/>
+      <c r="D52" s="468"/>
+      <c r="E52" s="468"/>
+      <c r="F52" s="468"/>
       <c r="G52" s="204"/>
-      <c r="H52" s="471" t="s">
+      <c r="H52" s="469" t="s">
         <v>45</v>
       </c>
-      <c r="I52" s="472"/>
-      <c r="J52" s="472"/>
-      <c r="K52" s="472"/>
-      <c r="L52" s="472"/>
-      <c r="M52" s="473"/>
-      <c r="N52" s="474">
+      <c r="I52" s="470"/>
+      <c r="J52" s="470"/>
+      <c r="K52" s="470"/>
+      <c r="L52" s="470"/>
+      <c r="M52" s="471"/>
+      <c r="N52" s="472">
         <f>3.25-2.2</f>
         <v>1.0499999999999998</v>
       </c>
-      <c r="O52" s="475"/>
-      <c r="P52" s="476"/>
-      <c r="Q52" s="477">
-        <v>0</v>
-      </c>
-      <c r="R52" s="478"/>
-      <c r="S52" s="478"/>
-      <c r="T52" s="478"/>
+      <c r="O52" s="473"/>
+      <c r="P52" s="474"/>
+      <c r="Q52" s="475">
+        <v>0</v>
+      </c>
+      <c r="R52" s="476"/>
+      <c r="S52" s="476"/>
+      <c r="T52" s="476"/>
       <c r="U52" s="209">
         <v>0</v>
       </c>
@@ -13325,11 +13330,11 @@
       <c r="W52" s="207">
         <v>1.9</v>
       </c>
-      <c r="X52" s="465">
+      <c r="X52" s="463">
         <f>Q52+V52</f>
         <v>9</v>
       </c>
-      <c r="Y52" s="466"/>
+      <c r="Y52" s="464"/>
       <c r="Z52" s="208"/>
       <c r="AA52" s="207">
         <f>U52+W52</f>
@@ -13341,12 +13346,12 @@
       <c r="AE52" s="197"/>
     </row>
     <row r="53" spans="1:31" ht="20.25" x14ac:dyDescent="0.15">
-      <c r="A53" s="467"/>
-      <c r="B53" s="467"/>
-      <c r="C53" s="468"/>
-      <c r="D53" s="468"/>
-      <c r="E53" s="468"/>
-      <c r="F53" s="468"/>
+      <c r="A53" s="465"/>
+      <c r="B53" s="465"/>
+      <c r="C53" s="466"/>
+      <c r="D53" s="466"/>
+      <c r="E53" s="466"/>
+      <c r="F53" s="466"/>
       <c r="G53" s="173"/>
       <c r="H53" s="172"/>
       <c r="I53" s="172"/>
@@ -13370,29 +13375,29 @@
       <c r="AE54" s="24"/>
     </row>
     <row r="55" spans="1:31" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A55" s="463" t="s">
+      <c r="A55" s="461" t="s">
         <v>153</v>
       </c>
-      <c r="B55" s="463"/>
-      <c r="C55" s="463"/>
-      <c r="D55" s="463"/>
-      <c r="E55" s="463"/>
-      <c r="F55" s="463"/>
-      <c r="G55" s="463"/>
-      <c r="H55" s="463"/>
-      <c r="I55" s="463"/>
-      <c r="J55" s="463"/>
-      <c r="K55" s="463"/>
-      <c r="L55" s="463"/>
-      <c r="M55" s="463"/>
-      <c r="N55" s="464" t="str">
+      <c r="B55" s="461"/>
+      <c r="C55" s="461"/>
+      <c r="D55" s="461"/>
+      <c r="E55" s="461"/>
+      <c r="F55" s="461"/>
+      <c r="G55" s="461"/>
+      <c r="H55" s="461"/>
+      <c r="I55" s="461"/>
+      <c r="J55" s="461"/>
+      <c r="K55" s="461"/>
+      <c r="L55" s="461"/>
+      <c r="M55" s="461"/>
+      <c r="N55" s="462" t="str">
         <f>AB1</f>
         <v>20.09.2026</v>
       </c>
-      <c r="O55" s="464"/>
-      <c r="P55" s="464"/>
-      <c r="Q55" s="464"/>
-      <c r="R55" s="464"/>
+      <c r="O55" s="462"/>
+      <c r="P55" s="462"/>
+      <c r="Q55" s="462"/>
+      <c r="R55" s="462"/>
       <c r="S55" s="183"/>
       <c r="T55" s="183"/>
       <c r="U55" s="36"/>
@@ -13409,29 +13414,29 @@
       <c r="AE56" s="24"/>
     </row>
     <row r="57" spans="1:31" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="463" t="s">
+      <c r="A57" s="461" t="s">
         <v>154</v>
       </c>
-      <c r="B57" s="463"/>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
-      <c r="G57" s="463"/>
-      <c r="H57" s="463"/>
-      <c r="I57" s="463"/>
-      <c r="J57" s="463"/>
-      <c r="K57" s="463"/>
-      <c r="L57" s="463"/>
-      <c r="M57" s="463"/>
-      <c r="N57" s="464" t="str">
+      <c r="B57" s="461"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
+      <c r="G57" s="461"/>
+      <c r="H57" s="461"/>
+      <c r="I57" s="461"/>
+      <c r="J57" s="461"/>
+      <c r="K57" s="461"/>
+      <c r="L57" s="461"/>
+      <c r="M57" s="461"/>
+      <c r="N57" s="462" t="str">
         <f>AB1</f>
         <v>20.09.2026</v>
       </c>
-      <c r="O57" s="464"/>
-      <c r="P57" s="464"/>
-      <c r="Q57" s="464"/>
-      <c r="R57" s="464"/>
+      <c r="O57" s="462"/>
+      <c r="P57" s="462"/>
+      <c r="Q57" s="462"/>
+      <c r="R57" s="462"/>
       <c r="S57" s="175"/>
       <c r="T57" s="175"/>
       <c r="U57" s="36"/>

--- a/reports/2026-09-20.xlsx
+++ b/reports/2026-09-20.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFCB66DC-5F84-9047-9221-37265C377E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D94A0151-832E-104E-9E26-A50324FD2306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
